--- a/workspaces/btc_daily_14days/dxy/dxy_ma_ratio_50.xlsx
+++ b/workspaces/btc_daily_14days/dxy/dxy_ma_ratio_50.xlsx
@@ -575,46 +575,46 @@
         <v>33</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>2.052016225244564</v>
+        <v>2.045931111009708</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>6.502603234345138</v>
+        <v>6.482393935392267</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.04556610581305875</v>
+        <v>0.04561680496821197</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-5.88924777452219</v>
+        <v>-5.869883181625035</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.3630291716170362</v>
+        <v>-0.3616154384028434</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>2.968665952126969</v>
+        <v>2.959526533816906</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>2.884542457306985</v>
+        <v>2.875604126736221</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>5.453004472087812</v>
+        <v>5.4354214769726</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>2.356945526183253</v>
+        <v>2.349288953263176</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>1.50555359050071</v>
+        <v>1.50057749885049</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>1.300718819214197</v>
+        <v>1.296346217787644</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>1.335672037819101</v>
+        <v>1.331023236853696</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.9143303695153904</v>
+        <v>0.9112466141014437</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-1.874916465186239</v>
+        <v>-1.869097871971434</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>26</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>9.045023218251565</v>
+        <v>9.016115370171441</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.2589714064117601</v>
+        <v>-0.2574982543274729</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>10.89015047799612</v>
+        <v>10.85494821251271</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>3.325057959776053</v>
+        <v>3.314754269711827</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>2.786968342671514</v>
+        <v>2.778162881728996</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.7655548591399395</v>
+        <v>-0.7626898651304614</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-4.702537719965456</v>
+        <v>-4.686943747255967</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-5.171514006220995</v>
+        <v>-5.154818095735244</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-5.233928077666185</v>
+        <v>-5.217021104937423</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-2.23241183818881</v>
+        <v>-2.225309920048304</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-6.293980628421167</v>
+        <v>-6.273728796405848</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>1.45260182681934</v>
+        <v>1.447504322045795</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-2.826456530066189</v>
+        <v>-2.817425184670597</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-6.435281749747446</v>
+        <v>-6.414552417424602</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>49</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>4.649418822647164</v>
+        <v>4.634428637488298</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>11.20389703679168</v>
+        <v>11.16767226397406</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.6024697878344085</v>
+        <v>0.600457314520547</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-1.309500012565124</v>
+        <v>-1.304746366710184</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>4.279897390416167</v>
+        <v>4.266011299805463</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>6.622111644666816</v>
+        <v>6.600717198168354</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>4.494969991171907</v>
+        <v>4.480589773424271</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>4.02829221902892</v>
+        <v>4.015027297202401</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>6.013143046653504</v>
+        <v>5.993355360731364</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>5.162680333372663</v>
+        <v>5.145578820029407</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>9.050693305220946</v>
+        <v>9.020828207175811</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>2.948214498808397</v>
+        <v>2.938097936419609</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-1.56690135352946</v>
+        <v>-1.56184389836136</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-7.459454202078838</v>
+        <v>-7.43496058068898</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>49</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-1.473030156944667</v>
+        <v>-1.46799399024944</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-7.168089457852666</v>
+        <v>-7.144000004394819</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-3.48124876504744</v>
+        <v>-3.469702889528691</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>2.775246389195551</v>
+        <v>2.766507124021075</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.1941826712609327</v>
+        <v>0.1935632954592421</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.4920122957630042</v>
+        <v>0.490508809475692</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.4072168329464532</v>
+        <v>0.4060977097185159</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>1.983987003293258</v>
+        <v>1.977201447132209</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-8.301621422625445</v>
+        <v>-8.274202560255702</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-7.110235048660257</v>
+        <v>-7.086866951223222</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-7.317218426838167</v>
+        <v>-7.293288069126127</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-3.191331663893415</v>
+        <v>-3.181242464428593</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-3.614132517059744</v>
+        <v>-3.60212565514184</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-1.317151451437169</v>
+        <v>-1.312511601098997</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>69</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-1.768800639050554</v>
+        <v>-1.762605995334567</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>3.866972176974123</v>
+        <v>3.85436715085185</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>2.022900233425062</v>
+        <v>2.016128905481509</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>3.604114746917539</v>
+        <v>3.592294447833261</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>7.418529374864136</v>
+        <v>7.393382443348486</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>16.42527178331743</v>
+        <v>16.36966866636178</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>19.24773516794613</v>
+        <v>19.1826654197455</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>18.78497659311413</v>
+        <v>18.72098499303463</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>18.72855740121292</v>
+        <v>18.66512112293723</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>20.78678929696807</v>
+        <v>20.71623675740226</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>17.68090154965842</v>
+        <v>17.62076307191022</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>17.72025247534685</v>
+        <v>17.65971013298864</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>17.30284720530891</v>
+        <v>17.24426327216418</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>20.46615859700474</v>
+        <v>20.39704178547395</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>94</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>4.95337019042833</v>
+        <v>4.936456622839231</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>2.278553750911577</v>
+        <v>2.270923262050658</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>9.33490601911933</v>
+        <v>9.30240975761042</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>8.403028103638576</v>
+        <v>8.374002726333664</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>5.736524172717303</v>
+        <v>5.716130349226191</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>4.970858088380659</v>
+        <v>4.952666440116658</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>8.084039471708486</v>
+        <v>8.054957330542024</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>6.552656347406639</v>
+        <v>6.528415826081471</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>7.559269347892176</v>
+        <v>7.531911355153078</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>8.842182935431111</v>
+        <v>8.810094766853211</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>5.439253778642147</v>
+        <v>5.419066838922411</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>9.743415833172833</v>
+        <v>9.70797527640589</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>11.4585062945598</v>
+        <v>11.41769316150417</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>9.577155397021002</v>
+        <v>9.542894391086037</v>
       </c>
     </row>
     <row r="12">
@@ -887,46 +887,46 @@
         <v>115</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>5.767431245007415</v>
+        <v>5.746620981493088</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>7.636218114552285</v>
+        <v>7.608923146281917</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>6.373337533470284</v>
+        <v>6.349593320445194</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>8.246022698753087</v>
+        <v>8.215886299203255</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>7.709462176603729</v>
+        <v>7.680812624942426</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>9.751216952214435</v>
+        <v>9.714823062792163</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>5.314269352353321</v>
+        <v>5.293448001704725</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>3.105490947827583</v>
+        <v>3.092221136200692</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>6.531143315856006</v>
+        <v>6.505896230633724</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>3.065933256534869</v>
+        <v>3.052720279398159</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>2.861341280862689</v>
+        <v>2.849239848200341</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>5.513988176510985</v>
+        <v>5.491679135938753</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>4.221167095524827</v>
+        <v>4.203968498704647</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>4.472935326554285</v>
+        <v>4.455012799966894</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>120</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.826771653543112</v>
+        <v>-0.8245062031676298</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1.728875499664724</v>
+        <v>1.721672206088051</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>3.835901987846604</v>
+        <v>3.819981575002167</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-1.870870601086082</v>
+        <v>-1.86548386075448</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.7416255493942003</v>
+        <v>-0.740834194462245</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.3909695723085207</v>
+        <v>0.3868710445548942</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>1.141099487437884</v>
+        <v>1.134368399661881</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>4.013582019888695</v>
+        <v>3.996051977126072</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>8.965280808625245</v>
+        <v>8.929306674463895</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>7.28027305989216</v>
+        <v>7.25053382895279</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>2.898303163636449</v>
+        <v>2.885252732644133</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>6.278524875786147</v>
+        <v>6.251881949508729</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>4.185879350662326</v>
+        <v>4.167657936379833</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>4.437775299016074</v>
+        <v>4.418780915908535</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>164</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>5.433390948082703</v>
+        <v>5.411475887552506</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1.383290674040538</v>
+        <v>1.376820194886292</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>5.869848935832415</v>
+        <v>5.844655474898133</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>5.39164640053967</v>
+        <v>5.369215564720726</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>3.023026257077831</v>
+        <v>3.009227696261597</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>5.154334131827632</v>
+        <v>5.131341407860504</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.1843599639827147</v>
+        <v>0.1807813125280759</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.283241021490241</v>
+        <v>-0.2855329188821045</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>2.101124245679721</v>
+        <v>2.088815095411022</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>6.140741343811342</v>
+        <v>6.112909261935485</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>7.771475299900416</v>
+        <v>7.738341742171087</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>5.362791427918673</v>
+        <v>5.337447676172729</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>6.777926308423311</v>
+        <v>6.748063237325397</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>10.7036236086895</v>
+        <v>10.65861831428272</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>190</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>2.243403785053061</v>
+        <v>2.23219431413581</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>2.73807723974322</v>
+        <v>2.725286412867533</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.2376959944228219</v>
+        <v>0.2329215563744569</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.1586305938496437</v>
+        <v>-0.1606698497873538</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>4.045341288473857</v>
+        <v>4.02577112208855</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.6552449266163833</v>
+        <v>0.6482410039777946</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-1.011571300986191</v>
+        <v>-1.010615095715004</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-2.534576678266276</v>
+        <v>-2.527832046010289</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-4.178418916206915</v>
+        <v>-4.166188015059888</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-1.864567781978742</v>
+        <v>-1.862480377779249</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.014793621692348</v>
+        <v>-1.015379635266257</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-5.732606030242998</v>
+        <v>-5.714993770926036</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-3.514937595861426</v>
+        <v>-3.505665797608508</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-4.321251734332165</v>
+        <v>-4.309289259529983</v>
       </c>
     </row>
     <row r="16">
@@ -1095,46 +1095,46 @@
         <v>190</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1.190772206105692</v>
+        <v>1.182747801622369</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.6322287615478004</v>
+        <v>0.6270470985800856</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1.29113392580571</v>
+        <v>1.281118196927146</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>2.475679599763936</v>
+        <v>2.46180494342979</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-1.224166666333367</v>
+        <v>-1.223099137488404</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-2.507648396363727</v>
+        <v>-2.501655995042803</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>4.262223655611564</v>
+        <v>4.240132893517412</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>8.016232388647651</v>
+        <v>7.977489505657907</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>6.903206530392261</v>
+        <v>6.868322396605627</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>6.054068546128555</v>
+        <v>6.021634470547653</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>7.962973232892395</v>
+        <v>7.922869255726752</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>10.11386263082021</v>
+        <v>10.06411719022067</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>9.695431682989273</v>
+        <v>9.647856060732501</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>11.53635413503466</v>
+        <v>11.4801844246809</v>
       </c>
     </row>
     <row r="17">
@@ -1147,46 +1147,46 @@
         <v>237</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-2.704408784344899</v>
+        <v>-2.695088981568333</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.5184756689712913</v>
+        <v>-0.5189745297679949</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.3535337293200058</v>
+        <v>0.3464247184148448</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.329015367366992</v>
+        <v>1.318440548199206</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.635858497442541</v>
+        <v>1.62343429509243</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-2.292202248162795</v>
+        <v>-2.286298768429901</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.108886802893373</v>
+        <v>-1.108791054867261</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-3.691705131495823</v>
+        <v>-3.680609668884934</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.9018162058167292</v>
+        <v>0.8901218402489803</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.320643486814511</v>
+        <v>1.305727844554021</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.424881907189985</v>
+        <v>-1.426441535137691</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-2.660448796564054</v>
+        <v>-2.656988966987278</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-4.354734071896736</v>
+        <v>-4.342670691908737</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-6.64738555535493</v>
+        <v>-6.625522881559718</v>
       </c>
     </row>
     <row r="18">
@@ -1199,46 +1199,46 @@
         <v>219</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>4.584187250566281</v>
+        <v>4.557349674841859</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.6803737156095337</v>
+        <v>-0.6801225987459603</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.075071675362921</v>
+        <v>-1.076055971410966</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1.341034383371905</v>
+        <v>1.328470605055678</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>2.632309544106647</v>
+        <v>2.612446548357575</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.2713546146454533</v>
+        <v>-0.2748714435331436</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-2.186560535903268</v>
+        <v>-2.180850157581794</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-4.028977538890217</v>
+        <v>-4.014108975101969</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-5.921756949662608</v>
+        <v>-5.900141758569376</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-7.233752941852536</v>
+        <v>-7.206956390464555</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-2.858052293100251</v>
+        <v>-2.8524525024811</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-5.116722169465795</v>
+        <v>-5.099874710590512</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-5.541575343666771</v>
+        <v>-5.521150062836981</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-4.832800011988844</v>
+        <v>-4.816378901442867</v>
       </c>
     </row>
     <row r="19">
@@ -1251,46 +1251,46 @@
         <v>229</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-8.825316049467716</v>
+        <v>-8.780781457656374</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-7.81996511044531</v>
+        <v>-7.778848915091388</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-12.15136245432715</v>
+        <v>-12.08921974268061</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-11.58845452486703</v>
+        <v>-11.52957820506496</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-13.00684509591077</v>
+        <v>-12.94121539675031</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-15.77845538419565</v>
+        <v>-15.69401409054057</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-11.92944227834045</v>
+        <v>-11.86690880760958</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-10.65100705873918</v>
+        <v>-10.59535243499712</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-10.71482343280329</v>
+        <v>-10.66154884422077</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-8.502623888836808</v>
+        <v>-8.46329427793593</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-12.21992414061366</v>
+        <v>-12.1597012012631</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-12.19049757809437</v>
+        <v>-12.12989165752642</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-11.74139307363644</v>
+        <v>-11.68150070560281</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-11.49412415523906</v>
+        <v>-11.43638647856007</v>
       </c>
     </row>
     <row r="20">
@@ -1303,46 +1303,46 @@
         <v>237</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.093059570085387</v>
+        <v>1.084483821557768</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>1.591924737327595</v>
+        <v>1.582380932197452</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>2.464747767628097</v>
+        <v>2.447827676496907</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>3.019157081554567</v>
+        <v>2.998277590921958</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>5.863687051428776</v>
+        <v>5.823900217399988</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>9.969649074099451</v>
+        <v>9.909085107511814</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>12.85273993293772</v>
+        <v>12.77142079130459</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>9.426609812848717</v>
+        <v>9.36686239208084</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>8.524832764435644</v>
+        <v>8.467508643011001</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>8.525088826461285</v>
+        <v>8.464746043342132</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>6.626392898546783</v>
+        <v>6.580116951411291</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>6.663981624861698</v>
+        <v>6.618124182319946</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>6.242937796532935</v>
+        <v>6.201756793035585</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>4.375272501280357</v>
+        <v>4.344941253461563</v>
       </c>
     </row>
     <row r="21">
@@ -1355,46 +1355,46 @@
         <v>242</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-2.906661460705749</v>
+        <v>-2.888558329090877</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-2.453443012411327</v>
+        <v>-2.436235676544577</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-3.263295707500568</v>
+        <v>-3.243246527587267</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-2.306308173222185</v>
+        <v>-2.294190576223009</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-2.017540425779217</v>
+        <v>-2.01086594298129</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-3.378609293342116</v>
+        <v>-3.358662274536293</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-3.048050824343669</v>
+        <v>-3.035911241184486</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-6.008405663225396</v>
+        <v>-5.972311197285222</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-10.22105865249658</v>
+        <v>-10.15791573533745</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-11.07768983338823</v>
+        <v>-11.0121652463326</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-8.383040014472499</v>
+        <v>-8.332961393813306</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-9.600317082410221</v>
+        <v>-9.54062011368886</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-8.366677896198347</v>
+        <v>-8.313040346308263</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-5.205847509923466</v>
+        <v>-5.174882995936947</v>
       </c>
     </row>
     <row r="22">
@@ -1407,46 +1407,46 @@
         <v>244</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-2.903274385783746</v>
+        <v>-2.879527095567482</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>2.453790632755911</v>
+        <v>2.435258915008205</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>3.291405830205221</v>
+        <v>3.262797873721219</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>5.067191489282884</v>
+        <v>5.021303706868139</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>3.299688420921257</v>
+        <v>3.263886967956878</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.54272332937191</v>
+        <v>1.527671590630533</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>2.696573067674557</v>
+        <v>2.664366891207081</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>3.872940688613539</v>
+        <v>3.837522844994204</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>1.754425496897319</v>
+        <v>1.736979222436133</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.7454024289101255</v>
+        <v>-0.7459479817313337</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-2.190709623900567</v>
+        <v>-2.176841245302626</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-2.984752537901173</v>
+        <v>-2.961799355304798</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.760152499173095</v>
+        <v>-1.745081668119234</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.506177271994801</v>
+        <v>-1.496519630539453</v>
       </c>
     </row>
     <row r="23">
@@ -1456,49 +1456,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-2.493438320209975</v>
+        <v>-2.491254030379764</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-2.556520321107115</v>
+        <v>-2.554653961038007</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-3.729436638477928</v>
+        <v>-3.727098847689973</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.657350600727362</v>
+        <v>-1.657054832744635</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.6413821846327679</v>
+        <v>-0.6421452342663372</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>2.37740181086096</v>
+        <v>2.375184130273311</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>1.910795892106819</v>
+        <v>1.90800861672701</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>2.038264560005189</v>
+        <v>2.035938214096426</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>2.189432984895035</v>
+        <v>2.187267865873942</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.9534203503875034</v>
+        <v>0.9520696698582327</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.3612181152167437</v>
+        <v>0.360733141370325</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.3964368697722165</v>
+        <v>0.3962755597308956</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>1.148211251934704</v>
+        <v>1.147581320627047</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.1645462252029475</v>
+        <v>-0.1645524174245594</v>
       </c>
     </row>
     <row r="24">
@@ -1508,49 +1508,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>2.186364635454993</v>
+        <v>2.195713570351018</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-2.876476241775727</v>
+        <v>-2.901095481861255</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.300211559018543</v>
+        <v>-1.30968166610694</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-5.11935483276843</v>
+        <v>-5.149013199952655</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-2.694422024599838</v>
+        <v>-2.70084568534736</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-7.348552327877208</v>
+        <v>-7.395604780913374</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-8.917966075734725</v>
+        <v>-8.966568965825068</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-4.934423545230622</v>
+        <v>-4.959394823828355</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-4.007328945417868</v>
+        <v>-4.028359684765256</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-5.085823642557905</v>
+        <v>-5.115354136113766</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-5.509710269222161</v>
+        <v>-5.548268909164435</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-3.70777919139266</v>
+        <v>-3.736848856772816</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.6573776822601332</v>
+        <v>-0.6635166368341743</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-3.390270386984653</v>
+        <v>-3.414552417424602</v>
       </c>
     </row>
     <row r="25">
@@ -1560,49 +1560,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.937882764654354</v>
+        <v>-1.968052753617727</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>4.231882362315929</v>
+        <v>4.268699089700021</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2.171145424840084</v>
+        <v>2.193681295568574</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.6339783022977841</v>
+        <v>0.6464051032654297</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.4582108634480804</v>
+        <v>-0.4442702585785909</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>2.625802423017589</v>
+        <v>2.655138223160705</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.064068968082253</v>
+        <v>-1.06159229990331</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.1446677072541362</v>
+        <v>0.1578004891110396</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>2.31819016629521</v>
+        <v>2.352518075357636</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>4.819882477342787</v>
+        <v>4.879714799141958</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>5.732452619077577</v>
+        <v>5.79135399468182</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>8.559977381872173</v>
+        <v>8.647468759173805</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>5.106221435954737</v>
+        <v>5.160746725960408</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>5.672714075178874</v>
+        <v>5.732340237942637</v>
       </c>
     </row>
     <row r="26">
@@ -1615,46 +1615,46 @@
         <v>148</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>6.966021139249484</v>
+        <v>6.928467361538239</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1.301641776910344</v>
+        <v>1.295400253514487</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>2.940807788049483</v>
+        <v>2.920167799579666</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1.720890672899941</v>
+        <v>1.705162174596353</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.5101549573391679</v>
+        <v>0.4941571146276047</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>3.523686671667946</v>
+        <v>3.497501323588239</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>4.124200336403405</v>
+        <v>4.088443281991715</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>3.653367755403593</v>
+        <v>3.621259883210172</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>2.912229342319165</v>
+        <v>2.884584321352193</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.01730955792317701</v>
+        <v>0.007432109297248246</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>2.525082140333687</v>
+        <v>2.505381487682364</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.1596291370417973</v>
+        <v>-0.1629380576749</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.7774739600427978</v>
+        <v>0.7681586827315456</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>1.028654965206421</v>
+        <v>1.017880015007833</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>183</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>5.976507034981282</v>
+        <v>5.926029716853641</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>2.730018060484703</v>
+        <v>2.707873556671032</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.6965999215210701</v>
+        <v>0.6835405947941666</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-2.463910051062769</v>
+        <v>-2.452491967878856</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-2.999612784920636</v>
+        <v>-2.994447324050554</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.59652719525306</v>
+        <v>0.58065004608126</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>2.725831433283609</v>
+        <v>2.681708678535699</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.04806218014786623</v>
+        <v>0.02873293002745214</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>2.1907439464226</v>
+        <v>2.153525393571954</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>2.432678634935336</v>
+        <v>2.396296383407417</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.01503805563105232</v>
+        <v>0.0057507093630349</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>2.803160253310516</v>
+        <v>2.772374303866961</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.7269799771533059</v>
+        <v>0.7127754306269409</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>2.632626974641902</v>
+        <v>2.601841025198347</v>
       </c>
     </row>
     <row r="28">
@@ -1716,49 +1716,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-2.143787970559607</v>
+        <v>-2.146868935704354</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-2.360695715644837</v>
+        <v>-2.373060539119869</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-1.681145360030399</v>
+        <v>-1.683937737910362</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-3.275538406608696</v>
+        <v>-3.293926439257511</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-1.018717856747521</v>
+        <v>-1.010116131515446</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-4.238591034821468</v>
+        <v>-4.255996855441822</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-10.67559356141203</v>
+        <v>-10.72370929611831</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-11.13155909002221</v>
+        <v>-11.19089269489981</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-9.788006788686104</v>
+        <v>-9.833452864770074</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-5.700386792066411</v>
+        <v>-5.719039042705809</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-6.595575124962409</v>
+        <v>-6.633012225179392</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-6.56493125767409</v>
+        <v>-6.598629067834004</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-6.978953718523798</v>
+        <v>-7.018883678778842</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-5.327173058767166</v>
+        <v>-5.350722630190539</v>
       </c>
     </row>
     <row r="29">
@@ -1768,49 +1768,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-2.493438320210039</v>
+        <v>-2.52436296715365</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.2569359711552082</v>
+        <v>-0.2628318995955183</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.4276555921132328</v>
+        <v>0.4813927684688863</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>1.657358999583288</v>
+        <v>1.70941162495599</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.5101324729868466</v>
+        <v>-0.4395559971280463</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-6.124312979920973</v>
+        <v>-6.296000042946794</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-4.057726283497082</v>
+        <v>-4.133542748983118</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-7.718001358149692</v>
+        <v>-7.971512664618558</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-9.990568670780426</v>
+        <v>-10.27970356203684</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-10.84069385580835</v>
+        <v>-11.12982874706477</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-6.607250574040968</v>
+        <v>-6.840200048910411</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-5.508503524738529</v>
+        <v>-5.682221385946995</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.4563211440176147</v>
+        <v>-0.4844984688020446</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-6.781055078334354</v>
+        <v>-6.976350170233623</v>
       </c>
     </row>
     <row r="30">
@@ -2213,10 +2213,8 @@
           <t>X &gt; -0.02849</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>4045~4058</t>
-        </is>
+      <c r="B6" t="n">
+        <v>4045</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>0.1679712411502976</v>
@@ -2267,10 +2265,8 @@
           <t>X &gt; -0.02654</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>4012~4025</t>
-        </is>
+      <c r="B7" t="n">
+        <v>4012</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>0.1525244127092762</v>
@@ -2321,10 +2317,8 @@
           <t>X &gt; -0.02458</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>3986~3999</t>
-        </is>
+      <c r="B8" t="n">
+        <v>3986</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>0.09470871654921353</v>
@@ -2375,10 +2369,8 @@
           <t>X &gt; -0.02262</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>3937~3950</t>
-        </is>
+      <c r="B9" t="n">
+        <v>3937</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>0.0382072494102772</v>
@@ -2429,10 +2421,8 @@
           <t>X &gt; -0.02066</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>3888~3901</t>
-        </is>
+      <c r="B10" t="n">
+        <v>3888</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>0.05718972388128662</v>
@@ -2483,10 +2473,8 @@
           <t>X &gt; -0.0187</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>3819~3832</t>
-        </is>
+      <c r="B11" t="n">
+        <v>3819</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>0.09006898667937691</v>
@@ -2537,10 +2525,8 @@
           <t>X &gt; -0.01674</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>3725~3738</t>
-        </is>
+      <c r="B12" t="n">
+        <v>3725</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>-0.0322291174277396</v>
@@ -2591,10 +2577,8 @@
           <t>X &gt; -0.01478</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>3610~3623</t>
-        </is>
+      <c r="B13" t="n">
+        <v>3610</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>-0.2163199100526469</v>
@@ -2645,10 +2629,8 @@
           <t>X &gt; -0.01283</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>3490~3503</t>
-        </is>
+      <c r="B14" t="n">
+        <v>3490</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>-0.1954080604326478</v>
@@ -2699,10 +2681,8 @@
           <t>X &gt; -0.01087</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>3326~3339</t>
-        </is>
+      <c r="B15" t="n">
+        <v>3326</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>-0.4718749778919218</v>
@@ -2753,10 +2733,8 @@
           <t>X &gt; -0.008909</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>3136~3149</t>
-        </is>
+      <c r="B16" t="n">
+        <v>3136</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>-0.6357057066818683</v>
@@ -2807,10 +2785,8 @@
           <t>X &gt; -0.006951</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2946~2959</t>
-        </is>
+      <c r="B17" t="n">
+        <v>2946</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>-0.7529854645154757</v>
@@ -2861,10 +2837,8 @@
           <t>X &gt; -0.004993</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2709~2722</t>
-        </is>
+      <c r="B18" t="n">
+        <v>2709</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>-0.5830782908198202</v>
@@ -2915,10 +2889,8 @@
           <t>X &gt; -0.003034</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2490~2503</t>
-        </is>
+      <c r="B19" t="n">
+        <v>2490</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>-1.035188220329829</v>
@@ -2969,10 +2941,8 @@
           <t>X &gt; -0.001076</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2261~2274</t>
-        </is>
+      <c r="B20" t="n">
+        <v>2261</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>-0.2506942568854313</v>
@@ -3023,10 +2993,8 @@
           <t>X &gt; 0.0008829</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2024~2037</t>
-        </is>
+      <c r="B21" t="n">
+        <v>2024</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>-0.407036749272315</v>
@@ -3077,10 +3045,8 @@
           <t>X &gt; 0.002841</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>1782~1795</t>
-        </is>
+      <c r="B22" t="n">
+        <v>1782</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>-0.07003999151916673</v>
@@ -3131,10 +3097,8 @@
           <t>X &gt; 0.0048</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>1538~1551</t>
-        </is>
+      <c r="B23" t="n">
+        <v>1538</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>0.375678378693955</v>
@@ -3185,10 +3149,8 @@
           <t>X &gt; 0.006758</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>1282~1293</t>
-        </is>
+      <c r="B24" t="n">
+        <v>1282</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>0.9481703418163221</v>
@@ -3239,10 +3201,8 @@
           <t>X &gt; 0.008717</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>1082~1090</t>
-        </is>
+      <c r="B25" t="n">
+        <v>1082</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>0.7175708541019574</v>
@@ -3293,10 +3253,8 @@
           <t>X &gt; 0.01068</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>905~910</t>
-        </is>
+      <c r="B26" t="n">
+        <v>905</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>1.242825416053762</v>
@@ -3347,10 +3305,8 @@
           <t>X &gt; 0.01263</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>757~762</t>
-        </is>
+      <c r="B27" t="n">
+        <v>757</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>0.1312335958005235</v>
@@ -3401,10 +3357,8 @@
           <t>X &gt; 0.01459</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>574~579</t>
-        </is>
+      <c r="B28" t="n">
+        <v>574</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>-1.716236247671112</v>
@@ -3455,10 +3409,8 @@
           <t>X &gt; 0.01655</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>433~436</t>
-        </is>
+      <c r="B29" t="n">
+        <v>433</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>-1.576007127549431</v>
@@ -3509,10 +3461,8 @@
           <t>X &gt; 0.01851</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>344~344</t>
-        </is>
+      <c r="B30" t="n">
+        <v>344</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>-1.330647622535551</v>
@@ -3563,10 +3513,8 @@
           <t>X &gt; 0.02047</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>257~257</t>
-        </is>
+      <c r="B31" t="n">
+        <v>257</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>0.4248496175332193</v>
@@ -3617,10 +3565,8 @@
           <t>X &gt; 0.02243</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>185~185</t>
-        </is>
+      <c r="B32" t="n">
+        <v>185</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>1.560615733844081</v>
@@ -3671,10 +3617,8 @@
           <t>X &gt; 0.02438</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>146~146</t>
-        </is>
+      <c r="B33" t="n">
+        <v>146</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>2.301082227735229</v>
@@ -3725,10 +3669,8 @@
           <t>X &gt; 0.02634</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>112~112</t>
-        </is>
+      <c r="B34" t="n">
+        <v>112</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>1.970847394075733</v>
@@ -3779,10 +3721,8 @@
           <t>X &gt; 0.0283</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>83~83</t>
-        </is>
+      <c r="B35" t="n">
+        <v>83</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>0.5186098725611146</v>
@@ -3967,10 +3907,8 @@
           <t>X &lt; -0.02849</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>83~83</t>
-        </is>
+      <c r="B6" t="n">
+        <v>83</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>-5.505486512981058</v>
@@ -4021,10 +3959,8 @@
           <t>X &lt; -0.02654</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>116~116</t>
-        </is>
+      <c r="B7" t="n">
+        <v>116</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>-3.355507285727221</v>
@@ -4075,10 +4011,8 @@
           <t>X &lt; -0.02458</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>142~142</t>
-        </is>
+      <c r="B8" t="n">
+        <v>142</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>-1.084987615984623</v>
@@ -4129,10 +4063,8 @@
           <t>X &lt; -0.02262</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>191~191</t>
-        </is>
+      <c r="B9" t="n">
+        <v>191</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>0.3861428316224789</v>
@@ -4183,10 +4115,8 @@
           <t>X &lt; -0.02066</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>240~240</t>
-        </is>
+      <c r="B10" t="n">
+        <v>240</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>0.006561679790024755</v>
@@ -4237,10 +4167,8 @@
           <t>X &lt; -0.0187</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>309~309</t>
-        </is>
+      <c r="B11" t="n">
+        <v>309</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>-0.3898784496598111</v>
@@ -4291,10 +4219,8 @@
           <t>X &lt; -0.01674</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>403~403</t>
-        </is>
+      <c r="B12" t="n">
+        <v>403</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>0.8564376103111186</v>
@@ -4345,10 +4271,8 @@
           <t>X &lt; -0.01478</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>518~518</t>
-        </is>
+      <c r="B13" t="n">
+        <v>518</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>1.946716119944469</v>
@@ -4399,10 +4323,8 @@
           <t>X &lt; -0.01283</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>638~638</t>
-        </is>
+      <c r="B14" t="n">
+        <v>638</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>1.425056977595673</v>
@@ -4453,10 +4375,8 @@
           <t>X &lt; -0.01087</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>802~802</t>
-        </is>
+      <c r="B15" t="n">
+        <v>802</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>2.24471629325636</v>
@@ -4507,10 +4427,8 @@
           <t>X &lt; -0.008909</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>992~992</t>
-        </is>
+      <c r="B16" t="n">
+        <v>992</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>2.244464905596473</v>
@@ -4561,10 +4479,8 @@
           <t>X &lt; -0.006951</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1182~1182</t>
-        </is>
+      <c r="B17" t="n">
+        <v>1182</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>2.075089598571751</v>
@@ -4615,10 +4531,8 @@
           <t>X &lt; -0.004993</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1419~1419</t>
-        </is>
+      <c r="B18" t="n">
+        <v>1419</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>1.276822426794951</v>
@@ -4669,10 +4583,8 @@
           <t>X &lt; -0.003034</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1638~1638</t>
-        </is>
+      <c r="B19" t="n">
+        <v>1638</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>1.719015892244236</v>
@@ -4723,10 +4635,8 @@
           <t>X &lt; -0.001076</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1867~1867</t>
-        </is>
+      <c r="B20" t="n">
+        <v>1867</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>0.4256832652211955</v>
@@ -4777,10 +4687,8 @@
           <t>X &lt; 0.0008829</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2104~2104</t>
-        </is>
+      <c r="B21" t="n">
+        <v>2104</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>0.5008582577367875</v>
@@ -4831,10 +4739,8 @@
           <t>X &lt; 0.002841</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2346~2346</t>
-        </is>
+      <c r="B22" t="n">
+        <v>2346</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>0.1493579287243776</v>
@@ -4885,10 +4791,8 @@
           <t>X &lt; 0.0048</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2590~2590</t>
-        </is>
+      <c r="B23" t="n">
+        <v>2590</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>-0.1382259649976234</v>
@@ -4939,10 +4843,8 @@
           <t>X &lt; 0.006758</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2846~2848</t>
-        </is>
+      <c r="B24" t="n">
+        <v>2846</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>-0.3515843876257065</v>
@@ -4993,10 +4895,8 @@
           <t>X &lt; 0.008717</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>3046~3051</t>
-        </is>
+      <c r="B25" t="n">
+        <v>3046</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>-0.1827205227665161</v>
@@ -5047,10 +4947,8 @@
           <t>X &lt; 0.01068</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>3223~3231</t>
-        </is>
+      <c r="B26" t="n">
+        <v>3223</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>-0.2805011490555387</v>
@@ -5101,10 +4999,8 @@
           <t>X &lt; 0.01263</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>3371~3379</t>
-        </is>
+      <c r="B27" t="n">
+        <v>3371</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>0.03689609825703144</v>
@@ -5155,10 +5051,8 @@
           <t>X &lt; 0.01459</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>3554~3562</t>
-        </is>
+      <c r="B28" t="n">
+        <v>3554</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>0.3420473619910354</v>
@@ -5209,10 +5103,8 @@
           <t>X &lt; 0.01655</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>3695~3705</t>
-        </is>
+      <c r="B29" t="n">
+        <v>3695</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>0.2461028403838199</v>
@@ -5263,10 +5155,8 @@
           <t>X &lt; 0.01851</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>3784~3797</t>
-        </is>
+      <c r="B30" t="n">
+        <v>3784</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>0.1797247032295886</v>
@@ -5317,10 +5207,8 @@
           <t>X &lt; 0.02047</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>3871~3884</t>
-        </is>
+      <c r="B31" t="n">
+        <v>3871</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>0.02973366743162842</v>
@@ -5371,10 +5259,8 @@
           <t>X &lt; 0.02243</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>3943~3956</t>
-        </is>
+      <c r="B32" t="n">
+        <v>3943</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>-0.01618857299056486</v>
@@ -5425,10 +5311,8 @@
           <t>X &lt; 0.02438</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>3982~3995</t>
-        </is>
+      <c r="B33" t="n">
+        <v>3982</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>-0.02785634273813287</v>
@@ -5479,10 +5363,8 @@
           <t>X &lt; 0.02634</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>4016~4029</t>
-        </is>
+      <c r="B34" t="n">
+        <v>4016</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>0.0009771675040965988</v>
@@ -5533,10 +5415,8 @@
           <t>X &lt; 0.0283</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>4045~4058</t>
-        </is>
+      <c r="B35" t="n">
+        <v>4045</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>0.04475783553176882</v>

--- a/workspaces/btc_daily_14days/dxy/dxy_ma_ratio_50.xlsx
+++ b/workspaces/btc_daily_14days/dxy/dxy_ma_ratio_50.xlsx
@@ -479,7 +479,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that DXY MA Ratio-50 is approximately at value x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that DXY MA Ratio-50 is approximately at value x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -568,105 +568,105 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ -0.02752</t>
+          <t>X ≈ -0.02751</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>33</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>2.045931111009708</v>
+        <v>2.058413018989661</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>6.482393935392267</v>
+        <v>6.495268448987879</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.04561680496821197</v>
+        <v>0.05858716253711549</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-5.869883181625035</v>
+        <v>-5.856941127319466</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.3616154384028434</v>
+        <v>-0.3485352187940975</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>2.959526533816906</v>
+        <v>2.972543959746595</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>2.875604126736221</v>
+        <v>2.888648029175023</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>5.4354214769726</v>
+        <v>5.448584178211149</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>2.349288953263176</v>
+        <v>2.362471465568809</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>1.50057749885049</v>
+        <v>1.513969229541622</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>1.296346217787644</v>
+        <v>1.309793389588009</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>1.331023236853696</v>
+        <v>1.344468795279944</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.9112466141014437</v>
+        <v>0.924799233861485</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-1.869097871971434</v>
+        <v>-1.879527507668215</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -0.02556</t>
+          <t>X ≈ -0.02555</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>26</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>9.016115370171441</v>
+        <v>9.028602388206572</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.2574982543274729</v>
+        <v>-0.2446292663751919</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>10.85494821251271</v>
+        <v>10.86792548848468</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>3.314754269711827</v>
+        <v>3.327701486276936</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>2.778162881728996</v>
+        <v>2.791244420234754</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.7626898651304614</v>
+        <v>-0.7496746645011569</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-4.686943747255967</v>
+        <v>-4.673903482387495</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-5.154818095735244</v>
+        <v>-5.141659627202785</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-5.217021104937423</v>
+        <v>-5.203841199071348</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-2.225309920048304</v>
+        <v>-2.211919318578992</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-6.273728796405848</v>
+        <v>-6.260283198479172</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>1.447504322045795</v>
+        <v>1.460949798232569</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-2.817425184670597</v>
+        <v>-2.803872849289995</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-6.414552417424602</v>
+        <v>-6.424982053120999</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>49</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>4.634428637488298</v>
+        <v>4.646911463409239</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>11.16767226397406</v>
+        <v>11.18054928647771</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.600457314520547</v>
+        <v>0.6134269118815752</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-1.304746366710184</v>
+        <v>-1.291802690415842</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>4.266011299805463</v>
+        <v>4.279093173359037</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>6.600717198168354</v>
+        <v>6.61373565569415</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>4.480589773424271</v>
+        <v>4.493633635439913</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>4.015027297202401</v>
+        <v>4.028188843195018</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>5.993355360731364</v>
+        <v>6.006538487713996</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>5.145578820029407</v>
+        <v>5.158971034321027</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>9.020828207175811</v>
+        <v>9.034276517170213</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>2.938097936419609</v>
+        <v>2.951543478905229</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-1.56184389836136</v>
+        <v>-1.548291556033654</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-7.43496058068898</v>
+        <v>-7.445390216388986</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>49</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-1.46799399024944</v>
+        <v>-1.455517287801811</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-7.144000004394819</v>
+        <v>-7.131138077457784</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-3.469702889528691</v>
+        <v>-3.456737176983317</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>2.766507124021075</v>
+        <v>2.779452570891863</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.1935632954592421</v>
+        <v>0.2066420854128026</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.490508809475692</v>
+        <v>0.5035235113962528</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.4060977097185159</v>
+        <v>0.4191391756787226</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>1.977201447132209</v>
+        <v>1.990361735648165</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-8.274202560255702</v>
+        <v>-8.261024488829307</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-7.086866951223222</v>
+        <v>-7.073478260614777</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-7.293288069126127</v>
+        <v>-7.279843175044405</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-3.181242464428593</v>
+        <v>-3.167797890766423</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-3.60212565514184</v>
+        <v>-3.588573543552009</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-1.312511601098997</v>
+        <v>-1.322941236796233</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>69</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-1.762605995334567</v>
+        <v>-1.750130998542154</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>3.85436715085185</v>
+        <v>3.86723644252659</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>2.016128905481509</v>
+        <v>2.029097387992934</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>3.592294447833261</v>
+        <v>3.605239475370837</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>7.393382443348486</v>
+        <v>7.406464681438607</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>16.36966866636178</v>
+        <v>16.38269119616663</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>19.1826654197455</v>
+        <v>19.19571511928831</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>18.72098499303463</v>
+        <v>18.73415154337489</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>18.66512112293723</v>
+        <v>18.67830769253654</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>20.71623675740226</v>
+        <v>20.72963249798232</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>17.62076307191022</v>
+        <v>17.63421265794481</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>17.65971013298864</v>
+        <v>17.67315731156909</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>17.24426327216418</v>
+        <v>17.25781668335176</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>20.39704178547395</v>
+        <v>20.38661214977514</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>94</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>4.936456622839231</v>
+        <v>4.948935738238966</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>2.270923262050658</v>
+        <v>2.283789558461251</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>9.30240975761042</v>
+        <v>9.315382379131549</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>8.374002726333664</v>
+        <v>8.386949807927827</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>5.716130349226191</v>
+        <v>5.729210459627069</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>4.952666440116658</v>
+        <v>4.965681915240829</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>8.054957330542024</v>
+        <v>8.068001116245149</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>6.528415826081471</v>
+        <v>6.541576828869324</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>7.531911355153078</v>
+        <v>7.545093673917052</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>8.810094766853211</v>
+        <v>8.823486924245643</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>5.419066838922411</v>
+        <v>5.432513615642748</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>9.70797527640589</v>
+        <v>9.721421195661755</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>11.41769316150417</v>
+        <v>11.43124609066379</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>9.542894391086037</v>
+        <v>9.532464755387885</v>
       </c>
     </row>
     <row r="12">
@@ -887,46 +887,46 @@
         <v>115</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>5.746620981493088</v>
+        <v>5.759098682233223</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>7.608923146281917</v>
+        <v>7.621791942713585</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>6.349593320445194</v>
+        <v>6.362561906034799</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>8.215886299203255</v>
+        <v>8.228831766304893</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>7.680812624942426</v>
+        <v>7.693892542101054</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>9.714823062792163</v>
+        <v>9.727840049481742</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>5.293448001704725</v>
+        <v>5.306489260029757</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>3.092221136200692</v>
+        <v>3.105379583067702</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>6.505896230633724</v>
+        <v>6.519077375806148</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>3.052720279398159</v>
+        <v>3.06611008034929</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>2.849239848200341</v>
+        <v>2.862685500422266</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>5.491679135938753</v>
+        <v>5.505124127585347</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>4.203968498704647</v>
+        <v>4.217520744587709</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>4.455012799966894</v>
+        <v>4.444583164268742</v>
       </c>
     </row>
     <row r="13">
@@ -939,618 +939,618 @@
         <v>120</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.8245062031676298</v>
+        <v>-0.8120380783741226</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1.721672206088051</v>
+        <v>1.734532956772966</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>3.819981575002167</v>
+        <v>3.832945683603569</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-1.86548386075448</v>
+        <v>-1.852548459115951</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.740834194462245</v>
+        <v>-0.7277621746350817</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.3868710445548942</v>
+        <v>0.3998806111738844</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>1.134368399661881</v>
+        <v>1.147405809753032</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>3.996051977126072</v>
+        <v>4.009209470058472</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>8.929306674463895</v>
+        <v>8.94248781713344</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>7.25053382895279</v>
+        <v>7.263924054289561</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>2.885252732644133</v>
+        <v>2.898697664559208</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>6.251881949508729</v>
+        <v>6.265326641109894</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>4.167657936379833</v>
+        <v>4.18120994903451</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>4.418780915908535</v>
+        <v>4.408351280210965</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.01185</t>
+          <t>X ≈ -0.01184</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>5.411475887552506</v>
+        <v>5.677936212060828</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1.376820194886292</v>
+        <v>1.658475827035289</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>5.844655474898133</v>
+        <v>6.097027007787155</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>5.369215564720726</v>
+        <v>5.625319788219123</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>3.009227696261597</v>
+        <v>3.276597353464808</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>5.131341407860504</v>
+        <v>5.387664559083227</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.1807813125280759</v>
+        <v>0.4667072029692676</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.2855329188821045</v>
+        <v>0.0005940689736192439</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>2.088815095411022</v>
+        <v>2.360286685383635</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>6.112909261935485</v>
+        <v>6.355140717176447</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>7.738341742171087</v>
+        <v>7.969622223601263</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>5.337447676172729</v>
+        <v>5.583566536617568</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>6.748063237325397</v>
+        <v>6.98327732769728</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>10.65861831428272</v>
+        <v>10.84774521960438</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.009889</t>
+          <t>X ≈ -0.009888</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>190</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>2.23219431413581</v>
+        <v>2.244592965156187</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>2.725286412867533</v>
+        <v>2.7380820239987</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.2329215563744569</v>
+        <v>0.2458239412401042</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.1606698497873538</v>
+        <v>-0.1477859903487015</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>4.02577112208855</v>
+        <v>4.038796118811206</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.6482410039777946</v>
+        <v>0.6612075796584307</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-1.010615095715004</v>
+        <v>-0.9976156632414259</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-2.527832046010289</v>
+        <v>-2.514708347990677</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-4.166188015059888</v>
+        <v>-4.153037065048885</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-1.862480377779249</v>
+        <v>-1.849113504941812</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.015379635266257</v>
+        <v>-1.001951050428964</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-5.714993770926036</v>
+        <v>-5.701560633306499</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-3.505665797608508</v>
+        <v>-3.492119332738831</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-4.309289259529983</v>
+        <v>-4.319718895228135</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.00793</t>
+          <t>X ≈ -0.007928</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1.182747801622369</v>
+        <v>0.9511525099020233</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.6270470985800856</v>
+        <v>0.4013133151037351</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1.281118196927146</v>
+        <v>1.060961775422726</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>2.46180494342979</v>
+        <v>2.247103781152191</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-1.223099137488404</v>
+        <v>-1.454396365403142</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-2.501655995042803</v>
+        <v>-2.74142570770497</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>4.240132893517412</v>
+        <v>4.0364328034754</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>7.977489505657907</v>
+        <v>7.796076198169153</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>6.868322396605627</v>
+        <v>6.681310105417609</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>6.021634470547653</v>
+        <v>5.83477033293368</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>7.922869255726752</v>
+        <v>7.747127566611425</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>10.06411719022067</v>
+        <v>9.899447995977674</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>9.647856060732501</v>
+        <v>9.483239654755323</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>11.4801844246809</v>
+        <v>11.29988567174509</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.005972</t>
+          <t>X ≈ -0.00597</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>237</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-2.695088981568333</v>
+        <v>-2.682653566031007</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.5189745297679949</v>
+        <v>-0.5061442323304917</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.3464247184148448</v>
+        <v>0.3593611279414759</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.318440548199206</v>
+        <v>1.331356183424148</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.62343429509243</v>
+        <v>1.636487859732931</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-2.286298768429901</v>
+        <v>-2.273310551943645</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.108791054867261</v>
+        <v>-1.095771573177004</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-3.680609668884934</v>
+        <v>-3.667470788246675</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.8901218402489803</v>
+        <v>0.9032887493621828</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.305727844554021</v>
+        <v>1.319107558174338</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.426441535137691</v>
+        <v>-1.413004547815255</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-2.656988966987278</v>
+        <v>-2.643550455462339</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-4.342670691908737</v>
+        <v>-4.329121849114458</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-6.625522881559718</v>
+        <v>-6.63595251725777</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -0.004013</t>
+          <t>X ≈ -0.004011</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>219</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>4.557349674841859</v>
+        <v>4.569783709697063</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.6801225987459603</v>
+        <v>-0.667307063522756</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.076055971410966</v>
+        <v>-1.063134522569236</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1.328470605055678</v>
+        <v>1.341375272946308</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>2.612446548357575</v>
+        <v>2.625491732444019</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.2748714435331436</v>
+        <v>-0.2618908848622823</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-2.180850157581794</v>
+        <v>-2.167840424319287</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-4.014108975101969</v>
+        <v>-4.000978485372293</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-5.900141758569376</v>
+        <v>-5.886985797283245</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-7.206956390464555</v>
+        <v>-7.193586465750087</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-2.8524525024811</v>
+        <v>-2.839019890413944</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-5.099874710590512</v>
+        <v>-5.08643954524932</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-5.521150062836981</v>
+        <v>-5.507602796304326</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-4.816378901442867</v>
+        <v>-4.826808537141019</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ -0.002055</t>
+          <t>X ≈ -0.002053</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>229</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-8.780781457656374</v>
+        <v>-8.768396174593263</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-7.778848915091388</v>
+        <v>-7.766068541046948</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-12.08921974268061</v>
+        <v>-12.07633868141252</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-11.52957820506496</v>
+        <v>-11.51671240975384</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-12.94121539675031</v>
+        <v>-12.92820921977052</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-15.69401409054057</v>
+        <v>-15.68106967959218</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-11.86690880760958</v>
+        <v>-11.85392371889301</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-10.59535243499712</v>
+        <v>-10.58224022441232</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-10.66154884422077</v>
+        <v>-10.64840670785167</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-8.46329427793593</v>
+        <v>-8.449933014846486</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-12.1597012012631</v>
+        <v>-12.14627903631173</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-12.12989165752642</v>
+        <v>-12.1164628540869</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-11.68150070560281</v>
+        <v>-11.66795651873844</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-11.43638647856007</v>
+        <v>-11.44681611425813</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ -9.655e-05</t>
+          <t>X ≈ -9.48e-05</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>237</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.084483821557768</v>
+        <v>1.096863837328875</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>1.582380932197452</v>
+        <v>1.59515465239776</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>2.447827676496907</v>
+        <v>2.460712741009495</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>2.998277590921958</v>
+        <v>3.01114757831175</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>5.823900217399988</v>
+        <v>5.836918304070238</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>9.909085107511814</v>
+        <v>9.922050836627903</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>12.77142079130459</v>
+        <v>12.78442538589532</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>9.36686239208084</v>
+        <v>9.379985041997237</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>8.467508643011001</v>
+        <v>8.480658740543007</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>8.464746043342132</v>
+        <v>8.47811234711277</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>6.580116951411291</v>
+        <v>6.593543163041268</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>6.618124182319946</v>
+        <v>6.631555666982237</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>6.201756793035585</v>
+        <v>6.215302089650152</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>4.344941253461563</v>
+        <v>4.334511617763326</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 0.001862</t>
+          <t>X ≈ 0.001864</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>242</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-2.888558329090877</v>
+        <v>-2.876231112919378</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-2.436235676544577</v>
+        <v>-2.423512028863414</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-3.243246527587267</v>
+        <v>-3.23041149191468</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-2.294190576223009</v>
+        <v>-2.281363905968689</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-2.01086594298129</v>
+        <v>-1.997890589183683</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-3.358662274536293</v>
+        <v>-3.345744847095403</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-3.035911241184486</v>
+        <v>-3.022951260520713</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-5.972311197285222</v>
+        <v>-5.959228898883268</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-10.15791573533745</v>
+        <v>-10.14480458227857</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-11.0121652463326</v>
+        <v>-10.99883102149918</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-8.332961393813306</v>
+        <v>-8.319555968289734</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-9.54062011368886</v>
+        <v>-9.527203309297747</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-8.313040346308263</v>
+        <v>-8.299502024390286</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-5.174882995936947</v>
+        <v>-5.185312631635156</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.003821</t>
+          <t>X ≈ 0.003822</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>244</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-2.879527095567482</v>
+        <v>-2.867264602257571</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>2.435258915008205</v>
+        <v>2.447945499642749</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>3.262797873721219</v>
+        <v>3.275605511259059</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>5.021303706868139</v>
+        <v>5.034111344237182</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>3.263886967956878</v>
+        <v>3.276838792966764</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.527671590630533</v>
+        <v>1.540563523458722</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>2.664366891207081</v>
+        <v>2.677308909062695</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>3.837522844994204</v>
+        <v>3.850595455491622</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>1.736979222436133</v>
+        <v>1.750082881387257</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.7459479817313337</v>
+        <v>-0.7326229140571243</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-2.176841245302626</v>
+        <v>-2.16344674826734</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-2.961799355304798</v>
+        <v>-2.9483900736222</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.745081668119234</v>
+        <v>-1.731547013346784</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.496519630539453</v>
+        <v>-1.506949266237505</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.005779</t>
+          <t>X ≈ 0.005781</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>256</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-2.491254030379764</v>
+        <v>-2.478776459417055</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-2.554653961038007</v>
+        <v>-2.541758298380969</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-3.727098847689973</v>
+        <v>-3.714080873153883</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.657054832744635</v>
+        <v>-1.644023837259276</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.6421452342663372</v>
+        <v>-0.6289495457675329</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>2.375184130273311</v>
+        <v>2.388346701692335</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>1.90800861672701</v>
+        <v>1.921219516218379</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>2.035938214096426</v>
+        <v>1.840818124216391</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>2.187267865873942</v>
+        <v>1.990213320260764</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.9520696698582327</v>
+        <v>0.9653678016402409</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.360733141370325</v>
+        <v>0.3741068698364813</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.3962755597308956</v>
+        <v>0.4096711122630765</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>1.147581320627047</v>
+        <v>1.161109050504322</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.1645524174245594</v>
+        <v>-0.1749820531227542</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.007738</t>
+          <t>X ≈ 0.007739</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>200</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>2.195713570351018</v>
+        <v>2.208556427131761</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-2.901095481861255</v>
+        <v>-2.887847740434097</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.30968166610694</v>
+        <v>-1.296284462817731</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-5.149013199952655</v>
+        <v>-5.135625132660216</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-2.70084568534736</v>
+        <v>-2.687274410447401</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-7.395604780913374</v>
+        <v>-7.382071772619156</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-8.966568965825068</v>
+        <v>-8.95298152058318</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-4.959394823828355</v>
+        <v>-4.949293504420901</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-4.028359684765256</v>
+        <v>-4.017754651817455</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-5.115354136113766</v>
+        <v>-5.379232409890825</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-5.548268909164435</v>
+        <v>-5.818292720938317</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-3.736848856772816</v>
+        <v>-4.008474369383414</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.6635166368341743</v>
+        <v>-0.6500021120811965</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-3.414552417424602</v>
+        <v>-3.424982053122804</v>
       </c>
     </row>
     <row r="25">
@@ -1560,49 +1560,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.968052753617727</v>
+        <v>-1.937288084138707</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>4.268699089700021</v>
+        <v>4.259903050899517</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2.193681295568574</v>
+        <v>2.193564709115179</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.6464051032654297</v>
+        <v>0.6523494617081553</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.4442702585785909</v>
+        <v>-0.4390505710544659</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>2.655138223160705</v>
+        <v>2.651153698929484</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.06159229990331</v>
+        <v>-1.349286104789826</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.1578004891110396</v>
+        <v>0.1644138979749812</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>2.352518075357636</v>
+        <v>2.34854969824962</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>4.879714799141958</v>
+        <v>4.863198255458535</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>5.79135399468182</v>
+        <v>5.775355175891477</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>8.647468759173805</v>
+        <v>8.617167301462892</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>5.160746725960408</v>
+        <v>4.827266458514785</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>5.732340237942637</v>
+        <v>5.934568508675063</v>
       </c>
     </row>
     <row r="26">
@@ -1612,49 +1612,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>6.928467361538239</v>
+        <v>7.202956208529379</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1.295400253514487</v>
+        <v>0.9372633816511993</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>2.920167799579666</v>
+        <v>2.545308692558464</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1.705162174596353</v>
+        <v>2.008354681201354</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.4941571146276047</v>
+        <v>0.8024171187676714</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>3.497501323588239</v>
+        <v>3.786010437275664</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>4.088443281991715</v>
+        <v>4.378128437072128</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>3.621259883210172</v>
+        <v>3.911059793285425</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>2.884584321352193</v>
+        <v>3.178936697165298</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.007432109297248246</v>
+        <v>0.3155950820434867</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>2.505381487682364</v>
+        <v>2.795457682172518</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.1629380576749</v>
+        <v>0.1452720761386601</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.7681586827315456</v>
+        <v>1.067403102019846</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>1.017880015007833</v>
+        <v>1.293138752246414</v>
       </c>
     </row>
     <row r="27">
@@ -1664,49 +1664,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>5.926029716853641</v>
+        <v>5.701376832725103</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>2.707873556671032</v>
+        <v>3.025952249908208</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.6835405947941666</v>
+        <v>0.9951039932928225</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-2.452491967878856</v>
+        <v>-2.700769016925598</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-2.994447324050554</v>
+        <v>-3.2440643301466</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.58065004608126</v>
+        <v>0.3445195868543749</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>2.681708678535699</v>
+        <v>2.460582895365469</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.02873293002745214</v>
+        <v>-0.2042879462234879</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>2.153525393571954</v>
+        <v>1.93253209505599</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>2.396296383407417</v>
+        <v>2.18151439762724</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.0057507093630349</v>
+        <v>-0.2209889584351572</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>2.772374303866961</v>
+        <v>2.560641941172882</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.7127754306269409</v>
+        <v>0.4921394395078167</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>2.601841025198347</v>
+        <v>2.366226738086006</v>
       </c>
     </row>
     <row r="28">
@@ -1719,46 +1719,46 @@
         <v>141</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-2.146868935704354</v>
+        <v>-2.13293212774893</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-2.373060539119869</v>
+        <v>-2.355521489072807</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-1.683937737910362</v>
+        <v>-2.045668407205561</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-3.293926439257511</v>
+        <v>-3.659436035791593</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-1.010116131515446</v>
+        <v>-1.000189813189536</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-4.255996855441822</v>
+        <v>-4.237559852592526</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-10.72370929611831</v>
+        <v>-10.71064304181783</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-11.19089269489981</v>
+        <v>-11.17771168560457</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-9.833452864770074</v>
+        <v>-9.82025412581531</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-5.719039042705809</v>
+        <v>-5.705633915052978</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-6.633012225179392</v>
+        <v>-6.619554931469175</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-6.598629067834004</v>
+        <v>-6.585176779113894</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-7.018883678778842</v>
+        <v>-7.005327632427239</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-5.350722630190539</v>
+        <v>-5.361152265888691</v>
       </c>
     </row>
     <row r="29">
@@ -1771,46 +1771,46 @@
         <v>89</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-2.52436296715365</v>
+        <v>-2.505513430237784</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.2628318995955183</v>
+        <v>-0.8527453562545801</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.4813927684688863</v>
+        <v>0.4943998998864885</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>1.70941162495599</v>
+        <v>1.722390767354455</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.4395559971280463</v>
+        <v>-1.011430233500455</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-6.296000042946794</v>
+        <v>-6.883588845508136</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-4.133542748983118</v>
+        <v>-4.120476494682642</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-7.971512664618558</v>
+        <v>-7.95833165532332</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-10.27970356203684</v>
+        <v>-10.26650482308208</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-11.12982874706477</v>
+        <v>-11.11642361941194</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-6.840200048910411</v>
+        <v>-6.826742755200193</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-5.682221385946995</v>
+        <v>-5.668769097226885</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.4844984688020446</v>
+        <v>-0.4709424224504417</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-6.976350170233623</v>
+        <v>-6.986779805931775</v>
       </c>
     </row>
     <row r="30">
@@ -1823,46 +1823,46 @@
         <v>87</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-6.516426825957105</v>
+        <v>-7.09027801620821</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-4.679724576852394</v>
+        <v>-4.666814767276342</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-7.373443858161629</v>
+        <v>-7.360436726744027</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-2.645489576128867</v>
+        <v>-2.632510433730403</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-12.37931309005162</v>
+        <v>-12.36620228567668</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-7.484170002910602</v>
+        <v>-7.471127106616237</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-9.867754294895555</v>
+        <v>-9.854688040595079</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-4.587811256895442</v>
+        <v>-4.574630247600204</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-4.648811143077779</v>
+        <v>-4.635612404123016</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-11.24606276488728</v>
+        <v>-11.23265763723445</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-4.554264365066935</v>
+        <v>-4.540807071356717</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-10.26700764450312</v>
+        <v>-10.25355535578301</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-12.98611283016066</v>
+        <v>-12.97255678380905</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-12.73639149788437</v>
+        <v>-12.74682113358252</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>72</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-2.493438320209933</v>
+        <v>-2.48091603053431</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>5.617210289047989</v>
+        <v>5.63012009862404</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-1.722102861992987</v>
+        <v>-1.709095730575385</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-2.980738618274394</v>
+        <v>-2.96775947587593</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>2.036395722208994</v>
+        <v>2.049506526583933</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>10.66717099325793</v>
+        <v>10.68021388955229</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>10.58243727598568</v>
+        <v>10.59550353028615</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>12.89303165498198</v>
+        <v>12.90621266427721</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>10.0542539910219</v>
+        <v>10.06745272997667</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>10.59301769488282</v>
+        <v>10.60642282253565</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>6.221597703898581</v>
+        <v>6.235054997608799</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>7.644869750132898</v>
+        <v>7.658322038853008</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>7.224615139187996</v>
+        <v>7.238171185539599</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>8.863225360353184</v>
+        <v>8.852795724655032</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>39</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-1.211387038158698</v>
+        <v>-1.198864748483075</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>9.997552169389827</v>
+        <v>10.01046197896588</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>4.47447833458812</v>
+        <v>4.487485466005722</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>14.8611417236059</v>
+        <v>14.87412086600437</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>6.630412816226048</v>
+        <v>6.643523620600988</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>14.62016244624937</v>
+        <v>14.63320534254373</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>6.84312103666943</v>
+        <v>6.856187290969906</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>8.940040201990449</v>
+        <v>8.953221211285687</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>14.00724544401329</v>
+        <v>14.02044418296805</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>15.72122282308796</v>
+        <v>15.73462795074079</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>12.95236693466781</v>
+        <v>12.96582422837803</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>18.11495522021838</v>
+        <v>18.12840750893849</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>10.00239291696577</v>
+        <v>10.01594896331737</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>10.25211424924206</v>
+        <v>10.2416846135439</v>
       </c>
     </row>
     <row r="33">
@@ -1979,46 +1979,46 @@
         <v>34</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>3.388914620966517</v>
+        <v>3.40143691064214</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-4.105011933174211</v>
+        <v>-4.09210212359816</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>4.323648771993888</v>
+        <v>4.33665590341149</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>13.2774313163661</v>
+        <v>13.29041045876456</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>9.797833630705682</v>
+        <v>9.810944435080621</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-1.669430313931592</v>
+        <v>-1.656387417637227</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-1.754164031203871</v>
+        <v>-1.741097776903395</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-5.162523900573589</v>
+        <v>-5.149342891278351</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-11.10587672793234</v>
+        <v>-11.09267798897758</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-9.014825442372079</v>
+        <v>-9.001420314719248</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-3.33722582551318</v>
+        <v>-3.323768531802962</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-3.302842668167749</v>
+        <v>-3.289390379447639</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>2.159255662063821</v>
+        <v>2.172811708415423</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-3.473375946836363</v>
+        <v>-3.483805582534515</v>
       </c>
     </row>
     <row r="34">
@@ -2031,46 +2031,46 @@
         <v>29</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>6.127251334962409</v>
+        <v>6.139773624638032</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>7.96395358406717</v>
+        <v>7.976863393643221</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>14.46563660160849</v>
+        <v>14.4786437330261</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>7.699338010078058</v>
+        <v>7.712317152476523</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>3.712640932936914</v>
+        <v>3.725751737311853</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>14.35491045685949</v>
+        <v>14.36795335315385</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>10.82190087751824</v>
+        <v>10.83496713181871</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>6.906441616667749</v>
+        <v>6.919622625962987</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>10.29371759255444</v>
+        <v>10.3069163315092</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>16.34014413166443</v>
+        <v>16.35354925931726</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>16.13539080734685</v>
+        <v>16.14884810105707</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>19.61804982676125</v>
+        <v>19.63150211548136</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>19.19779521581635</v>
+        <v>19.21135126216795</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>26.34406827223057</v>
+        <v>26.33363863653242</v>
       </c>
     </row>
   </sheetData>
@@ -2121,7 +2121,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that DXY MA Ratio-50 is above threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that DXY MA Ratio-50 is above threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -2214,153 +2214,153 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4045</v>
+        <v>4046</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.1679712411502976</v>
+        <v>0.1675195447304887</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.2454933663081462</v>
+        <v>0.2450097541741201</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.06126334445008297</v>
+        <v>0.06082183303204403</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.1063281031942651</v>
+        <v>0.105876290067485</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.07468438087254725</v>
+        <v>0.07423594157224045</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.1389614365509786</v>
+        <v>0.1384992592831651</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.1170978002809449</v>
+        <v>0.116640136914981</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.009038676567833193</v>
+        <v>0.008603801712737891</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.01364724354603197</v>
+        <v>-0.01407720776165888</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.03512094017109746</v>
+        <v>-0.03555248610631878</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.05310585341367613</v>
+        <v>-0.05353477764435155</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.1036682615630085</v>
+        <v>-0.1040846365971433</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.04044774871226053</v>
+        <v>-0.04088325808118043</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.07339048911805435</v>
+        <v>-0.07302950739858005</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -0.02654</t>
+          <t>X &gt; -0.02653</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4012</v>
+        <v>4013</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.1525244127092762</v>
+        <v>0.1519702089092689</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.1941928381975373</v>
+        <v>0.1936121621161035</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.06139204230723294</v>
+        <v>0.0608402093406184</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.1554843774711898</v>
+        <v>0.1549101736393226</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.07827308825940804</v>
+        <v>0.07771250481473402</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.1157613746841406</v>
+        <v>0.1151941321674741</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.09440819191279104</v>
+        <v>0.09384515549344741</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.03559508026500424</v>
+        <v>-0.03613064942716449</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.03308315942207685</v>
+        <v>-0.03362021952838035</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.04775255744121409</v>
+        <v>-0.04829462829829367</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.06420553395945205</v>
+        <v>-0.06474579920394774</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.1154690640175744</v>
+        <v>-0.1159964888901754</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.04827574322195005</v>
+        <v>-0.04882433015546184</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.05862021403476803</v>
+        <v>-0.05817417871458019</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.02458</t>
+          <t>X &gt; -0.02457</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3986</v>
+        <v>3987</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.09470871654921353</v>
+        <v>0.09408396946565034</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.1971391423635325</v>
+        <v>0.1964700194375837</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.00901248865748272</v>
+        <v>-0.009634889043567796</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.1348769973411805</v>
+        <v>0.1342197863484813</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.06066216637526622</v>
+        <v>0.0600170370944042</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.1214913627010006</v>
+        <v>0.1208341092714065</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.1255961373263474</v>
+        <v>0.1249365687327071</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.00220325929104348</v>
+        <v>-0.002836505102564502</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.0007307860328680249</v>
+        <v>9.579388222391572e-05</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.03354872115727403</v>
+        <v>-0.0341852122091808</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.02370186992943957</v>
+        <v>-0.02434349863180074</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.1256640735603938</v>
+        <v>-0.1262800613670336</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.03021305243476746</v>
+        <v>-0.03085812461307569</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.01716154938647207</v>
+        <v>-0.0166549901681563</v>
       </c>
     </row>
     <row r="9">
@@ -2370,49 +2370,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3937</v>
+        <v>3938</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.0382072494102772</v>
+        <v>0.03743375433023743</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.06059961405291148</v>
+        <v>0.05979661057903485</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.01659796499878752</v>
+        <v>-0.01738756254415108</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.1527945855653314</v>
+        <v>0.1519635906556047</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.008322286380824551</v>
+        <v>0.007519644845302764</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.0408507566715528</v>
+        <v>0.04004381577858851</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.07139377812674752</v>
+        <v>0.07057746353498118</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.05220181079425856</v>
+        <v>-0.05299400689703049</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.07385356859253989</v>
+        <v>-0.07464155807251416</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.09800827145397761</v>
+        <v>-0.09880295118326643</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.1362703164059909</v>
+        <v>-0.137058679122994</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.1637957317999152</v>
+        <v>-0.1645770023201436</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.01115033680093802</v>
+        <v>-0.01197690619265046</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.07516056200135068</v>
+        <v>0.07577975490162459</v>
       </c>
     </row>
     <row r="10">
@@ -2422,49 +2422,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3888</v>
+        <v>3889</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.05718972388128662</v>
+        <v>0.05624440001408004</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.1513983232360303</v>
+        <v>0.1503997989857737</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.02692110426611549</v>
+        <v>0.02594700446729092</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.1198542783677254</v>
+        <v>0.1188581753736386</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.005987716050370295</v>
+        <v>0.005010773776184863</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.03518376989495664</v>
+        <v>0.03420413846173176</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.06717554442098361</v>
+        <v>0.06618571144060326</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.07777813786174903</v>
+        <v>-0.0787395536660469</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.02949445110691329</v>
+        <v>0.02850391984137701</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.009928519574174288</v>
+        <v>-0.01092455309581197</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.0460712757981554</v>
+        <v>-0.04706216580332523</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.1257672107354182</v>
+        <v>-0.1267375002543361</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.03410629658350217</v>
+        <v>0.03308692390007195</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.09264922866593395</v>
+        <v>0.09340313587184568</v>
       </c>
     </row>
     <row r="11">
@@ -2474,49 +2474,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3819</v>
+        <v>3820</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.09006898667937691</v>
+        <v>0.08887264674193318</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.08449472305129291</v>
+        <v>0.08326322086946192</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.009019020971862801</v>
+        <v>-0.01023555481629046</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.05711576784320727</v>
+        <v>0.05588427231085547</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.1274844589126047</v>
+        <v>-0.1286804093726914</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.2599404662548679</v>
+        <v>-0.2610957586538873</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.2781946575683776</v>
+        <v>-0.2793476731514204</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.4174258613579198</v>
+        <v>-0.4185535551570965</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.3072057951241121</v>
+        <v>-0.3083642634874195</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.3843996911142114</v>
+        <v>-0.3855576516623955</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.3652678115383665</v>
+        <v>-0.3664359780647501</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.4471073355631034</v>
+        <v>-0.4482539248658171</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.2768391947270672</v>
+        <v>-0.278040393744476</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.2742015402316227</v>
+        <v>-0.273149592389764</v>
       </c>
     </row>
     <row r="12">
@@ -2526,49 +2526,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3725</v>
+        <v>3726</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.0322291174277396</v>
+        <v>-0.03373764059051609</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.0293204189798999</v>
+        <v>0.02774806366773674</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.2439919888072239</v>
+        <v>-0.2455034253989794</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.1527600372838052</v>
+        <v>-0.1542929043794175</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.2749474903126128</v>
+        <v>-0.2764640222782191</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.3914800767780733</v>
+        <v>-0.3929575679255208</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.4884809090804225</v>
+        <v>-0.4899356458307693</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.5927034770946449</v>
+        <v>-0.594144606176549</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.5050251272384898</v>
+        <v>-0.5064922951879112</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.6164218331407696</v>
+        <v>-0.6178845948012537</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.5112349141271721</v>
+        <v>-0.5127326130106695</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.7033698229523964</v>
+        <v>-0.7048157770745078</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.5719495414346483</v>
+        <v>-0.5734437564751218</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.5219349677601741</v>
+        <v>-0.5205268733052506</v>
       </c>
     </row>
     <row r="13">
@@ -2578,101 +2578,101 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3610</v>
+        <v>3611</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.2163199100526469</v>
+        <v>-0.2182228738014658</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.2121350695629687</v>
+        <v>-0.2141004675120683</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.4540369501823065</v>
+        <v>-0.455951365890499</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.4193512640694053</v>
+        <v>-0.4212713970763744</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.5283858319343082</v>
+        <v>-0.530297033882654</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.7134260216674306</v>
+        <v>-0.7152759633843431</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.6726697801996266</v>
+        <v>-0.6745351651256897</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.7100902722550231</v>
+        <v>-0.7119638478722337</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.7283647272815017</v>
+        <v>-0.7302365522259322</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.7333058616565538</v>
+        <v>-0.7352092659843947</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.6182860492151718</v>
+        <v>-0.6202300051582199</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.9007190280140236</v>
+        <v>-0.902584563847121</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.724090974846284</v>
+        <v>-0.7260222437701103</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.6804803952639418</v>
+        <v>-0.6786513967948622</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.01283</t>
+          <t>X &gt; -0.01282</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3490</v>
+        <v>3491</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.1954080604326478</v>
+        <v>-0.1978110077032937</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.2786270102730271</v>
+        <v>-0.2810829971351509</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.6009946072087047</v>
+        <v>-0.6033783627221538</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.3696275071633224</v>
+        <v>-0.3720725292892766</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.521081017176904</v>
+        <v>-0.5235093464319789</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.7512585855489959</v>
+        <v>-0.7536084723923651</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.7348028981318251</v>
+        <v>-0.7371627552103277</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.8719060516033679</v>
+        <v>-0.8742499544754025</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.060433658000548</v>
+        <v>-1.062727793796576</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.007821839557167</v>
+        <v>-1.010172313372784</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.7387515660699293</v>
+        <v>-0.741189993805051</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.146653732112227</v>
+        <v>-1.148975095097427</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.8922886451463228</v>
+        <v>-0.8947039576448148</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.8558131624102785</v>
+        <v>-0.8535125601408069</v>
       </c>
     </row>
     <row r="15">
@@ -2685,566 +2685,566 @@
         <v>3326</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.4718749778919218</v>
+        <v>-0.4893017747691601</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.3602545934498522</v>
+        <v>-0.3773028425915967</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.9188198066872175</v>
+        <v>-0.935779711529733</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.6526011282664399</v>
+        <v>-0.6695980050526273</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.6951551690121107</v>
+        <v>-0.712029372133415</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-1.041320641748385</v>
+        <v>-1.058271746653787</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.7799489626382012</v>
+        <v>-0.7968857086377525</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.9008192187008675</v>
+        <v>-0.9176502142075407</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-1.215718322931238</v>
+        <v>-1.232540598686761</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-1.358934257069123</v>
+        <v>-1.375559159446325</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.156744140499136</v>
+        <v>-1.173325897554918</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-1.466374907986761</v>
+        <v>-1.482970696189724</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.269022772844863</v>
+        <v>-1.285523834999424</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-1.423572261080643</v>
+        <v>-1.434001896778796</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.008909</t>
+          <t>X &gt; -0.008907</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>3136</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.6357057066818683</v>
+        <v>-0.6549395300580088</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.5471974477866866</v>
+        <v>-0.5660538389730192</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.9886000550869909</v>
+        <v>-1.007369218553414</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.6824056381232779</v>
+        <v>-0.7012128911475628</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.9811806777203813</v>
+        <v>-0.9998663757301856</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-1.143685664926949</v>
+        <v>-1.162449384408674</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.76597365483061</v>
+        <v>-0.7847241361330646</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.8022438241891408</v>
+        <v>-0.8208896767653258</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.036958998471924</v>
+        <v>-1.055597254104867</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.328426041847528</v>
+        <v>-1.346868047952668</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.16530895427281</v>
+        <v>-1.18370893995094</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.208964964122465</v>
+        <v>-1.227380106887374</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.133511875298602</v>
+        <v>-1.151833419001179</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.248736090893985</v>
+        <v>-1.259165726592137</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.006951</t>
+          <t>X &gt; -0.006949</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2946</v>
+        <v>2947</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.7529854645154757</v>
+        <v>-0.7579430575613841</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.6229294450065481</v>
+        <v>-0.6280940127499193</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-1.134983784850291</v>
+        <v>-1.140017524580394</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.8851890768520931</v>
+        <v>-0.8902973333140594</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.9655783330645988</v>
+        <v>-0.9707159963449925</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-1.056104414851589</v>
+        <v>-1.061184869612944</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.088838639279409</v>
+        <v>-1.093919474302737</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-1.368485960194207</v>
+        <v>-1.373521692497469</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.546804030741001</v>
+        <v>-1.55178846243529</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-1.802462531105874</v>
+        <v>-1.807448181643714</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.751444005155335</v>
+        <v>-1.756470426120018</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.936013711347577</v>
+        <v>-1.940977158615055</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.828847892897357</v>
+        <v>-1.833892737270595</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-2.069678011450407</v>
+        <v>-2.064615578742028</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.004993</t>
+          <t>X &gt; -0.004991</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2709</v>
+        <v>2710</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.5830782908198202</v>
+        <v>-0.5896196662302771</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.6320240610683854</v>
+        <v>-0.6387589935467446</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.264586522123764</v>
+        <v>-1.271143997144108</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-1.07797616475802</v>
+        <v>-1.084589541235445</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-1.192081098983103</v>
+        <v>-1.19872607527136</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.9484794381819555</v>
+        <v>-0.9551797822652048</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-1.087093079111696</v>
+        <v>-1.093757501080148</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-1.166207141825915</v>
+        <v>-1.172906956079551</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-1.760001310705803</v>
+        <v>-1.766494476898757</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-2.074386163084981</v>
+        <v>-2.080877595052158</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.779877222355104</v>
+        <v>-1.786507847949629</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.872938356756727</v>
+        <v>-1.879534401658297</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.608923196195356</v>
+        <v>-1.615675283577978</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.67110465072102</v>
+        <v>-1.66483445164674</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; -0.003034</t>
+          <t>X &gt; -0.003032</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2490</v>
+        <v>2491</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.035188220329829</v>
+        <v>-1.043216350023165</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.6277937077545701</v>
+        <v>-0.6362491471698917</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.281168124776819</v>
+        <v>-1.289431461990311</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.289627507163317</v>
+        <v>-1.29787187536062</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.526696181219087</v>
+        <v>-1.534937917860553</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.007724478675151</v>
+        <v>-1.016131315196255</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.9908951673908248</v>
+        <v>-0.999327890405965</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.9157290287787418</v>
+        <v>-0.9242728071774522</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.395868476134666</v>
+        <v>-1.404235304211404</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-1.622967335857616</v>
+        <v>-1.631386128700143</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.685542288078963</v>
+        <v>-1.693974673602106</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-1.589123472624365</v>
+        <v>-1.597594527532877</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.264835772984711</v>
+        <v>-1.273510640748967</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.394472096139467</v>
+        <v>-1.386844758863418</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; -0.001076</t>
+          <t>X &gt; -0.001074</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2261</v>
+        <v>2262</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.2506942568854313</v>
+        <v>-0.2611358107541335</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.0964838873273095</v>
+        <v>0.08555838651615488</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.1865003580806857</v>
+        <v>-0.1973882465846302</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.2524984891095983</v>
+        <v>-0.26333850560993</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.3706037883147815</v>
+        <v>-0.3815077109032572</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.4797413864806046</v>
+        <v>0.4685154069287165</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.1106559708710364</v>
+        <v>0.0995679737512063</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.06464857406248115</v>
+        <v>0.05347897821016545</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.4574161080268766</v>
+        <v>-0.4683753345236852</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.9301611130641945</v>
+        <v>-0.9410911521627909</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.6246920487515979</v>
+        <v>-0.6358059295435226</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.521526871853645</v>
+        <v>-0.5326869913786396</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.2098086745461671</v>
+        <v>-0.2211993648605599</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.3774007146382203</v>
+        <v>-0.3683949620529035</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 0.0008829</t>
+          <t>X &gt; 0.0008844</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.407036749272315</v>
+        <v>-0.4200720658631099</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.07750702158288192</v>
+        <v>-0.09112028756479873</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.4949666348568158</v>
+        <v>-0.5084845103178566</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.6331476644887886</v>
+        <v>-0.6465746546911433</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.095948377916756</v>
+        <v>-1.109293866729779</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.6243863120788831</v>
+        <v>-0.6378983692879387</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.371854534288417</v>
+        <v>-1.385030153003441</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.024592866090856</v>
+        <v>-1.038067657403438</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.502478937076269</v>
+        <v>-1.515743767012971</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-2.030256466852876</v>
+        <v>-2.043486820966891</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.468338161912968</v>
+        <v>-1.481907527046033</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-1.357543324343347</v>
+        <v>-1.371168724727546</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.9605700459971871</v>
+        <v>-0.9745084239810708</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.9303626941044456</v>
+        <v>-0.9188092136165835</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.002841</t>
+          <t>X &gt; 0.002843</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1782</v>
+        <v>1783</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.07003999151916673</v>
+        <v>-0.08670667641408158</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.2428141537822839</v>
+        <v>0.2254466229199252</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.1217434395477355</v>
+        <v>-0.1390474213967039</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.407573935734753</v>
+        <v>-0.4246907518256506</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.9717003135252682</v>
+        <v>-0.9886879178605525</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.2530648850784871</v>
+        <v>-0.2703723751043015</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.145871524709939</v>
+        <v>-1.162721174865929</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.3526805001261906</v>
+        <v>-0.3701366307976528</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.3270492484235135</v>
+        <v>-0.3445532357206176</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.81049107704699</v>
+        <v>-0.8280110517415267</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.5361053773339108</v>
+        <v>-0.5538587761873899</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.2462612912223534</v>
+        <v>-0.2641802954140289</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.03791357503271087</v>
+        <v>0.01968588409466321</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.3539463568185468</v>
+        <v>-0.3397324737621261</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.0048</t>
+          <t>X &gt; 0.004801</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.375678378693955</v>
+        <v>0.3541355158574007</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.1050119331742323</v>
+        <v>-0.1269183711803805</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.6586927766333162</v>
+        <v>-0.6804218954499888</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.268852313364867</v>
+        <v>-1.29015385217609</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-1.643666046088107</v>
+        <v>-1.664963757653837</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.5355744429933154</v>
+        <v>-0.5574863187361316</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.750356683021877</v>
+        <v>-1.771536860686972</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-1.017446180366356</v>
+        <v>-1.039310528818824</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.6545023998472885</v>
+        <v>-0.6766462913244595</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.8207306838460937</v>
+        <v>-0.8431343172353536</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.2758065790345796</v>
+        <v>-0.2986674407829</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.1845522898154428</v>
+        <v>0.1613864270569181</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.3207814809683782</v>
+        <v>0.297334244702661</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.1726798556560638</v>
+        <v>-0.1546766600103453</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.006758</t>
+          <t>X &gt; 0.00676</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.9481703418163221</v>
+        <v>0.9193930884764612</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.384152153513071</v>
+        <v>0.354920304862766</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.04596894341140967</v>
+        <v>-0.07510880247087215</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.191332933519909</v>
+        <v>-1.219545343850832</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-1.843657721459699</v>
+        <v>-1.871682103907069</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-1.116817964644056</v>
+        <v>-1.145275292414759</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-2.480888287339901</v>
+        <v>-2.508361204013376</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.627170365220074</v>
+        <v>-1.613989355924836</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.221969785201914</v>
+        <v>-1.208771046247151</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.174737618751173</v>
+        <v>-1.203988987876151</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.4029159147784611</v>
+        <v>-0.4329076773523184</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.1422736961349713</v>
+        <v>0.1118456013259888</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.1556794849054981</v>
+        <v>0.1249832312301535</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.1743028074402062</v>
+        <v>-0.1506250772848716</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.008717</t>
+          <t>X &gt; 0.008718</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.7175708541019574</v>
+        <v>0.6813204497589567</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.9914067996081357</v>
+        <v>0.9537694360348468</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.1876193602291778</v>
+        <v>0.1504084016559659</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.4597839009075742</v>
+        <v>-0.4963542471178002</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-1.68521262647122</v>
+        <v>-1.72106487278235</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.04377109566450343</v>
+        <v>0.006487677152065885</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.282056368950776</v>
+        <v>-1.318218947952467</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.011232387658474</v>
+        <v>-0.9980513783632361</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.7032285838038845</v>
+        <v>-0.6900298448491213</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.4463426987211108</v>
+        <v>-0.4329375710682797</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.548165969581234</v>
+        <v>0.5616232632914517</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.8593018944543402</v>
+        <v>0.8727541831744503</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.3071020582400124</v>
+        <v>0.268101484842596</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0.4246342738877829</v>
+        <v>0.4540576514017189</v>
       </c>
     </row>
     <row r="26">
@@ -3257,46 +3257,46 @@
         <v>905</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.242825416053762</v>
+        <v>1.196361686260381</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.3504336113802253</v>
+        <v>0.303502272006213</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.2047264547488012</v>
+        <v>-0.2514499659989866</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.6761324685745649</v>
+        <v>-0.7222871312846806</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-1.927916271904365</v>
+        <v>-1.973217961961979</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.4669603756800598</v>
+        <v>-0.5136786785124414</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.325174755935755</v>
+        <v>-1.312108501635279</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.239871966871952</v>
+        <v>-1.226690957576714</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1.300871853054254</v>
+        <v>-1.287673114099491</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-1.488013612667814</v>
+        <v>-1.474608485014983</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.477297323725729</v>
+        <v>-0.4638400300155112</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.6639086415184181</v>
+        <v>-0.650456352798308</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.6421743021870796</v>
+        <v>-0.6286182558354767</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.6134474450489122</v>
+        <v>-0.6238770807470644</v>
       </c>
     </row>
     <row r="27">
@@ -3306,49 +3306,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.1312335958005235</v>
+        <v>0.01252228967562274</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.1656845188625624</v>
+        <v>0.1785943284386136</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.8156701134550346</v>
+        <v>-0.8026629820374325</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-1.141696018362275</v>
+        <v>-1.260469181629155</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-2.40145241616689</v>
+        <v>-2.520267733163983</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-1.242046678839515</v>
+        <v>-1.36110417884634</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-2.38358356652131</v>
+        <v>-2.433596998814387</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-2.190264983796858</v>
+        <v>-2.239289981225468</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-2.119164473677969</v>
+        <v>-2.167997005473104</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-1.780386091995197</v>
+        <v>-1.827439611326774</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.060436642204458</v>
+        <v>-1.106214843661036</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.7618526922566531</v>
+        <v>-0.8072864267554607</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.9179065105991739</v>
+        <v>-0.9628870155186036</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.9323859709252673</v>
+        <v>-1.001701629842337</v>
       </c>
     </row>
     <row r="28">
@@ -3361,46 +3361,46 @@
         <v>574</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-1.716236247671112</v>
+        <v>-1.791260858120559</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.6448043207174905</v>
+        <v>-0.7242264759297896</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-1.29364147165991</v>
+        <v>-1.372686657142147</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.7237941738299867</v>
+        <v>-0.8037887460473527</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-2.212396548322445</v>
+        <v>-2.290771251193888</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-1.823150338526801</v>
+        <v>-1.901911714312419</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-3.998476390293845</v>
+        <v>-3.985410135993369</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-2.897715538204267</v>
+        <v>-2.884534528909029</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-3.481363508010269</v>
+        <v>-3.468164769055505</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-3.111976497916245</v>
+        <v>-3.098571370263414</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-1.40035351561361</v>
+        <v>-1.386896221903392</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-1.888618441891879</v>
+        <v>-1.875166153171769</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-1.437792913463952</v>
+        <v>-1.424236867112349</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-2.059151720560493</v>
+        <v>-2.069581356258645</v>
       </c>
     </row>
     <row r="29">
@@ -3413,46 +3413,46 @@
         <v>433</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-1.576007127549431</v>
+        <v>-1.680000698726566</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.082023427427103</v>
+        <v>-0.1930195547908369</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-1.166547306437486</v>
+        <v>-1.153540175019884</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.1131311135263289</v>
+        <v>0.1261102559247931</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-2.603901256797705</v>
+        <v>-2.711029871883539</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-1.030930110154934</v>
+        <v>-1.141342690068782</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-1.808504474078482</v>
+        <v>-1.795438219778006</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.1971659329061737</v>
+        <v>-0.1839849236109359</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-1.412900230173932</v>
+        <v>-1.399701491219169</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-2.263025415201859</v>
+        <v>-2.249620287549028</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>0.3035838470856476</v>
+        <v>0.3170411407958653</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.3548736422201912</v>
+        <v>-0.3414213535000812</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.3796061579203496</v>
+        <v>0.3931622042719525</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.9873006853229924</v>
+        <v>-0.9977303210211446</v>
       </c>
     </row>
     <row r="30">
@@ -3465,46 +3465,46 @@
         <v>344</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-1.330647622535551</v>
+        <v>-1.466423276911165</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.03524449131376883</v>
+        <v>-0.02233468173771769</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-1.592903895584769</v>
+        <v>-1.579896764167167</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.2998600653028589</v>
+        <v>-0.2868809229043947</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-3.163862675723863</v>
+        <v>-3.150751871348923</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.331253680596447</v>
+        <v>0.3442965768908124</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-1.206968408768859</v>
+        <v>-1.193902154468383</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>1.814220285472899</v>
+        <v>1.827401294768137</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.8811273760347831</v>
+        <v>0.8943261149895463</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.03100219100685564</v>
+        <v>0.04440731865968672</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>2.151830262038118</v>
+        <v>2.165287555748336</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>1.023422721709132</v>
+        <v>1.036875010429242</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.6031681107642299</v>
+        <v>0.6167241571158328</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.5621917686219078</v>
+        <v>0.5517621329237556</v>
       </c>
     </row>
     <row r="31">
@@ -3517,46 +3517,46 @@
         <v>257</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.4248496175332193</v>
+        <v>0.437371907208842</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>1.537011413129271</v>
+        <v>1.549921222705322</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.3639325898011663</v>
+        <v>0.3769397212187684</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.4941857224086661</v>
+        <v>0.5071648648071303</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.04423549266350335</v>
+        <v>-0.03112468828856407</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>2.976941853612459</v>
+        <v>2.989984749906824</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>1.724892961242908</v>
+        <v>1.737959215543384</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>3.981444971021723</v>
+        <v>3.994625980316961</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>2.75312990974215</v>
+        <v>2.766328648696913</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>3.848530016543009</v>
+        <v>3.86193514419584</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>4.421986808956945</v>
+        <v>4.435444102667162</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>4.84547502466814</v>
+        <v>4.85892731338825</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>5.203430530454753</v>
+        <v>5.216986576806356</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>5.064046804365283</v>
+        <v>5.053617168667131</v>
       </c>
     </row>
     <row r="32">
@@ -3569,46 +3569,46 @@
         <v>185</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>1.560615733844081</v>
+        <v>1.573138023519704</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.05095787912017613</v>
+        <v>-0.03804806954412498</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>1.175795035904848</v>
+        <v>1.18880216732245</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>1.846588709052895</v>
+        <v>1.859567851451359</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.8539946681814357</v>
+        <v>-0.8408838638064964</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.01601218992524167</v>
+        <v>-0.00296929363087628</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-1.722367528819134</v>
+        <v>-1.709301274518658</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.5131517751020596</v>
+        <v>0.5263327843972974</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.08838865162077525</v>
+        <v>-0.07518991266601205</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>1.223648325513459</v>
+        <v>1.23705345316629</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>3.721597703898581</v>
+        <v>3.735054997608799</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>3.755980861244012</v>
+        <v>3.769433149964122</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>4.416807331380191</v>
+        <v>4.430363377731794</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>3.585447582575398</v>
+        <v>3.575017946877246</v>
       </c>
     </row>
     <row r="33">
@@ -3621,46 +3621,46 @@
         <v>146</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>2.301082227735229</v>
+        <v>2.313604517410852</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-2.735148919475598</v>
+        <v>-2.722239109899547</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.294639908174382</v>
+        <v>0.3076470395919841</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-1.629901479766062</v>
+        <v>-1.616922337367598</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-2.853254201687548</v>
+        <v>-2.840143397312609</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-3.925675277670514</v>
+        <v>-3.912632381376149</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-4.010408994942793</v>
+        <v>-3.997342740642317</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-1.737866366327033</v>
+        <v>-1.724685357031795</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-3.853660773057278</v>
+        <v>-3.840462034102515</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-2.648991437537262</v>
+        <v>-2.635586309884431</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>1.255844279241046</v>
+        <v>1.269301572951264</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.07963557711214975</v>
+        <v>-0.06618328839203969</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>2.924767346189526</v>
+        <v>2.938323392541129</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>1.80462566476718</v>
+        <v>1.794196029069028</v>
       </c>
     </row>
     <row r="34">
@@ -3673,46 +3673,46 @@
         <v>112</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>1.970847394075733</v>
+        <v>1.983369683751356</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-2.31929764745994</v>
+        <v>-2.306387837883889</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.9284520683422528</v>
+        <v>-0.9154449369246507</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-6.155341792877607</v>
+        <v>-6.142362650479143</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-6.693763007949777</v>
+        <v>-6.680652203574837</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-4.610606784519831</v>
+        <v>-4.597563888225466</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-4.69534050179211</v>
+        <v>-4.682274247491634</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.6982381862879024</v>
+        <v>-0.6850571769926646</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-1.652095215327343</v>
+        <v>-1.63889647637258</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.7165061146409784</v>
+        <v>-0.7031009869881473</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>2.650169132470012</v>
+        <v>2.66362642618023</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.898838004101151</v>
+        <v>0.9122902928212611</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>3.15715482172768</v>
+        <v>3.170710868079283</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>3.406876154003967</v>
+        <v>3.396446518305815</v>
       </c>
     </row>
     <row r="35">
@@ -3725,46 +3725,46 @@
         <v>83</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.5186098725611146</v>
+        <v>0.5311321622367373</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-5.912240848836881</v>
+        <v>-5.899331039260829</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-6.30710955543347</v>
+        <v>-6.294102424015868</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-10.99613353125971</v>
+        <v>-10.98315438886124</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-10.32973546922344</v>
+        <v>-10.3166246648485</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-11.23711280861622</v>
+        <v>-11.22406991232185</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-10.11702724878006</v>
+        <v>-10.10396099447959</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-3.355294984910962</v>
+        <v>-3.342113975615725</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-5.825933425310133</v>
+        <v>-5.81273468635537</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-6.67605861033806</v>
+        <v>-6.662653482685229</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-2.061534826221902</v>
+        <v>-2.048077532511684</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-5.641609500201774</v>
+        <v>-5.628157211481664</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-2.447406279821372</v>
+        <v>-2.433850233469769</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-4.607323501761954</v>
+        <v>-4.617753137460106</v>
       </c>
     </row>
   </sheetData>
@@ -3815,7 +3815,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that DXY MA Ratio-50 is below threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that DXY MA Ratio-50 is below threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -3911,150 +3911,150 @@
         <v>83</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-5.505486512981058</v>
+        <v>-5.492964223305435</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-9.526698680162184</v>
+        <v>-9.513788870586133</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-2.692651724108174</v>
+        <v>-2.679644592690572</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-3.767217868609109</v>
+        <v>-3.754238726210644</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.6911812523559746</v>
+        <v>-0.6780704479810353</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-4.008197145965617</v>
+        <v>-3.995154249671252</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.4784730319125927</v>
+        <v>-0.4654067776121167</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>2.668801400631203</v>
+        <v>2.681982409926441</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>6.222259345774205</v>
+        <v>6.235458084728968</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>4.16731488363785</v>
+        <v>4.180720011290681</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>3.962561559320271</v>
+        <v>3.976018853030489</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>5.201763993774129</v>
+        <v>5.215216282494239</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>3.5766901057208</v>
+        <v>3.590246152072403</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>3.826411437997088</v>
+        <v>3.815981802298936</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -0.02654</t>
+          <t>X &lt; -0.02653</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>116</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-3.355507285727221</v>
+        <v>-3.342984996051598</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-4.967080898691478</v>
+        <v>-4.954171089115427</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-1.9136737432191</v>
+        <v>-1.900666611801498</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-4.369627507163322</v>
+        <v>-4.356648364764858</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.5977038946492854</v>
+        <v>-0.5845930902743461</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-2.024399887968109</v>
+        <v>-2.011356991673743</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.4770732913113349</v>
+        <v>0.4901395456118109</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>3.458165754598795</v>
+        <v>3.471346763894033</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>5.121303799450985</v>
+        <v>5.134502538405748</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>3.409109648905819</v>
+        <v>3.42251477655865</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>3.20435632458824</v>
+        <v>3.217813618298457</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>4.100808447450909</v>
+        <v>4.114260736171019</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>2.818484870988769</v>
+        <v>2.832040917340372</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>2.206137237747804</v>
+        <v>2.195707602049652</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.02458</t>
+          <t>X &lt; -0.02457</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>142</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-1.084987615984623</v>
+        <v>-1.072465326309</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-4.105011933174232</v>
+        <v>-4.092102123598181</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.4296968250179134</v>
+        <v>0.4427039564355155</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-2.96117680293797</v>
+        <v>-2.948197660539506</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.02152874255324377</v>
+        <v>0.03463954692818305</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-1.793705376069127</v>
+        <v>-1.780662479774762</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.4699883891160468</v>
+        <v>-0.4569221348155708</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>1.87972962055315</v>
+        <v>1.892910629848387</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>3.2271804385962</v>
+        <v>3.240379177550963</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>2.377055253568273</v>
+        <v>2.390460381221104</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>1.468076577138021</v>
+        <v>1.481533870848239</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>3.615135790821476</v>
+        <v>3.628588079541586</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>1.786430475651223</v>
+        <v>1.799986522002825</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.627701103702158</v>
+        <v>0.6172714680040059</v>
       </c>
     </row>
     <row r="9">
@@ -4067,46 +4067,46 @@
         <v>191</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.3861428316224789</v>
+        <v>0.3986651212981016</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.1783103624936118</v>
+        <v>-0.1654005529175606</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.4739413497579719</v>
+        <v>0.486948481175574</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-2.537166774179028</v>
+        <v>-2.524187631780563</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>1.112893686141469</v>
+        <v>1.126004490516408</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.363215205008963</v>
+        <v>0.3762581013033284</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.8020416971607744</v>
+        <v>0.8151079514612505</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>2.429099136075607</v>
+        <v>2.442280145370844</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>3.938779878165555</v>
+        <v>3.951978617120318</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>3.088654693137627</v>
+        <v>3.102059820790458</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>3.407461578244124</v>
+        <v>3.420918871954342</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>3.441844735589555</v>
+        <v>3.455297024309665</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.9273492869483277</v>
+        <v>0.9409053332999306</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-1.440730427895808</v>
+        <v>-1.45116006359396</v>
       </c>
     </row>
     <row r="10">
@@ -4119,46 +4119,46 @@
         <v>240</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.006561679790024755</v>
+        <v>0.0190839694656475</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-1.605011933174232</v>
+        <v>-1.592102123598181</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.3332139731041579</v>
+        <v>-0.3202068416865558</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-1.452960840496658</v>
+        <v>-1.439981698098194</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.9252846110978439</v>
+        <v>0.9383954154727832</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.389393215480176</v>
+        <v>0.4024361117745414</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.7213261648745615</v>
+        <v>0.7343924191750375</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>2.337476099426382</v>
+        <v>2.35065710872162</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>1.443142879910752</v>
+        <v>1.456341618865515</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>1.009684361549489</v>
+        <v>1.02308948920232</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>1.221597703898574</v>
+        <v>1.235054997608792</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>2.089314194577348</v>
+        <v>2.102766483297458</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.002392916965774816</v>
+        <v>0.01594896331737772</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-1.414552417424595</v>
+        <v>-1.424982053122747</v>
       </c>
     </row>
     <row r="11">
@@ -4171,46 +4171,46 @@
         <v>309</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.3898784496598111</v>
+        <v>-0.3773561599841884</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.3833290852778006</v>
+        <v>-0.3704192757017495</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.1926759945333885</v>
+        <v>0.2056831259509906</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.3243200637976216</v>
+        <v>-0.3113409213991574</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>2.373504675822758</v>
+        <v>2.386615480197698</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>3.965444995415446</v>
+        <v>3.978487891709811</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>4.851585064550939</v>
+        <v>4.864651318851415</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>6.002524643115706</v>
+        <v>6.015705652410944</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>5.294275565994901</v>
+        <v>5.307474304949665</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>5.415024167374739</v>
+        <v>5.42842929502757</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>4.886646247587898</v>
+        <v>4.900103541298115</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>5.568278595871845</v>
+        <v>5.581730884591956</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>3.853525603049924</v>
+        <v>3.867081649401527</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>3.455997744387695</v>
+        <v>3.445568108689542</v>
       </c>
     </row>
     <row r="12">
@@ -4223,46 +4223,46 @@
         <v>403</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.8564376103111186</v>
+        <v>0.8689598999867414</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.2374198286123672</v>
+        <v>0.2503296381884184</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2.323940700179556</v>
+        <v>2.336947831597158</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1.709776959337916</v>
+        <v>1.72275610173638</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>3.156467406796772</v>
+        <v>3.169578211171711</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>4.198326217961558</v>
+        <v>4.211369114255923</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>5.602426247587545</v>
+        <v>5.615492501888021</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>6.12779868007155</v>
+        <v>6.140979689366787</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>5.818659836072868</v>
+        <v>5.831858575027631</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>6.209229440126833</v>
+        <v>6.222634567779664</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>5.011920284543741</v>
+        <v>5.025377578253959</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>6.535137188787438</v>
+        <v>6.548589477507548</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>5.618604662209783</v>
+        <v>5.632160708561386</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>4.875770163220558</v>
+        <v>4.865340527522406</v>
       </c>
     </row>
     <row r="13">
@@ -4275,98 +4275,98 @@
         <v>518</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1.946716119944469</v>
+        <v>1.959238409620092</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1.87954405138175</v>
+        <v>1.892453860957801</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>3.222127082236895</v>
+        <v>3.235134213654497</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>3.159330021794204</v>
+        <v>3.172309164192669</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>4.165310351123587</v>
+        <v>4.178421155498526</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>5.428003254090207</v>
+        <v>5.441046150384572</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>5.536319729868126</v>
+        <v>5.549385984168602</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>5.455236717187006</v>
+        <v>5.468417726482244</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>5.973387410155283</v>
+        <v>5.986586149110046</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>5.509362611227743</v>
+        <v>5.522767738880574</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>4.532408514709395</v>
+        <v>4.545865808419613</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>6.304243409506554</v>
+        <v>6.317695698226665</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>5.304838219411074</v>
+        <v>5.318394265762677</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>4.782358779486593</v>
+        <v>4.771929143788441</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.01283</t>
+          <t>X &lt; -0.01282</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>638</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1.425056977595673</v>
+        <v>1.437579267271296</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1.851100919490342</v>
+        <v>1.864010729066393</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>3.337109955840461</v>
+        <v>3.350117087258063</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>2.213444593150157</v>
+        <v>2.226423735548622</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>3.24242149720024</v>
+        <v>3.25553230157518</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>4.480302306389262</v>
+        <v>4.493345202683628</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>4.70904821294144</v>
+        <v>4.722114467241916</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>5.182303685633286</v>
+        <v>5.195484694928524</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>6.53196210666102</v>
+        <v>6.545160845615783</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>5.83857673354531</v>
+        <v>5.851981861198141</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>4.22316510201771</v>
+        <v>4.236622395727927</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>6.295165814222067</v>
+        <v>6.308618102942177</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>5.091212143716042</v>
+        <v>5.104768190067645</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>4.713974228343417</v>
+        <v>4.703544592645265</v>
       </c>
     </row>
     <row r="15">
@@ -4376,569 +4376,569 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>2.24471629325636</v>
+        <v>2.313604517410852</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1.755337194007808</v>
+        <v>1.823215435554999</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>3.854234073446129</v>
+        <v>3.919104075706557</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>2.862292692337931</v>
+        <v>2.928532208086942</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>3.196689432377973</v>
+        <v>3.261973663708559</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>4.616325883809345</v>
+        <v>4.680144704551623</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>3.783462490726599</v>
+        <v>3.848236337813475</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>4.064408767755566</v>
+        <v>4.128365701498716</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>5.624356512495957</v>
+        <v>5.686312561165224</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>5.896425841183742</v>
+        <v>5.95719077604334</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>4.943542841055688</v>
+        <v>5.005291610311168</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>6.100120512116831</v>
+        <v>6.160466773874461</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>5.430489342568436</v>
+        <v>5.491249918070395</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>5.929587233448217</v>
+        <v>5.966051570787585</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.008909</t>
+          <t>X &lt; -0.008907</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>2.244464905596473</v>
+        <v>2.302568360200794</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1.943375163599953</v>
+        <v>2.000546416180264</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>3.161409682809825</v>
+        <v>3.217053984093909</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>2.283598299288293</v>
+        <v>2.340229782264345</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>3.358080310022572</v>
+        <v>3.413219181837334</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>3.857135150964041</v>
+        <v>3.912003080556005</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>2.865143369175627</v>
+        <v>2.920948310413706</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>2.801185776845742</v>
+        <v>2.856699404794142</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>3.748250406792472</v>
+        <v>3.802766593689284</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>4.410221995958096</v>
+        <v>4.463421815486313</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>3.802242865188909</v>
+        <v>3.855900919058946</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>3.83662602253434</v>
+        <v>3.89027907141427</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>3.71879076642815</v>
+        <v>3.77224302172624</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>3.968512098704437</v>
+        <v>3.997978671952772</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.006951</t>
+          <t>X &lt; -0.006949</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>1182</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>2.075089598571751</v>
+        <v>2.087611888247373</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1.732551518602421</v>
+        <v>1.745461328178472</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>2.860525451599742</v>
+        <v>2.873532583017344</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>2.313959633276603</v>
+        <v>2.326938775675067</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>2.621562106867728</v>
+        <v>2.634672911242667</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>2.834401675717061</v>
+        <v>2.847444572011426</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>3.088077433910087</v>
+        <v>3.101143688210563</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>3.636122461524529</v>
+        <v>3.649303470819767</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>4.251941526272851</v>
+        <v>4.265140265227615</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>4.670851874239844</v>
+        <v>4.684257001892675</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>4.466098549922265</v>
+        <v>4.479555843632482</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>4.838891182733015</v>
+        <v>4.852343471453125</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>4.672443678387097</v>
+        <v>4.6859997247387</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>5.175972117262376</v>
+        <v>5.165542481564223</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.004993</t>
+          <t>X &lt; -0.004991</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>1419</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.276822426794951</v>
+        <v>1.289344716470573</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1.356580737720769</v>
+        <v>1.36949054729682</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>2.441627464527976</v>
+        <v>2.454634595945578</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>2.149047616162967</v>
+        <v>2.162026758561431</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>2.456292363035828</v>
+        <v>2.469403167410768</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.978540502301875</v>
+        <v>1.991583398596241</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>2.387111929497536</v>
+        <v>2.400178183798012</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>2.413233675183967</v>
+        <v>2.426414684479205</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>3.691204895414636</v>
+        <v>3.704403634369399</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>4.109578653304247</v>
+        <v>4.122983780957078</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>3.48199234801416</v>
+        <v>3.495449641724377</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>3.586847668855007</v>
+        <v>3.600299957575118</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>3.166593057910106</v>
+        <v>3.180149104261709</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>3.204897899700129</v>
+        <v>3.194468264001976</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; -0.003034</t>
+          <t>X &lt; -0.003032</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>1638</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1.719015892244236</v>
+        <v>1.731538181919859</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.08424325608096</v>
+        <v>1.097153065657011</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.971425831535647</v>
+        <v>1.98443296295325</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>2.040628903093086</v>
+        <v>2.053608045491551</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>2.47900866482189</v>
+        <v>2.49211946919683</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.677549503636456</v>
+        <v>1.690592399930821</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1.77596596951436</v>
+        <v>1.789032223814836</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.552982814933102</v>
+        <v>1.56616382422834</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>2.407733844501713</v>
+        <v>2.420932583456477</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>2.595459697324834</v>
+        <v>2.608864824977665</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>2.634906617207498</v>
+        <v>2.648363910917716</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>2.425089530352686</v>
+        <v>2.438541819072796</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>2.004834919407784</v>
+        <v>2.018390965759387</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>2.13245612958395</v>
+        <v>2.122026493885798</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; -0.001076</t>
+          <t>X &lt; -0.001074</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>1867</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.4256832652211955</v>
+        <v>0.4382055548968182</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.00752934078001033</v>
+        <v>0.005380468796040816</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.2403443200577726</v>
+        <v>0.2533514514753747</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.3705974526652724</v>
+        <v>0.3835765950637366</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.5820423329332272</v>
+        <v>0.5951531373081664</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.4595623281727441</v>
+        <v>-0.4465194318783787</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.09844632198935699</v>
+        <v>0.111512576289833</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.05975783483077635</v>
+        <v>0.07293884412601415</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.8021859079414639</v>
+        <v>0.8153846468962271</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>1.237545457782311</v>
+        <v>1.250950585435142</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.8185446776532714</v>
+        <v>0.8320019713634892</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.6386803791872353</v>
+        <v>0.6521326679073454</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.3255494961480707</v>
+        <v>0.3391055424996736</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.4681471005186211</v>
+        <v>0.4577174648204689</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 0.0008829</t>
+          <t>X &lt; 0.0008844</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>2104</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.5008582577367875</v>
+        <v>0.5133805474124102</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.1725546067497206</v>
+        <v>0.1854644163257717</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.4906136568071275</v>
+        <v>0.5036207882247297</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.6683953065248929</v>
+        <v>0.6813744489233571</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.175601467878572</v>
+        <v>1.188712272253511</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.7125871318299772</v>
+        <v>0.7256300281243426</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1.53089523965275</v>
+        <v>1.543961493953226</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.111240357981529</v>
+        <v>1.124421367276767</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1.668111194232679</v>
+        <v>1.681309933187443</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>2.053727454071677</v>
+        <v>2.067132581724508</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>1.468745992871966</v>
+        <v>1.482203286582184</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1.313015081776335</v>
+        <v>1.326467370496445</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.9878175050519573</v>
+        <v>1.00137355140356</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.9048392175563862</v>
+        <v>0.894409581858234</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.002841</t>
+          <t>X &lt; 0.002843</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>2346</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.1493579287243776</v>
+        <v>0.1618802184000003</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.09819181382214737</v>
+        <v>-0.08528200424609622</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.1036999228890281</v>
+        <v>0.1167070543066302</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.3618302933481843</v>
+        <v>0.3748094357466485</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.8464269810893228</v>
+        <v>0.8595377854642621</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.2913539997938983</v>
+        <v>0.3043968960882637</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.059135201532705</v>
+        <v>1.072201455833181</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.3788230729984292</v>
+        <v>0.392004082293667</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.445700424667784</v>
+        <v>0.4588991636225472</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.7038446343542688</v>
+        <v>0.7172497620070999</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.4564655640861375</v>
+        <v>0.4699228577963552</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.1924684997776822</v>
+        <v>0.2059207884977923</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.02796836453611462</v>
+        <v>0.04152441088771752</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.2776896968124021</v>
+        <v>0.2672600611142499</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.0048</t>
+          <t>X &lt; 0.004801</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>2590</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.1382259649976234</v>
+        <v>-0.1257036753220007</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.1420923139300143</v>
+        <v>0.1550021235060655</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.403594263704079</v>
+        <v>0.4166013951216812</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.8041176665818455</v>
+        <v>0.8170968089803097</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.07650726232049</v>
+        <v>1.089618066695429</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.4086982347851915</v>
+        <v>0.4217411310795569</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>1.211995405543796</v>
+        <v>1.225061659844272</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.7062019681522571</v>
+        <v>0.7193829774474949</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.5679820047498794</v>
+        <v>0.5811807437046426</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.567277669142797</v>
+        <v>0.5806827967956281</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.2080841903850654</v>
+        <v>0.2215414840952832</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.1050229997598464</v>
+        <v>-0.09157071103973635</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.1391772246043601</v>
+        <v>-0.1256211782527572</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.1105441076719273</v>
+        <v>0.1001144719737752</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.006758</t>
+          <t>X &lt; 0.00676</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>2846</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.3515843876257065</v>
+        <v>-0.3390620979500838</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.1022029444101946</v>
+        <v>-0.08929313483414347</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.02961374225164803</v>
+        <v>0.04262087366925016</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.5812151894658868</v>
+        <v>0.594194331864351</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.9206029631577692</v>
+        <v>0.9337137675327085</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.586022428963318</v>
+        <v>0.5990653252576834</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1.273760621803397</v>
+        <v>1.286826876103873</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.8262361977755361</v>
+        <v>0.8197582323171346</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.7146350326397339</v>
+        <v>0.7081856652301184</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.6023875707319633</v>
+        <v>0.6157926983847943</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.2219490742429286</v>
+        <v>0.2354063679531464</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.05990107832029423</v>
+        <v>-0.04644878960018417</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.02337424161936497</v>
+        <v>-0.009818195267762064</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.08579895291974537</v>
+        <v>0.07536931722159323</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.008717</t>
+          <t>X &lt; 0.008718</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>3046</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.1827205227665161</v>
+        <v>-0.1701982330908933</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.2865917430726341</v>
+        <v>-0.273681933496583</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.05871380922346248</v>
+        <v>-0.04570667780586035</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.202643879267363</v>
+        <v>0.2156230216658273</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.6802829722908896</v>
+        <v>0.6933937766658289</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.05999301882333441</v>
+        <v>0.0730359151176998</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.5980059419968171</v>
+        <v>0.6110721962972931</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.4440334764755747</v>
+        <v>0.4389888032480087</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.4012712280030186</v>
+        <v>0.3962323292480363</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.2255636266413603</v>
+        <v>0.2205039420283939</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.157627763774542</v>
+        <v>-0.1625827976667935</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.3017998347507387</v>
+        <v>-0.3067073160680422</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.06545562757350609</v>
+        <v>-0.05189958122190319</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.1440337043582787</v>
+        <v>-0.1544633400564308</v>
       </c>
     </row>
     <row r="26">
@@ -4948,49 +4948,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3223</v>
+        <v>3224</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.2805011490555387</v>
+        <v>-0.2679788593799159</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.03506454846361606</v>
+        <v>-0.02215473888756492</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.06526946855477433</v>
+        <v>0.07827659997237646</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.2264727713882095</v>
+        <v>0.2394519137866737</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.6165566630941228</v>
+        <v>0.6296674674690621</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.2021446856132485</v>
+        <v>0.2151875819076139</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.5058978883007654</v>
+        <v>0.5018792653526916</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.4274420331520048</v>
+        <v>0.423412526678284</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0.5075790633060393</v>
+        <v>0.5035182473366646</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.4804260204690252</v>
+        <v>0.4763112983720887</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.1692108471099871</v>
+        <v>0.1651758528923466</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.190089388375803</v>
+        <v>0.1860481530639362</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.2215823297035726</v>
+        <v>0.2174993509142809</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.1786836979958153</v>
+        <v>0.1817176987382894</v>
       </c>
     </row>
     <row r="27">
@@ -5000,49 +5000,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3371</v>
+        <v>3373</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.03689609825703144</v>
+        <v>0.06346266769049436</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.02342843379824444</v>
+        <v>0.02032391190477512</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.1908562646387679</v>
+        <v>0.1876827046645317</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.291514842644311</v>
+        <v>0.3179078482528936</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.6113357110287794</v>
+        <v>0.6376064608376737</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.3464811113073409</v>
+        <v>0.3728503129579721</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.662859616621148</v>
+        <v>0.6727553383071836</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.5674139140547609</v>
+        <v>0.5772034241995811</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.6117842701161251</v>
+        <v>0.62152811975362</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.459684361549499</v>
+        <v>0.4692201771896904</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.2716866191327227</v>
+        <v>0.2812635284144847</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.1745993018013792</v>
+        <v>0.1842479647789403</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.2455720391484562</v>
+        <v>0.2550321484586533</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.2155276775027275</v>
+        <v>0.2308139741526603</v>
       </c>
     </row>
     <row r="28">
@@ -5052,49 +5052,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3554</v>
+        <v>3555</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.3420473619910354</v>
+        <v>0.3545696516666581</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.1622536479599646</v>
+        <v>0.1751634575360157</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.2165707920090796</v>
+        <v>0.2295779234266817</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.1503051149590817</v>
+        <v>0.1632842573575459</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.4260332541822578</v>
+        <v>0.4391440585571971</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.3585116882482779</v>
+        <v>0.3715545845426433</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.766608388968919</v>
+        <v>0.7641041915875348</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.539723290437621</v>
+        <v>0.5372619949895281</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.6910589612070055</v>
+        <v>0.6885513566932318</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.5592908820666338</v>
+        <v>0.5567834107158518</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.2580047885204593</v>
+        <v>0.2555721420719763</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.3082868229987881</v>
+        <v>0.3058402345860003</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.2696221715368097</v>
+        <v>0.2671675609926751</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.3384020001330725</v>
+        <v>0.3401374968069248</v>
       </c>
     </row>
     <row r="29">
@@ -5104,49 +5104,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3695</v>
+        <v>3696</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.2461028403838199</v>
+        <v>0.2586251300594427</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.0650285526557326</v>
+        <v>0.07793836223178374</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.1437478699483989</v>
+        <v>0.1420063836845671</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.01870627625552856</v>
+        <v>0.01700174322649417</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.3714543833545747</v>
+        <v>0.384565187729514</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.1828039635222964</v>
+        <v>0.1958468598166618</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.3289706813521391</v>
+        <v>0.3271775483495816</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.09281249499515809</v>
+        <v>0.0910676975925071</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.2899897267576037</v>
+        <v>0.2881888673569151</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.3199709254856913</v>
+        <v>0.3181345342473705</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.004740857485955985</v>
+        <v>-0.006496773140057144</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.04486373925320919</v>
+        <v>0.04309458857958504</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.008429593856732254</v>
+        <v>-0.01019836334387492</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.1213068518582148</v>
+        <v>0.1226369944962897</v>
       </c>
     </row>
     <row r="30">
@@ -5156,49 +5156,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3784</v>
+        <v>3785</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.1797247032295886</v>
+        <v>0.1922469929052113</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.05726414691007164</v>
+        <v>0.05590946449768808</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.1509757502159985</v>
+        <v>0.1495859226267555</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.05841677327947536</v>
+        <v>0.05705387502433723</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.3516401783708929</v>
+        <v>0.350185961949677</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.0307434264506341</v>
+        <v>0.02938048298466356</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.2242057920617526</v>
+        <v>0.2227890436476088</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.09656083988759434</v>
+        <v>-0.09790527587346531</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.04171770176348844</v>
+        <v>0.04033458280570557</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.05095504088775726</v>
+        <v>0.04954765758448332</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.1653840758743215</v>
+        <v>-0.1667401449466368</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.08976662951140213</v>
+        <v>-0.09114250358750553</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.01962381575108907</v>
+        <v>-0.02102937793988957</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.04563064152608831</v>
+        <v>-0.04453291177533458</v>
       </c>
     </row>
     <row r="31">
@@ -5208,49 +5208,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3871</v>
+        <v>3872</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.02973366743162842</v>
+        <v>0.02873647911815169</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.04886977504907009</v>
+        <v>-0.04987761278458436</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.01765498289292111</v>
+        <v>-0.01867881352963252</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.002196432697978423</v>
+        <v>-0.003222295728278368</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.06617808188822494</v>
+        <v>0.06512392187148208</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.1378045158938974</v>
+        <v>-0.1388010016275345</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.002199707568280473</v>
+        <v>-0.003233257545772972</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.1973446382573911</v>
+        <v>-0.1983372182510408</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.06356506642567439</v>
+        <v>-0.06459381230979488</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.202681229848352</v>
+        <v>-0.203690696556194</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.2639469527870091</v>
+        <v>-0.2649450023911939</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.3183800992517263</v>
+        <v>-0.3193639589672088</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.3109679645769248</v>
+        <v>-0.3119622166464708</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.3308531149187957</v>
+        <v>-0.3299407308087012</v>
       </c>
     </row>
     <row r="32">
@@ -5260,49 +5260,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3943</v>
+        <v>3944</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.01618857299056486</v>
+        <v>-0.01692816093616756</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.05428010222399848</v>
+        <v>0.05349949419757394</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.04869197006925674</v>
+        <v>-0.04945252225966357</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.05644764376843625</v>
+        <v>-0.05720476334857238</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.1020727352543886</v>
+        <v>0.1012674957493616</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.05909708791752877</v>
+        <v>0.05830655711866939</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.1907354475749727</v>
+        <v>0.1899100096584547</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.0413251751417647</v>
+        <v>0.04053052644314903</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.1209544300627243</v>
+        <v>0.1201383606566964</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.005749301147915276</v>
+        <v>-0.006545769156339531</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.1456095946315727</v>
+        <v>-0.1463739357583194</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.1730432198713174</v>
+        <v>-0.1738005043693818</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.1734015387475409</v>
+        <v>-0.1741651051236843</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.1629673299277741</v>
+        <v>-0.1623045683357347</v>
       </c>
     </row>
     <row r="33">
@@ -5312,49 +5312,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3982</v>
+        <v>3983</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.02785634273813287</v>
+        <v>-0.02846357808190447</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.1513726436910687</v>
+        <v>0.1507013807822943</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.004513747709715688</v>
+        <v>-0.005150924477405283</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.08929032850801377</v>
+        <v>0.0886308739028081</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.1658675894658401</v>
+        <v>0.165182322620403</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.2014232906681386</v>
+        <v>0.2007322781488696</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.2557750660193747</v>
+        <v>0.2550691109043512</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.1283487172799482</v>
+        <v>0.1276688911232355</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.2567872240291464</v>
+        <v>0.2560741497916297</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.1481272449748161</v>
+        <v>0.147431099435579</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.01742362608887049</v>
+        <v>-0.01808097830690514</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.005980861244012203</v>
+        <v>0.005317717090846941</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.07376408362004128</v>
+        <v>-0.07441248246574617</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.06096125720360845</v>
+        <v>-0.0604327184504001</v>
       </c>
     </row>
     <row r="34">
@@ -5364,49 +5364,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4016</v>
+        <v>4017</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.0009771675040965988</v>
+        <v>0.0004735476294186469</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.1154448692090924</v>
+        <v>0.114897131800177</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.03202897036079122</v>
+        <v>0.03149789184538321</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.2006655877199393</v>
+        <v>0.2000936267921318</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.2472307808700975</v>
+        <v>0.2466418138831088</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.1856158794960692</v>
+        <v>0.1850448074267064</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.2387882578400067</v>
+        <v>0.2382028896853043</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.08362229534881749</v>
+        <v>0.08307073039699731</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.1607089911600283</v>
+        <v>0.1601374086881648</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.07062963518133358</v>
+        <v>0.07007199769938666</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.04550854143608518</v>
+        <v>-0.0460395297543883</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.02201814323582596</v>
+        <v>-0.02255490676641614</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.05486374223262658</v>
+        <v>-0.05539664809791844</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.08985122220547481</v>
+        <v>-0.08940824182079155</v>
       </c>
     </row>
     <row r="35">
@@ -5416,49 +5416,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4045</v>
+        <v>4046</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.04475783553176882</v>
+        <v>0.04433649471818057</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.1715471005945588</v>
+        <v>0.1710817108030014</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.1352278414915062</v>
+        <v>0.1347680987456172</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.2542935779168261</v>
+        <v>0.2538052841503315</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.2720203453520753</v>
+        <v>0.2715232412023312</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.2869999265583871</v>
+        <v>0.2865012326428058</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.314531166519842</v>
+        <v>0.3140247902581876</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.1324649910580789</v>
+        <v>0.1319996556120486</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.2332663367008792</v>
+        <v>0.2327754212188395</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.1871561652870426</v>
+        <v>0.1866697361159098</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.07041193314758942</v>
+        <v>0.0699525031657231</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.1187186917357366</v>
+        <v>0.1182473792131304</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.08313109458977408</v>
+        <v>0.08266504930700336</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.09966266292150294</v>
+        <v>0.0999808732242542</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/btc_daily_14days/dxy/dxy_ma_ratio_50.xlsx
+++ b/workspaces/btc_daily_14days/dxy/dxy_ma_ratio_50.xlsx
@@ -568,1041 +568,1041 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ -0.02751</t>
+          <t>X ≈ -0.02748</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>33</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>2.058413018989661</v>
+        <v>2.029290596595246</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>6.495268448987879</v>
+        <v>6.494096275165838</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.05858716253711549</v>
+        <v>0.05840326618572078</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-5.856941127319466</v>
+        <v>-5.857499676164473</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.3485352187940975</v>
+        <v>-0.3001287594893256</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>2.972543959746595</v>
+        <v>2.996443422105749</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>2.888648029175023</v>
+        <v>2.9365656886145</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>5.448584178211149</v>
+        <v>5.497759694466687</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>2.362471465568809</v>
+        <v>2.435628343477561</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>1.513969229541622</v>
+        <v>1.613207788954604</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>1.309793389588009</v>
+        <v>1.409619121607108</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>1.344468795279944</v>
+        <v>1.468098484111266</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.924799233861485</v>
+        <v>1.073448578219761</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-1.879527507668215</v>
+        <v>-4.737831778404576</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -0.02555</t>
+          <t>X ≈ -0.02552</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>9.028602388206572</v>
+        <v>7.4660698795876</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.2446292663751919</v>
+        <v>-2.086480651879029</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>10.86792548848468</v>
+        <v>9.487006736672086</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>3.327701486276936</v>
+        <v>1.639115555861537</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>2.791244420234754</v>
+        <v>1.151161390620679</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.7496746645011569</v>
+        <v>-2.568261978043168</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-4.673903482387495</v>
+        <v>-6.622526618092039</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-5.141659627202785</v>
+        <v>-7.089529572974008</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-5.203841199071348</v>
+        <v>-7.128212861354648</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-2.211919318578992</v>
+        <v>-3.957000776119578</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-6.260283198479172</v>
+        <v>-8.158974398558229</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>1.460949798232569</v>
+        <v>-0.1068826513664831</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-2.803872849289995</v>
+        <v>-4.500918782801598</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-6.424982053120999</v>
+        <v>-4.252983293554273</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -0.0236</t>
+          <t>X ≈ -0.02357</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>49</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>4.646911463409239</v>
+        <v>4.617856932409403</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>11.18054928647771</v>
+        <v>11.17945758647722</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.6134269118815752</v>
+        <v>0.613278876234979</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-1.291802690415842</v>
+        <v>-1.292306865770954</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>4.279093173359037</v>
+        <v>4.327549839676642</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>6.61373565569415</v>
+        <v>6.637678304286275</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>4.493633635439913</v>
+        <v>4.541577272440236</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>4.028188843195018</v>
+        <v>4.077375204916258</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>6.006538487713996</v>
+        <v>6.079719733424199</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>5.158971034321027</v>
+        <v>5.258227781695346</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>9.034276517170213</v>
+        <v>9.134124331463084</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>2.951543478905229</v>
+        <v>3.075179006783678</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-1.548291556033654</v>
+        <v>-1.399642510077122</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-7.445390216388986</v>
+        <v>-7.27339145682047</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ -0.02164</t>
+          <t>X ≈ -0.02161</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-1.455517287801811</v>
+        <v>-1.524504958147368</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-7.131138077457784</v>
+        <v>-5.057926436238468</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-3.456737176983317</v>
+        <v>-1.541549142148995</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>2.779452570891863</v>
+        <v>4.455345574351561</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.2066420854128026</v>
+        <v>2.01171877884267</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.5035235113962528</v>
+        <v>2.284528961335361</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.4191391756787226</v>
+        <v>2.224608730989132</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>1.990361735648165</v>
+        <v>3.717625760711883</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-8.261024488829307</v>
+        <v>-6.109724300495557</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-7.073478260614777</v>
+        <v>-4.975505982163298</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-7.279843175044405</v>
+        <v>-5.180767438284818</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-3.167797890766423</v>
+        <v>-1.204379575210837</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-3.588573543552009</v>
+        <v>-1.599662382318286</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-1.322941236796233</v>
+        <v>0.6097618044831208</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.01968</t>
+          <t>X ≈ -0.01965</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-1.750130998542154</v>
+        <v>-1.03580562666923</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>3.86723644252659</v>
+        <v>3.249866762021178</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>2.029097387992934</v>
+        <v>1.39133753719026</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>3.605239475370837</v>
+        <v>2.988244840540588</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>7.406464681438607</v>
+        <v>6.902043946781319</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>16.38269119616663</v>
+        <v>15.98126655949659</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>19.19571511928831</v>
+        <v>17.39284417798712</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>18.73415154337489</v>
+        <v>16.93203798184089</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>18.67830769253654</v>
+        <v>16.89969333652216</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>20.72963249798232</v>
+        <v>19.01919742065743</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>17.63421265794481</v>
+        <v>15.88128671356408</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>17.67315731156909</v>
+        <v>15.94354510333684</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>17.25781668335176</v>
+        <v>15.55273451337668</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>20.38661214977514</v>
+        <v>20.21760494173736</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.01772</t>
+          <t>X ≈ -0.0177</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>4.948935738238966</v>
+        <v>4.61693796341595</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>2.283789558461251</v>
+        <v>2.022884584542631</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>9.315382379131549</v>
+        <v>8.752416666384597</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>8.386949807927827</v>
+        <v>8.884474691132127</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>5.729210459627069</v>
+        <v>6.362405549507685</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>4.965681915240829</v>
+        <v>5.61784420683</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>8.068001116245149</v>
+        <v>9.632879298756578</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>6.541576828869324</v>
+        <v>7.132679821221693</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>7.545093673917052</v>
+        <v>8.116961386537341</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>8.823486924245643</v>
+        <v>9.334814276531674</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>5.432513615642748</v>
+        <v>7.094276823926819</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>9.721421195661755</v>
+        <v>10.21394871137645</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>11.43124609066379</v>
+        <v>11.86206622002243</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>9.532464755387885</v>
+        <v>9.053139155423032</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.01576</t>
+          <t>X ≈ -0.01574</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>5.759098682233223</v>
+        <v>5.128987750700233</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>7.621791942713585</v>
+        <v>7.144362067492374</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>6.362561906034799</v>
+        <v>5.854780686460536</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>8.228831766304893</v>
+        <v>6.88458558224756</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>7.693892542101054</v>
+        <v>6.398182352844124</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>9.727840049481742</v>
+        <v>8.469795678775093</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>5.306489260029757</v>
+        <v>3.915703851267935</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>3.105379583067702</v>
+        <v>2.552329449310299</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>6.519077375806148</v>
+        <v>6.115029976410597</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>3.06611008034929</v>
+        <v>2.594095688168018</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>2.862685500422266</v>
+        <v>1.490924867958569</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>5.505124127585347</v>
+        <v>5.151146045263232</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>4.217520744587709</v>
+        <v>3.857102612583311</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>4.444583164268742</v>
+        <v>4.107377066804673</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.0138</t>
+          <t>X ≈ -0.01378</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>120</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.8120380783741226</v>
+        <v>-0.8410595960322311</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1.734532956772966</v>
+        <v>1.73342279871472</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>3.832945683603569</v>
+        <v>3.832882248883905</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-1.852548459115951</v>
+        <v>-1.853007057322245</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.7277621746350817</v>
+        <v>-0.6793191719312048</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.3998806111738844</v>
+        <v>0.4238209130744224</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>1.147405809753032</v>
+        <v>1.195350858801127</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>4.009209470058472</v>
+        <v>4.058412068467547</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>8.94248781713344</v>
+        <v>9.847833054336583</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>7.263924054289561</v>
+        <v>8.195568629474096</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>2.898697664559208</v>
+        <v>3.831149983640927</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>6.265326641109894</v>
+        <v>7.221821104448757</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>4.18120994903451</v>
+        <v>5.162954794929867</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>4.408351280210965</v>
+        <v>5.41368337311058</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.01184</t>
+          <t>X ≈ -0.01183</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>5.677936212060828</v>
+        <v>5.299865976539863</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1.658475827035289</v>
+        <v>1.32268627344115</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>6.097027007787155</v>
+        <v>6.333523198829667</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>5.625319788219123</v>
+        <v>6.465777230019363</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>3.276597353464808</v>
+        <v>4.177087824766907</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>5.387664559083227</v>
+        <v>6.252990771471808</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.4667072029692676</v>
+        <v>0.7842481482726456</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.0005940689736192439</v>
+        <v>0.3194591851536686</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>2.360286685383635</v>
+        <v>2.087089167735371</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>6.355140717176447</v>
+        <v>6.680446757224999</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>7.969622223601263</v>
+        <v>8.28464816745867</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>5.583566536617568</v>
+        <v>5.937052933317766</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>6.98327732769728</v>
+        <v>7.35090936601646</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>10.84774521960438</v>
+        <v>11.2168962245162</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.009888</t>
+          <t>X ≈ -0.009869</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>190</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>2.244592965156187</v>
+        <v>2.739864012238613</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>2.7380820239987</v>
+        <v>3.785692048714097</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.2458239412401042</v>
+        <v>0.7701825179477879</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.1477859903487015</v>
+        <v>-0.148354557055697</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>4.038796118811206</v>
+        <v>4.087135488835948</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.6612075796584307</v>
+        <v>0.6850394862841114</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.9976156632414259</v>
+        <v>-0.4245812371576179</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-2.514708347990677</v>
+        <v>-1.940263108352902</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-4.153037065048885</v>
+        <v>-4.079929082899746</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-1.849113504941812</v>
+        <v>-2.275602377295094</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.001951050428964</v>
+        <v>-0.902184101692427</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-5.701560633306499</v>
+        <v>-5.577984590636639</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-3.492119332738831</v>
+        <v>-3.343498332727258</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-4.319718895228135</v>
+        <v>-4.147720135661359</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.007928</t>
+          <t>X ≈ -0.00791</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.9511525099020233</v>
+        <v>0.8863044558344626</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.4013133151037351</v>
+        <v>-0.689755032197084</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1.060961775422726</v>
+        <v>0.4811556598474809</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>2.247103781152191</v>
+        <v>2.177523922080638</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-1.454396365403142</v>
+        <v>-1.442030940640088</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-2.74142570770497</v>
+        <v>-3.259118285313285</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>4.0364328034754</v>
+        <v>3.993058577642657</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>7.796076198169153</v>
+        <v>7.187217738493267</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>6.681310105417609</v>
+        <v>7.152673068510644</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>5.83477033293368</v>
+        <v>6.332335804136825</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>7.747127566611425</v>
+        <v>7.700227841635957</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>9.899447995977674</v>
+        <v>9.854169150502393</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>9.483239654755323</v>
+        <v>9.462939942608593</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>11.29988567174509</v>
+        <v>11.28628372215059</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.00597</t>
+          <t>X ≈ -0.005954</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-2.682653566031007</v>
+        <v>-2.501688890662415</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.5061442323304917</v>
+        <v>0.562652825855892</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.3593611279414759</v>
+        <v>0.5907499355295727</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.331356183424148</v>
+        <v>1.143754083388878</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.636487859732931</v>
+        <v>1.92353606869213</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-2.273310551943645</v>
+        <v>-1.605905255597733</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.095771573177004</v>
+        <v>-0.8215204318428562</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-3.667470788246675</v>
+        <v>-2.977932379703908</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.9032887493621828</v>
+        <v>0.7907274369782584</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.319107558174338</v>
+        <v>1.237919045584491</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.413004547815255</v>
+        <v>-1.504367753038878</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-2.643550455462339</v>
+        <v>-2.716522412511104</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-4.329121849114458</v>
+        <v>-3.958903867260332</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-6.63595251725777</v>
+        <v>-6.252983293555992</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -0.004011</t>
+          <t>X ≈ -0.003996</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>4.569783709697063</v>
+        <v>4.408373600895935</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.667307063522756</v>
+        <v>-1.312509625683504</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.063134522569236</v>
+        <v>-1.246436901239178</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1.341375272946308</v>
+        <v>1.189284146611655</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>2.625491732444019</v>
+        <v>2.085976866031899</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.2618908848622823</v>
+        <v>-0.8703661269167</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-2.167840424319287</v>
+        <v>-2.777902041322655</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-4.000978485372293</v>
+        <v>-4.629018340592239</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-5.886985797283245</v>
+        <v>-6.054518662234322</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-7.193586465750087</v>
+        <v>-7.341469990410737</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-2.839019890413944</v>
+        <v>-2.923005777005578</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-5.08643954524932</v>
+        <v>-5.178365640271245</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-5.507602796304326</v>
+        <v>-6.037347327058676</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-4.826808537141019</v>
+        <v>-5.327057367630161</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ -0.002053</t>
+          <t>X ≈ -0.002038</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-8.768396174593263</v>
+        <v>-8.553954940676064</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-7.766068541046948</v>
+        <v>-7.53509330993414</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-12.07633868141252</v>
+        <v>-11.82728388892208</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-11.51671240975384</v>
+        <v>-11.26974781992227</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-12.92820921977052</v>
+        <v>-12.62863648417303</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-15.68106967959218</v>
+        <v>-15.39259140912169</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-11.85392371889301</v>
+        <v>-11.55833816660405</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-10.58224022441232</v>
+        <v>-10.29282257238913</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-10.64840670785167</v>
+        <v>-10.33490048033289</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-8.449933014846486</v>
+        <v>-8.123485018136634</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-12.14627903631173</v>
+        <v>-11.80394052571346</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-12.1164628540869</v>
+        <v>-11.75017423768765</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-11.66795651873844</v>
+        <v>-11.28027413759042</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-11.44681611425813</v>
+        <v>-11.03559198920816</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ -9.48e-05</t>
+          <t>X ≈ -8.145e-05</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.096863837328875</v>
+        <v>1.038096635139865</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>1.59515465239776</v>
+        <v>1.546508272193392</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>2.460712741009495</v>
+        <v>2.402568654239332</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>3.01114757831175</v>
+        <v>2.949140543934554</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>5.836918304070238</v>
+        <v>5.795458072804124</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>9.922050836627903</v>
+        <v>9.824557518600287</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>12.78442538589532</v>
+        <v>12.68620691226799</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>9.379985041997237</v>
+        <v>9.307558342735938</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>8.480658740543007</v>
+        <v>8.43915598221561</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>8.47811234711277</v>
+        <v>8.455567091964355</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>6.593543163041268</v>
+        <v>6.585664395955526</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>6.631555666982237</v>
+        <v>6.22945435922405</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>6.215302089650152</v>
+        <v>5.838017030210231</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>4.334511617763326</v>
+        <v>3.998062731548416</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 0.001864</t>
+          <t>X ≈ 0.001876</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-2.876231112919378</v>
+        <v>-2.700949846624908</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-2.423512028863414</v>
+        <v>-2.211979568487159</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-3.23041149191468</v>
+        <v>-3.431834352673228</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-2.281363905968689</v>
+        <v>-2.479776847738492</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.997890589183683</v>
+        <v>-2.144420399889981</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-3.345744847095403</v>
+        <v>-3.523560725210146</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-3.022951260520713</v>
+        <v>-3.175233358871132</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-5.959228898883268</v>
+        <v>-6.12063972128702</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-10.14480458227857</v>
+        <v>-9.88574515981243</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-10.99883102149918</v>
+        <v>-10.71357964015093</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-8.319555968289734</v>
+        <v>-8.021502008937503</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-9.527203309297747</v>
+        <v>-8.795781907636048</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-8.299502024390286</v>
+        <v>-7.535777792434608</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-5.185312631635156</v>
+        <v>-4.385763376543593</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.003822</t>
+          <t>X ≈ 0.003833</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-2.867264602257571</v>
+        <v>-3.309639717176218</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>2.447945499642749</v>
+        <v>2.090230634594903</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>3.275605511259059</v>
+        <v>3.339567521345359</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>5.034111344237182</v>
+        <v>5.11132228683428</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>3.276838792966764</v>
+        <v>3.39231764793427</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.540563523458722</v>
+        <v>1.614878911450212</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>2.677308909062695</v>
+        <v>2.785683212439018</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>3.850595455491622</v>
+        <v>3.9737737177905</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>1.750082881387257</v>
+        <v>1.468184184606173</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.7326229140571243</v>
+        <v>-1.002227124046328</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-2.16344674826734</v>
+        <v>-2.44272011219271</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-2.9483900736222</v>
+        <v>-3.210780777256161</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.731547013346784</v>
+        <v>-1.955458880329239</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.506949266237505</v>
+        <v>-1.707528748101637</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.005781</t>
+          <t>X ≈ 0.005791</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-2.478776459417055</v>
+        <v>-2.481068164138485</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-2.541758298380969</v>
+        <v>-2.15135306306378</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-3.714080873153883</v>
+        <v>-3.3107088433363</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.644023837259276</v>
+        <v>-1.280219780219781</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.6289495457675329</v>
+        <v>-0.2414305885701253</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>2.388346701692335</v>
+        <v>2.713572845609306</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>1.921219516218379</v>
+        <v>2.266528542405709</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1.840818124216391</v>
+        <v>2.192212180325235</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>1.990213320260764</v>
+        <v>2.159169326061473</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.9653678016402409</v>
+        <v>0.9560965650808839</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.3741068698364813</v>
+        <v>0.3714760482839807</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.4096711122630765</v>
+        <v>0.04682554539119366</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>1.161109050504322</v>
+        <v>0.8050727289970112</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.1749820531227542</v>
+        <v>-0.4837525243252756</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.007739</t>
+          <t>X ≈ 0.007747</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>2.208556427131761</v>
+        <v>2.881651296028274</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-2.887847740434097</v>
+        <v>-3.335784265275656</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.296284462817731</v>
+        <v>-1.993086723328211</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-5.135625132660216</v>
+        <v>-5.800742450393408</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-2.687274410447401</v>
+        <v>-3.350375345623348</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-7.382071772619156</v>
+        <v>-7.98947757275657</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-8.95298152058318</v>
+        <v>-9.540542098134672</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-4.949293504420901</v>
+        <v>-5.574232855373481</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-4.017754651817455</v>
+        <v>-4.627150527122978</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-5.379232409890825</v>
+        <v>-5.944195033819689</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-5.818292720938317</v>
+        <v>-6.643519582541103</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-4.008474369383414</v>
+        <v>-4.61336941472873</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.6500021120811965</v>
+        <v>-1.550210883850674</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-3.424982053122804</v>
+        <v>-4.272785273754167</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.009699</t>
+          <t>X ≈ 0.009703</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-1.937288084138707</v>
+        <v>-2.218413797874121</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>4.259903050899517</v>
+        <v>4.451280447148733</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2.193564709115179</v>
+        <v>2.407066431354629</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.6523494617081553</v>
+        <v>0.6310511656594855</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.4390505710544659</v>
+        <v>-0.4155963569196359</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>2.651153698929484</v>
+        <v>2.625382743587465</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.349286104789826</v>
+        <v>-1.301627890256896</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.1644138979749812</v>
+        <v>-0.1065158682099181</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>2.34854969824962</v>
+        <v>2.069401901524152</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>4.863198255458535</v>
+        <v>4.572059803593618</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>5.775355175891477</v>
+        <v>5.485093848131839</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>8.617167301462892</v>
+        <v>8.320950675877519</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>4.827266458514785</v>
+        <v>4.604183475692736</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>5.934568508675063</v>
+        <v>4.858127817555079</v>
       </c>
     </row>
     <row r="26">
@@ -1612,153 +1612,153 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>7.202956208529379</v>
+        <v>7.541498226723185</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.9372633816511993</v>
+        <v>1.298504717044921</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>2.545308692558464</v>
+        <v>2.904054022135135</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>2.008354681201354</v>
+        <v>2.359963859963941</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.8024171187676714</v>
+        <v>1.19606428855684</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>3.786010437275664</v>
+        <v>4.160755612073075</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>4.378128437072128</v>
+        <v>4.768289576479219</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>3.911059793285425</v>
+        <v>4.315263834519143</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>3.178936697165298</v>
+        <v>3.614003215601016</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.3155950820434867</v>
+        <v>0.7834477151744252</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>2.795457682172518</v>
+        <v>3.279456578162225</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.1452720761386601</v>
+        <v>0.6462851068248696</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>1.067403102019846</v>
+        <v>1.603014866399576</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>1.293138752246414</v>
+        <v>1.855124814552013</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 0.01361</t>
+          <t>X ≈ 0.01362</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>182</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>5.701376832725103</v>
+        <v>5.62607183543119</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>3.025952249908208</v>
+        <v>2.963744743772878</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.9951039932928225</v>
+        <v>1.484646479459215</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-2.700769016925598</v>
+        <v>-2.180577345618808</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-3.2440643301466</v>
+        <v>-2.672510285351407</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.3445195868543749</v>
+        <v>0.6041431215506563</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>2.460582895365469</v>
+        <v>2.447305725583306</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.2042879462234879</v>
+        <v>-0.1776794994263824</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1.93253209505599</v>
+        <v>1.968633118844991</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>2.18151439762724</v>
+        <v>2.251204976041485</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.2209889584351572</v>
+        <v>-0.1269112808499031</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>2.560641941172882</v>
+        <v>2.671672705114979</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.4921394395078167</v>
+        <v>0.6376840609757934</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>2.366226738086006</v>
+        <v>2.538225497652668</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 0.01557</t>
+          <t>X ≈ 0.01558</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-2.13293212774893</v>
+        <v>-1.475562106768265</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-2.355521489072807</v>
+        <v>-2.369439867812495</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-2.045668407205561</v>
+        <v>-1.383540103988274</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-3.659436035791593</v>
+        <v>-3.323112690982022</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-1.000189813189536</v>
+        <v>-1.383127545819342</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-4.237559852592526</v>
+        <v>-4.556980858254605</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-10.71064304181783</v>
+        <v>-10.83947371876741</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-11.17771168560457</v>
+        <v>-11.62510977953512</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-9.82025412581531</v>
+        <v>-10.30565578242404</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-5.705633915052978</v>
+        <v>-6.28387743853434</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-6.619554931469175</v>
+        <v>-7.175562997528985</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-6.585176779113894</v>
+        <v>-7.132871766332421</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-7.005327632427239</v>
+        <v>-7.537679848398575</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-5.361152265888691</v>
+        <v>-5.903332943905703</v>
       </c>
     </row>
     <row r="29">
@@ -1768,49 +1768,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-2.505513430237784</v>
+        <v>-3.613138461642933</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.8527453562545801</v>
+        <v>-0.9150197875285571</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.4943998998864885</v>
+        <v>-0.1975554648527122</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>1.722390767354455</v>
+        <v>0.9890263924551945</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-1.011430233500455</v>
+        <v>-1.619068830172864</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-6.883588845508136</v>
+        <v>-6.831439022940323</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-4.120476494682642</v>
+        <v>-4.6969427376333</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-7.95833165532332</v>
+        <v>-8.485481532008912</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-10.26650482308208</v>
+        <v>-11.17656158558422</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-11.11642361941194</v>
+        <v>-12.50523839334314</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-6.826742755200193</v>
+        <v>-8.383026435925863</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-5.668769097226885</v>
+        <v>-7.247765946562382</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.4709424224504417</v>
+        <v>-2.179515805536205</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-6.986779805931775</v>
+        <v>-7.901334941907741</v>
       </c>
     </row>
     <row r="30">
@@ -1823,46 +1823,46 @@
         <v>87</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-7.09027801620821</v>
+        <v>-6.536695253678424</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-4.666814767276342</v>
+        <v>-4.73978446350818</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-7.360436726744027</v>
+        <v>-8.541021615361302</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-2.632510433730403</v>
+        <v>-2.713698109440955</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-12.36620228567668</v>
+        <v>-13.45833828686312</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-7.471127106616237</v>
+        <v>-7.526489106835939</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-9.854688040595079</v>
+        <v>-9.849674209016193</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-4.574630247600204</v>
+        <v>-4.661925565833748</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-4.635612404123016</v>
+        <v>-4.682451402043114</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-11.23265763723445</v>
+        <v>-11.23113073577618</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-4.540807071356717</v>
+        <v>-3.940764866190158</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-10.25355535578301</v>
+        <v>-9.640103612316011</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-12.97255678380905</v>
+        <v>-12.82386723603123</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-12.74682113358252</v>
+        <v>-12.57482237401586</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>72</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-2.48091603053431</v>
+        <v>-3.242239301200463</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>5.63012009862404</v>
+        <v>4.859122803996762</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-1.709095730575385</v>
+        <v>-2.468293048228347</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-2.96775947587593</v>
+        <v>-3.727297895902574</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>2.049506526583933</v>
+        <v>1.339008518701057</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>10.68021388955229</v>
+        <v>9.90744433898432</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>10.59550353028615</v>
+        <v>9.862938120559818</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>12.90621266427721</v>
+        <v>13.52070570470708</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>10.06745272997667</v>
+        <v>10.72210518859355</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>10.60642282253565</v>
+        <v>11.26024904533239</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>6.235054997608799</v>
+        <v>6.8786753505956</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>7.658322038853008</v>
+        <v>7.782018659881253</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>7.238171185539599</v>
+        <v>7.386860733317427</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>8.852795724655032</v>
+        <v>9.024794484221694</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>39</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-1.198864748483075</v>
+        <v>-1.228060542835706</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>10.01046197896588</v>
+        <v>10.00927519252122</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>4.487485466005722</v>
+        <v>4.487332076001401</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>14.87412086600437</v>
+        <v>14.87362637362637</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>6.643523620600988</v>
+        <v>6.692069540366759</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>14.63320534254373</v>
+        <v>14.65716275149335</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>6.856187290969906</v>
+        <v>6.904198969960227</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>8.953221211285687</v>
+        <v>9.002468773679404</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>14.02044418296805</v>
+        <v>14.09370129274775</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>15.73462795074079</v>
+        <v>15.83397527603536</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>12.96582422837803</v>
+        <v>13.0657322643967</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>18.12840750893849</v>
+        <v>18.25210412996673</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>10.01594896331737</v>
+        <v>10.1646385110952</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>10.2416846135439</v>
+        <v>10.41368337311057</v>
       </c>
     </row>
     <row r="33">
@@ -1979,46 +1979,46 @@
         <v>34</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>3.40143691064214</v>
+        <v>3.372241116289509</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-4.09210212359816</v>
+        <v>-4.093288910042816</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>4.33665590341149</v>
+        <v>4.336502513407169</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>13.29041045876456</v>
+        <v>13.28991596638656</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>9.810944435080621</v>
+        <v>9.859490354846393</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-1.656387417637227</v>
+        <v>-1.632430008687614</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-1.741097776903395</v>
+        <v>-1.693086097913074</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-5.149342891278351</v>
+        <v>-5.100095328884635</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-11.09267798897758</v>
+        <v>-11.01942087919788</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-9.001420314719248</v>
+        <v>-8.902072989424674</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-3.323768531802962</v>
+        <v>-3.223860495784287</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-3.289390379447639</v>
+        <v>-3.165693758419394</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>2.172811708415423</v>
+        <v>2.321501256193251</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-3.483805582534515</v>
+        <v>-3.311806822967853</v>
       </c>
     </row>
     <row r="34">
@@ -2028,49 +2028,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>6.139773624638032</v>
+        <v>4.632745317970134</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>7.976863393643221</v>
+        <v>6.620996804242907</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>14.4786437330261</v>
+        <v>13.37011595878532</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>7.712317152476523</v>
+        <v>6.357142857142883</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>3.725751737311853</v>
+        <v>2.296465144762358</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>14.36795335315385</v>
+        <v>16.85496494929561</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>10.83496713181871</v>
+        <v>13.22288028864158</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>6.919622625962987</v>
+        <v>5.61419038540101</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>10.3069163315092</v>
+        <v>9.148646347692839</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>16.35354925931726</v>
+        <v>15.467674909735</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>16.14884810105707</v>
+        <v>15.2635344621989</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>19.63150211548136</v>
+        <v>18.89312977099237</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>19.21135126216795</v>
+        <v>18.49797184442854</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>26.33363863653242</v>
+        <v>25.88987384930102</v>
       </c>
     </row>
   </sheetData>
@@ -2210,1041 +2210,1041 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.02849</t>
+          <t>X &gt; -0.02846</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4046</v>
+        <v>4056</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.1675195447304887</v>
+        <v>0.1563910013602481</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.2450097541741201</v>
+        <v>0.2331614341066199</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.06082183303204403</v>
+        <v>0.04948650218339878</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.105876290067485</v>
+        <v>0.0944065771906395</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.07423594157224045</v>
+        <v>0.06135707939599655</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.1384992592831651</v>
+        <v>0.1261966703304438</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.116640136914981</v>
+        <v>0.1036158464630006</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.008603801712737891</v>
+        <v>-0.004083512045660598</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.01407720776165888</v>
+        <v>-0.02748901657353287</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.03555248610631878</v>
+        <v>-0.04956646957534616</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.05353477764435155</v>
+        <v>-0.067475990762766</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.1040846365971433</v>
+        <v>-0.118698715947005</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.04088325808118043</v>
+        <v>-0.05637866087093357</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.07302950739858005</v>
+        <v>-0.08927520677107736</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -0.02653</t>
+          <t>X &gt; -0.0265</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4013</v>
+        <v>4023</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.1519702089092689</v>
+        <v>0.1410279174321474</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.1936121621161035</v>
+        <v>0.1818040267601333</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.0608402093406184</v>
+        <v>0.04941335945108705</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.1549101736393226</v>
+        <v>0.1432290744217326</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.07771250481473402</v>
+        <v>0.06432228761951109</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.1151941321674741</v>
+        <v>0.1026525135299039</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.09384515549344741</v>
+        <v>0.0803776300098562</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.03613064942716449</v>
+        <v>-0.04921421694621131</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.03362021952838035</v>
+        <v>-0.04769355867686187</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.04829462829829367</v>
+        <v>-0.06320593030899602</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.06474579920394774</v>
+        <v>-0.07959235633775563</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.1159964888901754</v>
+        <v>-0.1317149495045271</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.04882433015546184</v>
+        <v>-0.06564644582991264</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.05817417871458019</v>
+        <v>-0.05114387024015343</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.02457</t>
+          <t>X &gt; -0.02455</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3987</v>
+        <v>3998</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.09408396946565034</v>
+        <v>0.09522350296143145</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.1964700194375837</v>
+        <v>0.1959878979372078</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.009634889043567796</v>
+        <v>-0.009601106389467873</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.1342197863484813</v>
+        <v>0.1338751069289899</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.0600170370944042</v>
+        <v>0.05752614515452592</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.1208341092714065</v>
+        <v>0.1193540798854116</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.1249365687327071</v>
+        <v>0.1222917386147913</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.002836505102564502</v>
+        <v>-0.005190233979554648</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>9.579388222391572e-05</v>
+        <v>-0.003418175343455232</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.0341852122091808</v>
+        <v>-0.03885753832668826</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.02434349863180074</v>
+        <v>-0.02907095787465153</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.1262800613670336</v>
+        <v>-0.1318702290076388</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.03085812461307569</v>
+        <v>-0.03791212656420839</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.0166549901681563</v>
+        <v>-0.02486923652757866</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.02262</t>
+          <t>X &gt; -0.02259</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3938</v>
+        <v>3949</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.03743375433023743</v>
+        <v>0.03910574199842642</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.05979661057903485</v>
+        <v>0.05970275872767417</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.01738756254415108</v>
+        <v>-0.01732992866057259</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.1519635906556047</v>
+        <v>0.151571464655575</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.007519644845302764</v>
+        <v>0.004542817468632165</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.04004381577858851</v>
+        <v>0.03847337920279159</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.07057746353498118</v>
+        <v>0.06745633948654728</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.05299400689703049</v>
+        <v>-0.05584754127403357</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.07464155807251416</v>
+        <v>-0.07889899517876131</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.09880295118326643</v>
+        <v>-0.1045848568075982</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.137058679122994</v>
+        <v>-0.1427697598947901</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.1645770023201436</v>
+        <v>-0.1716639521157077</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.01197690619265046</v>
+        <v>-0.02101549734361186</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.07577975490162459</v>
+        <v>0.06507191029297843</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.02066</t>
+          <t>X &gt; -0.02063</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3889</v>
+        <v>3898</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.05624440001408004</v>
+        <v>0.05956344997878205</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.1503997989857737</v>
+        <v>0.1266599390620229</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.02594700446729092</v>
+        <v>0.002612395579525639</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.1188581753736386</v>
+        <v>0.09526246527268967</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.005010773776184863</v>
+        <v>-0.02171833543800261</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.03420413846173176</v>
+        <v>0.009086813094853596</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.06618571144060326</v>
+        <v>0.03923295006462979</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.0787395536660469</v>
+        <v>-0.1052182797043315</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.02850391984137701</v>
+        <v>6.107584496817253e-06</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.01092455309581197</v>
+        <v>-0.04085551422341638</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.04706216580332523</v>
+        <v>-0.0768544490692733</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.1267375002543361</v>
+        <v>-0.1581522802896842</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.03308692390007195</v>
+        <v>-0.0003610614447637772</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.09340313587184568</v>
+        <v>0.05794538781896819</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.0187</t>
+          <t>X &gt; -0.01868</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3820</v>
+        <v>3830</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.08887264674193318</v>
+        <v>0.07901125603937231</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.08326322086946192</v>
+        <v>0.07120874742722805</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.01023555481629046</v>
+        <v>-0.02204382103392533</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.05588427231085547</v>
+        <v>0.0438988095238102</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.1286804093726914</v>
+        <v>-0.1446467519369321</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.2610957586538873</v>
+        <v>-0.2744923573373441</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.2793476731514204</v>
+        <v>-0.268872941188306</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.4185535551570965</v>
+        <v>-0.4077074248179144</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.3083642634874195</v>
+        <v>-0.3000405586211912</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.3855576516623955</v>
+        <v>-0.379258542832261</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.3664359780647501</v>
+        <v>-0.3601843704946219</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.4482539248658171</v>
+        <v>-0.4440309805733946</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.278040393744476</v>
+        <v>-0.2764995729559558</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.273149592389764</v>
+        <v>-0.2999806825900322</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.01674</t>
+          <t>X &gt; -0.01672</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3726</v>
+        <v>3732</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.03373764059051609</v>
+        <v>-0.04015187829152467</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.02774806366773674</v>
+        <v>0.01995895320501972</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.2455034253989794</v>
+        <v>-0.2524556987850062</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.1542929043794175</v>
+        <v>-0.1882492173780221</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.2764640222782191</v>
+        <v>-0.3155179002599766</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.3929575679255208</v>
+        <v>-0.429221452537881</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.4899356458307693</v>
+        <v>-0.5288867995791406</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.594144606176549</v>
+        <v>-0.6057133064127456</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.5064922951879112</v>
+        <v>-0.5210657972668358</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.6178845948012537</v>
+        <v>-0.6343440563096649</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.5127326130106695</v>
+        <v>-0.5559338873899264</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.7048157770745078</v>
+        <v>-0.7239029017446441</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.5734437564751218</v>
+        <v>-0.5952507647329881</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.5205268733052506</v>
+        <v>-0.5455877951638044</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.01478</t>
+          <t>X &gt; -0.01476</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3611</v>
+        <v>3621</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.2182228738014658</v>
+        <v>-0.1986093482771878</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.2141004675120683</v>
+        <v>-0.1984361712594662</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.455951365890499</v>
+        <v>-0.4396700701637002</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.4212713970763744</v>
+        <v>-0.4050635401503015</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.530297033882654</v>
+        <v>-0.5213231275713639</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.7152759633843431</v>
+        <v>-0.7020165095872386</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.6745351651256897</v>
+        <v>-0.6651335718089157</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.7119638478722337</v>
+        <v>-0.7025215764721935</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.7302365522259322</v>
+        <v>-0.7244920968741795</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.7352092659843947</v>
+        <v>-0.7333103119398814</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.6202300051582199</v>
+        <v>-0.6186793504784873</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.902584563847121</v>
+        <v>-0.9039996797390799</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.7260222437701103</v>
+        <v>-0.7317354995802958</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.6786513967948622</v>
+        <v>-0.6882221778421993</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.01282</t>
+          <t>X &gt; -0.0128</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3491</v>
+        <v>3501</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.1978110077032937</v>
+        <v>-0.1765887742324566</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.2810829971351509</v>
+        <v>-0.2646524170169329</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.6033783627221538</v>
+        <v>-0.5861157366263399</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.3720725292892766</v>
+        <v>-0.3554339423037831</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.5235093464319789</v>
+        <v>-0.515907667610449</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.7536084723923651</v>
+        <v>-0.7406056243314296</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.7371627552103277</v>
+        <v>-0.7289033894819283</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.8742499544754025</v>
+        <v>-0.8657069627597593</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.062727793796576</v>
+        <v>-1.086868280291853</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.010172313372784</v>
+        <v>-1.039355862631012</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.741189993805051</v>
+        <v>-0.7712013499341666</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.148975095097427</v>
+        <v>-1.182519672341918</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.8947039576448148</v>
+        <v>-0.9337814394092661</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.8535125601408069</v>
+        <v>-0.8973706114652629</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.01087</t>
+          <t>X &gt; -0.01085</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3326</v>
+        <v>3335</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.4893017747691601</v>
+        <v>-0.4491799252454101</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.3773028425915967</v>
+        <v>-0.343662378820845</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.935779711529733</v>
+        <v>-0.9305415427090082</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.6695980050526273</v>
+        <v>-0.6949604954089281</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.712029372133415</v>
+        <v>-0.7495020459416679</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-1.058271746653787</v>
+        <v>-1.08871267131893</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.7968857086377525</v>
+        <v>-0.8042206774181295</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.9176502142075407</v>
+        <v>-0.9246987410367069</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-1.232540598686761</v>
+        <v>-1.244852369159176</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-1.375559159446325</v>
+        <v>-1.423609906078127</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.173325897554918</v>
+        <v>-1.221957277936333</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-1.482970696189724</v>
+        <v>-1.536897199340274</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.285523834999424</v>
+        <v>-1.346152855811269</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-1.434001896778796</v>
+        <v>-1.50035960540017</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.008907</t>
+          <t>X &gt; -0.008889</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3136</v>
+        <v>3145</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.6549395300580088</v>
+        <v>-0.641840767255573</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.5660538389730192</v>
+        <v>-0.5931305318356763</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-1.007369218553414</v>
+        <v>-1.033287988344867</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.7012128911475628</v>
+        <v>-0.7279827937514156</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.9998663757301856</v>
+        <v>-1.041699544068145</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-1.162449384408674</v>
+        <v>-1.195870989266339</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.7847241361330646</v>
+        <v>-0.8271559695165465</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.8208896767653258</v>
+        <v>-0.863345090864982</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.055597254104867</v>
+        <v>-1.073575874529382</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.346868047952668</v>
+        <v>-1.372138182856752</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.18370893995094</v>
+        <v>-1.241275848202257</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.227380106887374</v>
+        <v>-1.292761554079128</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.151833419001179</v>
+        <v>-1.225486515393456</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-1.259165726592137</v>
+        <v>-1.340423675114124</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.006949</t>
+          <t>X &gt; -0.006932</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2947</v>
+        <v>2954</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.7579430575613841</v>
+        <v>-0.740647719730255</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.6280940127499193</v>
+        <v>-0.5868829761251035</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-1.140017524580394</v>
+        <v>-1.131209023146745</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.8902973333140594</v>
+        <v>-0.9158473105841551</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.9707159963449925</v>
+        <v>-1.015814880308753</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-1.061184869612944</v>
+        <v>-1.062465358411572</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.093919474302737</v>
+        <v>-1.138821839018036</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-1.373521692497469</v>
+        <v>-1.383879112668438</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-1.55178846243529</v>
+        <v>-1.605469425010305</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-1.807448181643714</v>
+        <v>-1.870294760891881</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.756470426120018</v>
+        <v>-1.819416404992744</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.940977158615055</v>
+        <v>-2.013500810875023</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.833892737270595</v>
+        <v>-1.916579763016465</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-2.064615578742028</v>
+        <v>-2.156842467557439</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.004991</t>
+          <t>X &gt; -0.004975</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2710</v>
+        <v>2718</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.5896196662302771</v>
+        <v>-0.5877390676551997</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.6387589935467446</v>
+        <v>-0.6866955034494282</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.271143997144108</v>
+        <v>-1.280724223385022</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-1.084589541235445</v>
+        <v>-1.094679514034361</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-1.19872607527136</v>
+        <v>-1.271034462341206</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.9551797822652048</v>
+        <v>-1.015279259906812</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-1.093757501080148</v>
+        <v>-1.166372660244434</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-1.172906956079551</v>
+        <v>-1.245469778223864</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-1.766494476898757</v>
+        <v>-1.813527725021089</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-2.080877595052158</v>
+        <v>-2.140176460056125</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.786507847949629</v>
+        <v>-1.846771622748854</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.879534401658297</v>
+        <v>-1.952458464301756</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.615675283577978</v>
+        <v>-1.739247721588377</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.66483445164674</v>
+        <v>-1.80118049738244</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; -0.003032</t>
+          <t>X &gt; -0.003017</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2491</v>
+        <v>2502</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.043216350023165</v>
+        <v>-1.019058146954578</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.6362491471698917</v>
+        <v>-0.6326683849831696</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.289431461990311</v>
+        <v>-1.283684279973144</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.29787187536062</v>
+        <v>-1.29185623293904</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.534937917860553</v>
+        <v>-1.560848389970531</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.016131315196255</v>
+        <v>-1.027789746208121</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.999327890405965</v>
+        <v>-1.027247821590194</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.9242728071774522</v>
+        <v>-0.9533648663647227</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.404235304211404</v>
+        <v>-1.447399011017069</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-1.631386128700143</v>
+        <v>-1.691143925061489</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.693974673602106</v>
+        <v>-1.753859321661942</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-1.597594527532877</v>
+        <v>-1.673962880764826</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.273510640748967</v>
+        <v>-1.368188762842735</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.386844758863418</v>
+        <v>-1.496788249591262</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; -0.001074</t>
+          <t>X &gt; -0.00106</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2262</v>
+        <v>2272</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.2611358107541335</v>
+        <v>-0.2562825032239715</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.08555838651615488</v>
+        <v>0.06608061710252855</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.1973882465846302</v>
+        <v>-0.2163304463207467</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.26333850560993</v>
+        <v>-0.2817703768624042</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.3815077109032572</v>
+        <v>-0.4404297008567255</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.4685154069287165</v>
+        <v>0.4263935207241545</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.0995679737512063</v>
+        <v>0.0388396693223001</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.05347897821016545</v>
+        <v>-0.007909200702037822</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.4683753345236852</v>
+        <v>-0.5476959573451268</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.9410911521627909</v>
+        <v>-1.039982634829407</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.6358059295435226</v>
+        <v>-0.7364655378010951</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.5326869913786396</v>
+        <v>-0.6539238789636599</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.2211993648605599</v>
+        <v>-0.3647646271948659</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.3683949620529035</v>
+        <v>-0.5311523076406033</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 0.0008844</t>
+          <t>X &gt; 0.0008971</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2025</v>
+        <v>2033</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.4200720658631099</v>
+        <v>-0.40845004580585</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.09112028756479873</v>
+        <v>-0.1079588366932001</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.5084845103178566</v>
+        <v>-0.524208894443646</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.6465746546911433</v>
+        <v>-0.6615970911125117</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.109293866729779</v>
+        <v>-1.173522262541404</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.6378983692879387</v>
+        <v>-0.6784570427251353</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.385030153003441</v>
+        <v>-1.447988058697391</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.038067657403438</v>
+        <v>-1.103037947815508</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.515743767012971</v>
+        <v>-1.604192570013602</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-2.043486820966891</v>
+        <v>-2.156281889479537</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.481907527046033</v>
+        <v>-1.597257005665249</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-1.371168724727546</v>
+        <v>-1.463135585272987</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.9745084239810708</v>
+        <v>-1.093965225384643</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.9188092136165835</v>
+        <v>-1.063607986128645</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.002843</t>
+          <t>X &gt; 0.002854</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1783</v>
+        <v>1792</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.08670667641408158</v>
+        <v>-0.1001395257180135</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.2254466229199252</v>
+        <v>0.175003772883997</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.1390474213967039</v>
+        <v>-0.1331722117241583</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.4246907518256506</v>
+        <v>-0.4170762644680508</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.9886879178605525</v>
+        <v>-1.042949466168075</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.2703723751043015</v>
+        <v>-0.2958287014980741</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.162721174865929</v>
+        <v>-1.215696698573574</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.3701366307976528</v>
+        <v>-0.4282377093073464</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.3445532357206176</v>
+        <v>-0.4904346603364189</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.8280110517415267</v>
+        <v>-1.005439948680532</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.5538587761873899</v>
+        <v>-0.7332820917207172</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.2641802954140289</v>
+        <v>-0.4769928599998252</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.01968588409466321</v>
+        <v>-0.227627709391875</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.3397324737621261</v>
+        <v>-0.6168225792703836</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.004801</t>
+          <t>X &gt; 0.004812</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1539</v>
+        <v>1550</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.3541355158574007</v>
+        <v>0.4009566332064267</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.1269183711803805</v>
+        <v>-0.1240187435895734</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.6804218954499888</v>
+        <v>-0.6753677055324303</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.29015385217609</v>
+        <v>-1.280219780219781</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-1.664963757653837</v>
+        <v>-1.735423428498883</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.5574863187361316</v>
+        <v>-0.5941456320358043</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.771536860686972</v>
+        <v>-1.840428271776837</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-1.039310528818824</v>
+        <v>-1.115519493409074</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.6766462913244595</v>
+        <v>-0.7962319251597165</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.8431343172353536</v>
+        <v>-1.005941563881478</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.2986674407829</v>
+        <v>-0.4663891878792867</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.1613864270569181</v>
+        <v>-0.05016919807980003</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.297334244702661</v>
+        <v>0.04213689923189179</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.1546766600103453</v>
+        <v>-0.4465316806528605</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.00676</t>
+          <t>X &gt; 0.006769</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1283</v>
+        <v>1290</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.9193930884764612</v>
+        <v>0.9818298481751739</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.354920304862766</v>
+        <v>0.2845912742889567</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.07510880247087215</v>
+        <v>-0.1442136777580032</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.219545343850832</v>
+        <v>-1.280219780219781</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-1.871682103907069</v>
+        <v>-2.036538264453519</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-1.145275292414759</v>
+        <v>-1.260817573266607</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-2.508361204013376</v>
+        <v>-2.668187009519045</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.613989355924836</v>
+        <v>-1.782194094316758</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.208771046247151</v>
+        <v>-1.391894192847708</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.203988987876151</v>
+        <v>-1.401391109253751</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.4329076773523184</v>
+        <v>-0.6352612509819622</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.1118456013259888</v>
+        <v>-0.06971852622125141</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.1249832312301535</v>
+        <v>-0.1116331129688248</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.1506250772848716</v>
+        <v>-0.4390298051839991</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.008718</t>
+          <t>X &gt; 0.008726</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1083</v>
+        <v>1088</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.6813204497589567</v>
+        <v>0.6291056455406761</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.9537694360348468</v>
+        <v>0.9567565858625287</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.1504084016559659</v>
+        <v>0.1990513545996961</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.4963542471178002</v>
+        <v>-0.440931563882387</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-1.72106487278235</v>
+        <v>-1.792608953427504</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.006487677152065885</v>
+        <v>-0.0115626836554128</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.318218947952467</v>
+        <v>-1.392253436081226</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.9980513783632361</v>
+        <v>-1.078157486105866</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.6900298448491213</v>
+        <v>-0.7912307925502731</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.4329375710682797</v>
+        <v>-0.5579661159060265</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.5616232632914517</v>
+        <v>0.480242593664137</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.8727541831744503</v>
+        <v>0.7738637159464972</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.268101484842596</v>
+        <v>0.1554557746397478</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0.4540576514017189</v>
+        <v>0.2727520005615602</v>
       </c>
     </row>
     <row r="26">
@@ -3254,205 +3254,205 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.196361686260381</v>
+        <v>1.193591878816726</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.303502272006213</v>
+        <v>0.2640095649027003</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.2514499659989866</v>
+        <v>-0.2386608852856469</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.7222871312846806</v>
+        <v>-0.6534391534391517</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-1.973217961961979</v>
+        <v>-2.065585018814524</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.5136786785124414</v>
+        <v>-0.5343051692321907</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.312108501635279</v>
+        <v>-1.410218852654324</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.226690957576714</v>
+        <v>-1.270773665864965</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1.287673114099491</v>
+        <v>-1.358316568908641</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-1.474608485014983</v>
+        <v>-1.57493160655573</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.4638400300155112</v>
+        <v>-0.5119085360761559</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.650456352798308</v>
+        <v>-0.7222548443922463</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.6286182558354767</v>
+        <v>-0.7264505978156848</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.6238770807470644</v>
+        <v>-0.6362432054503628</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 0.01263</t>
+          <t>X &gt; 0.01264</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.01252228967562274</v>
+        <v>-0.04257935735451923</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.1785943284386136</v>
+        <v>0.06255524580132032</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.8026629820374325</v>
+        <v>-0.8506632619939012</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-1.260469181629155</v>
+        <v>-1.240259740259745</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-2.520267733163983</v>
+        <v>-2.700748304986845</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-1.36110417884634</v>
+        <v>-1.448606479275853</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-2.433596998814387</v>
+        <v>-2.613402073064542</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-2.239289981225468</v>
+        <v>-2.358580968571346</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-2.167997005473104</v>
+        <v>-2.326610421681579</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-1.827439611326774</v>
+        <v>-2.034194948155815</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.106214843661036</v>
+        <v>-1.250227005691002</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.8072864267554607</v>
+        <v>-0.9887599927871591</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.9628870155186036</v>
+        <v>-1.18008334611023</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-1.001701629842337</v>
+        <v>-1.121404346187674</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 0.01459</t>
+          <t>X &gt; 0.0146</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-1.791260858120559</v>
+        <v>-1.827517968231696</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.7242264759297896</v>
+        <v>-0.850968090930202</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-1.372686657142147</v>
+        <v>-1.586003007572558</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.8037887460473527</v>
+        <v>-0.944173573866415</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-2.290771251193888</v>
+        <v>-2.709639861342637</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-1.901911714312419</v>
+        <v>-2.094974000643369</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-3.985410135993369</v>
+        <v>-4.206912141150887</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-2.884534528909029</v>
+        <v>-3.045300808336712</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-3.468164769055505</v>
+        <v>-3.67909195174358</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-3.098571370263414</v>
+        <v>-3.383576931207564</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-1.386896221903392</v>
+        <v>-1.603935417319164</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-1.875166153171769</v>
+        <v>-2.141352987628323</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-1.424236867112349</v>
+        <v>-1.752459934500649</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-2.069581356258645</v>
+        <v>-2.273744539230826</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 0.01655</t>
+          <t>X &gt; 0.01656</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-1.680000698726566</v>
+        <v>-1.943218400850697</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.1930195547908369</v>
+        <v>-0.3517923114033792</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-1.153540175019884</v>
+        <v>-1.652559778176133</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.1261102559247931</v>
+        <v>-0.1621315192743822</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-2.711029871883539</v>
+        <v>-3.145711725985933</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-1.141342690068782</v>
+        <v>-1.285624619865423</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-1.795438219778006</v>
+        <v>-2.026552817934423</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.1839849236109359</v>
+        <v>-0.2248118821726379</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-1.399701491219169</v>
+        <v>-1.500704301657812</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-2.249620287549028</v>
+        <v>-2.430144810408187</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>0.3170411407958653</v>
+        <v>0.2276570975544132</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.3414213535000812</v>
+        <v>-0.5004629063531709</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.3931622042719525</v>
+        <v>0.1493479912175317</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.9977303210211446</v>
+        <v>-1.080569500452647</v>
       </c>
     </row>
     <row r="30">
@@ -3465,46 +3465,46 @@
         <v>344</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-1.466423276911165</v>
+        <v>-1.501466291745778</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.02233468173771769</v>
+        <v>-0.2027989964981671</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-1.579896764167167</v>
+        <v>-2.037459175014604</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.2868809229043947</v>
+        <v>-0.4666529435981914</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-3.150751871348923</v>
+        <v>-3.549562026913222</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.3442965768908124</v>
+        <v>0.1814367483898494</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-1.193902154468383</v>
+        <v>-1.320141531037336</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>1.827401294768137</v>
+        <v>1.960423403103817</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.8943261149895463</v>
+        <v>1.058897479845982</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.04440731865968672</v>
+        <v>0.235068899030999</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>2.165287555748336</v>
+        <v>2.505483264841345</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>1.036875010429242</v>
+        <v>1.284434118818453</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.6167241571158328</v>
+        <v>0.7654137048936605</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.5517621329237556</v>
+        <v>0.723760892490418</v>
       </c>
     </row>
     <row r="31">
@@ -3517,46 +3517,46 @@
         <v>257</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.437371907208842</v>
+        <v>0.203066469686668</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>1.549921222705322</v>
+        <v>1.333067679104445</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.3769397212187684</v>
+        <v>0.164135892340127</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.5071648648071303</v>
+        <v>0.2940199335548073</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.03112468828856407</v>
+        <v>-0.1952292073971122</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>2.989984749906824</v>
+        <v>2.790734605995468</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>1.737959215543384</v>
+        <v>1.567287819095583</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>3.994625980316961</v>
+        <v>4.202230252510695</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>2.766328648696913</v>
+        <v>3.002466945699481</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>3.86193514419584</v>
+        <v>4.116622861008523</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>4.435444102667162</v>
+        <v>4.687676211922046</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>4.85892731338825</v>
+        <v>4.982623934416495</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>5.216986576806356</v>
+        <v>5.365676124584184</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>5.053617168667131</v>
+        <v>5.225615928233793</v>
       </c>
     </row>
     <row r="32">
@@ -3569,46 +3569,46 @@
         <v>185</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>1.573138023519704</v>
+        <v>1.543942229167072</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.03804806954412498</v>
+        <v>-0.03923485598878074</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>1.18880216732245</v>
+        <v>1.188648777318129</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>1.859567851451359</v>
+        <v>1.859073359073356</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.8408838638064964</v>
+        <v>-0.7923379440407246</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.00296929363087628</v>
+        <v>0.02098811531873679</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-1.709301274518658</v>
+        <v>-1.661289595528338</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.5263327843972974</v>
+        <v>0.5755803467910141</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.07518991266601205</v>
+        <v>-0.001932802886315699</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>1.23705345316629</v>
+        <v>1.336400778460863</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>3.735054997608799</v>
+        <v>3.834963033627474</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>3.769433149964122</v>
+        <v>3.893129770992367</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>4.430363377731794</v>
+        <v>4.579052925509622</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>3.575017946877246</v>
+        <v>3.747016706443908</v>
       </c>
     </row>
     <row r="33">
@@ -3621,46 +3621,46 @@
         <v>146</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>2.313604517410852</v>
+        <v>2.28440872305822</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-2.722239109899547</v>
+        <v>-2.723425896344203</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.3076470395919841</v>
+        <v>0.3074936495876628</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-1.616922337367598</v>
+        <v>-1.617416829745601</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-2.840143397312609</v>
+        <v>-2.791597477546837</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-3.912632381376149</v>
+        <v>-3.888674972426536</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-3.997342740642317</v>
+        <v>-3.949331061651996</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-1.724685357031795</v>
+        <v>-1.675437794638079</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-3.840462034102515</v>
+        <v>-3.767204924322819</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-2.635586309884431</v>
+        <v>-2.536238984589858</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>1.269301572951264</v>
+        <v>1.369209608969939</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.06618328839203969</v>
+        <v>0.05751333263620495</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>2.938323392541129</v>
+        <v>3.087012940318957</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>1.794196029069028</v>
+        <v>1.96619478863569</v>
       </c>
     </row>
     <row r="34">
@@ -3673,46 +3673,46 @@
         <v>112</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>1.983369683751356</v>
+        <v>1.954173889398724</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-2.306387837883889</v>
+        <v>-2.307574624328545</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.9154449369246507</v>
+        <v>-0.915598326928972</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-6.142362650479143</v>
+        <v>-6.142857142857146</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-6.680652203574837</v>
+        <v>-6.632106283809065</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-4.597563888225466</v>
+        <v>-4.573606479275853</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-4.682274247491634</v>
+        <v>-4.634262568501313</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.6850571769926646</v>
+        <v>-0.6358096145989478</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-1.63889647637258</v>
+        <v>-1.565639366592883</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.7031009869881473</v>
+        <v>-0.6037536616935739</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>2.66362642618023</v>
+        <v>2.763534462198905</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.9122902928212611</v>
+        <v>1.035986913849506</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>3.170710868079283</v>
+        <v>3.31940041585711</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>3.396446518305815</v>
+        <v>3.568445277872478</v>
       </c>
     </row>
     <row r="35">
@@ -3722,49 +3722,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.5311321622367373</v>
+        <v>1.061316746541586</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-5.899331039260829</v>
+        <v>-5.283765100519027</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-6.294102424015868</v>
+        <v>-5.677503088833731</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-10.98315438886124</v>
+        <v>-10.30952380952382</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-10.3166246648485</v>
+        <v>-9.60829675999954</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-11.22406991232185</v>
+        <v>-11.716463622133</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-10.10396099447959</v>
+        <v>-10.58664352088227</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-3.342113975615725</v>
+        <v>-2.719142947932269</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-5.81273468635537</v>
+        <v>-5.137067938021453</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-6.662653482685229</v>
+        <v>-5.960896518836435</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-2.048077532511684</v>
+        <v>-1.403132204467759</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-5.628157211481664</v>
+        <v>-4.916394038531443</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-2.433850233469769</v>
+        <v>-1.740123393666693</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-4.617753137460106</v>
+        <v>-3.872030912603705</v>
       </c>
     </row>
   </sheetData>
@@ -3904,1041 +3904,1041 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.02849</t>
+          <t>X &lt; -0.02846</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-5.492964223305435</v>
+        <v>-4.891064205839371</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-9.513788870586133</v>
+        <v>-8.855193671947596</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-2.679644592690572</v>
+        <v>-2.106074517405155</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-3.754238726210644</v>
+        <v>-3.166666666666671</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.6780704479810353</v>
+        <v>-0.08448723619001441</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-3.995154249671252</v>
+        <v>-3.383130288799663</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.4654067776121167</v>
+        <v>0.1276421934034531</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>2.681982409926441</v>
+        <v>3.23323800444868</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>6.235458084728968</v>
+        <v>6.767693966740453</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>4.180720011290681</v>
+        <v>4.753389195449273</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>3.976018853030489</v>
+        <v>4.549248747913182</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>5.215216282494239</v>
+        <v>5.797891675754272</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>3.590246152072403</v>
+        <v>4.212257558714249</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>3.815981802298936</v>
+        <v>4.461302420729616</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -0.02653</t>
+          <t>X &lt; -0.0265</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-3.342984996051598</v>
+        <v>-2.93746225223741</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-4.954171089115427</v>
+        <v>-4.520639337393263</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-1.900666611801498</v>
+        <v>-1.495573906904546</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-4.356648364764858</v>
+        <v>-3.929792429792435</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.5845930902743461</v>
+        <v>-0.1455372972400752</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-2.011356991673743</v>
+        <v>-1.582153487822858</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.4901395456118109</v>
+        <v>0.9212929870542439</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>3.471346763894033</v>
+        <v>3.874263645474322</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>5.134502538405748</v>
+        <v>5.546692745739229</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>3.42251477655865</v>
+        <v>3.868163310223395</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>3.217813618298457</v>
+        <v>3.664022862687304</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>4.114260736171019</v>
+        <v>4.576890454753048</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>2.832040917340372</v>
+        <v>3.327031673488371</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>2.195707602049652</v>
+        <v>1.866674826102035</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.02457</t>
+          <t>X &lt; -0.02455</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>142</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-1.072465326309</v>
+        <v>-1.101661120661632</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-4.092102123598181</v>
+        <v>-4.093288910042837</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.4427039564355155</v>
+        <v>0.4425505664311942</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-2.948197660539506</v>
+        <v>-2.948692152917509</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.03463954692818305</v>
+        <v>0.08318546669395488</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-1.780662479774762</v>
+        <v>-1.756705070825149</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.4569221348155708</v>
+        <v>-0.4089104558252501</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>1.892910629848387</v>
+        <v>1.942158192242104</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>3.240379177550963</v>
+        <v>3.31363628733066</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>2.390460381221104</v>
+        <v>2.489807706515677</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>1.481533870848239</v>
+        <v>1.581441906866914</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>3.628588079541586</v>
+        <v>3.752284700569831</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>1.799986522002825</v>
+        <v>1.948676069780653</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.6172714680040059</v>
+        <v>0.7892702275706682</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.02262</t>
+          <t>X &lt; -0.02259</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>191</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.3986651212981016</v>
+        <v>0.3694693269454703</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.1654005529175606</v>
+        <v>-0.1665873393622164</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.486948481175574</v>
+        <v>0.4867950911712526</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-2.524187631780563</v>
+        <v>-2.524682124158566</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>1.126004490516408</v>
+        <v>1.17455041028218</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.3762581013033284</v>
+        <v>0.4002155102529414</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.8151079514612505</v>
+        <v>0.8631196304515711</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>2.442280145370844</v>
+        <v>2.491527707764561</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>3.951978617120318</v>
+        <v>4.025235726900014</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>3.102059820790458</v>
+        <v>3.201407146085032</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>3.420918871954342</v>
+        <v>3.520826907973017</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>3.455297024309665</v>
+        <v>3.57899364533791</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.9409053332999306</v>
+        <v>1.089594881077758</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-1.45116006359396</v>
+        <v>-1.279161304027298</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.02066</t>
+          <t>X &lt; -0.02063</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.0190839694656475</v>
+        <v>-0.03077298191177391</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-1.592102123598181</v>
+        <v>-1.200726926571761</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.3202068416865558</v>
+        <v>0.05842764709699821</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-1.439981698098194</v>
+        <v>-1.051357733175919</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.9383954154727832</v>
+        <v>1.351955109343237</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.4024361117745414</v>
+        <v>0.7982943471704331</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.7343924191750375</v>
+        <v>1.150861398440838</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>2.35065710872162</v>
+        <v>2.751144340536825</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>1.456341618865515</v>
+        <v>1.887725450408297</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>1.02308948920232</v>
+        <v>1.47712001008918</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>1.235054997608792</v>
+        <v>1.686202703048956</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>2.102766483297458</v>
+        <v>2.570815721405594</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.01594896331737772</v>
+        <v>0.5227652328582906</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-1.424982053122747</v>
+        <v>-0.8810824671098061</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.0187</t>
+          <t>X &lt; -0.01868</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.3773561599841884</v>
+        <v>-0.2520473087579518</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.3704192757017495</v>
+        <v>-0.2223211681073565</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.2056831259509906</v>
+        <v>0.3516827790618109</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.3113409213991574</v>
+        <v>-0.1635944700460783</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>2.386615480197698</v>
+        <v>2.572962840614899</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>3.978487891709811</v>
+        <v>4.13607094007898</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>4.864651318851415</v>
+        <v>4.720576141176103</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>6.015705652410944</v>
+        <v>5.867646606599209</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>5.307474304949665</v>
+        <v>5.185512707139843</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>5.42842929502757</v>
+        <v>5.329426061808725</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>4.900103541298115</v>
+        <v>4.802704969111339</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>5.581730884591956</v>
+        <v>5.506032996798815</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>3.867081649401527</v>
+        <v>3.820552489589836</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>3.445568108689542</v>
+        <v>3.747016706443908</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.01674</t>
+          <t>X &lt; -0.01672</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.8689598999867414</v>
+        <v>0.9212607241326225</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.2503296381884184</v>
+        <v>0.318475795839511</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2.336947831597158</v>
+        <v>2.375718199681671</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1.72275610173638</v>
+        <v>2.015406162464984</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>3.169578211171711</v>
+        <v>3.486941335238555</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>4.211369114255923</v>
+        <v>4.495020971704541</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>5.615492501888021</v>
+        <v>5.904953117773189</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>6.140979689366787</v>
+        <v>6.174414475036919</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>5.831858575027631</v>
+        <v>5.892343826684431</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>6.222634567779664</v>
+        <v>6.294005441947881</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>5.025377578253959</v>
+        <v>5.354570876764733</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>6.548589477507548</v>
+        <v>6.638227810208051</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>5.632160708561386</v>
+        <v>5.752873805212857</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>4.865340527522406</v>
+        <v>5.021526510365483</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.01478</t>
+          <t>X &lt; -0.01476</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1.959238409620092</v>
+        <v>1.825148290719945</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1.892453860957801</v>
+        <v>1.783397024446565</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>3.235134213654497</v>
+        <v>3.123763082374637</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>3.172309164192669</v>
+        <v>3.060968896229006</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>4.178421155498526</v>
+        <v>4.11314557415956</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>5.441046150384572</v>
+        <v>5.349322229780029</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>5.549385984168602</v>
+        <v>5.481344367914872</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>5.468417726482244</v>
+        <v>5.400868062252144</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>5.986586149110046</v>
+        <v>5.941930135196273</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>5.522767738880574</v>
+        <v>5.503458009101912</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>4.545865808419613</v>
+        <v>4.528604652124585</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>6.317695698226665</v>
+        <v>6.320875435732255</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>5.318394265762677</v>
+        <v>5.347682827087496</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>4.771929143788441</v>
+        <v>4.826014779661634</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.01282</t>
+          <t>X &lt; -0.0128</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1.437579267271296</v>
+        <v>1.324003981059811</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1.864010729066393</v>
+        <v>1.775255690896124</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>3.350117087258063</v>
+        <v>3.259451974881898</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>2.226423735548622</v>
+        <v>2.137379834562935</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>3.25553230157518</v>
+        <v>3.21307592052807</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>4.493345202683628</v>
+        <v>4.42482857549723</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>4.722114467241916</v>
+        <v>4.67716153165518</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>5.195484694928524</v>
+        <v>5.150295907422077</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>6.545160845615783</v>
+        <v>6.678268525202341</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>5.851981861198141</v>
+        <v>6.010934467079053</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>4.236622395727927</v>
+        <v>4.398343315317611</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>6.308618102942177</v>
+        <v>6.490938847674684</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>5.104768190067645</v>
+        <v>5.313308307652335</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>4.703544592645265</v>
+        <v>4.936375078900866</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.01087</t>
+          <t>X &lt; -0.01085</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>2.313604517410852</v>
+        <v>2.148273268280718</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1.823215435554999</v>
+        <v>1.683108605485117</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>3.919104075706557</v>
+        <v>3.898066269344319</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>2.928532208086942</v>
+        <v>3.034161490683225</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>3.261973663708559</v>
+        <v>3.41447756712261</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>4.680144704551623</v>
+        <v>4.805275508301783</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>3.848236337813475</v>
+        <v>3.875054201685025</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>4.128365701498716</v>
+        <v>4.154563056208517</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>5.686312561165224</v>
+        <v>5.732497279369859</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>5.95719077604334</v>
+        <v>6.150904723399584</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>5.005291610311168</v>
+        <v>5.201422660956666</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>6.160466773874461</v>
+        <v>6.377601820681811</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>5.491249918070395</v>
+        <v>5.733996689149038</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>5.966051570787585</v>
+        <v>6.231488756133352</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.008907</t>
+          <t>X &lt; -0.008889</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>2.302568360200794</v>
+        <v>2.263757521846692</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>2.000546416180264</v>
+        <v>2.087615612570225</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>3.217053984093909</v>
+        <v>3.301917825260546</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>2.340229782264345</v>
+        <v>2.426776740847089</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>3.413219181837334</v>
+        <v>3.545567800900194</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>3.912003080556005</v>
+        <v>4.019358344844754</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>2.920948310413706</v>
+        <v>3.054179642553969</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>2.856699404794142</v>
+        <v>2.990356932421882</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>3.802766593689284</v>
+        <v>3.85790693635041</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>4.463421815486313</v>
+        <v>4.541616043977633</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>3.855900919058946</v>
+        <v>4.035968058753106</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>3.89027907141427</v>
+        <v>4.094134796117999</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>3.77224302172624</v>
+        <v>4.00048440724261</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>3.997978671952772</v>
+        <v>4.249529269257977</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.006949</t>
+          <t>X &lt; -0.006932</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1182</v>
+        <v>1186</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>2.087611888247373</v>
+        <v>2.043007905298509</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1.745461328178472</v>
+        <v>1.640269268709268</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>2.873532583017344</v>
+        <v>2.848554889163545</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>2.326938775675067</v>
+        <v>2.388219706094915</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>2.634672911242667</v>
+        <v>2.742140885547713</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>2.847444572011426</v>
+        <v>2.8462923402857</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>3.101143688210563</v>
+        <v>3.207221411262594</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>3.649303470819767</v>
+        <v>3.668876003324449</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>4.265140265227615</v>
+        <v>4.390756682551903</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>4.684257001892675</v>
+        <v>4.831683582344006</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>4.479555843632482</v>
+        <v>4.627543134807915</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>4.852343471453125</v>
+        <v>5.022978000334696</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>4.6859997247387</v>
+        <v>4.880771169892284</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>5.165542481564223</v>
+        <v>5.382767128029066</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.004991</t>
+          <t>X &lt; -0.004975</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1419</v>
+        <v>1422</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.289344716470573</v>
+        <v>1.287356529543395</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1.36949054729682</v>
+        <v>1.46226664551272</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>2.454634595945578</v>
+        <v>2.47499841809816</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>2.162026758561431</v>
+        <v>2.182941531042793</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>2.469403167410768</v>
+        <v>2.607897734675966</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.991583398596241</v>
+        <v>2.10712488499982</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>2.400178183798012</v>
+        <v>2.538733212089404</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>2.426414684479205</v>
+        <v>2.565164868021107</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>3.704403634369399</v>
+        <v>3.794015043694436</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>4.122983780957078</v>
+        <v>4.236009247689587</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>3.495449641724377</v>
+        <v>3.60992787188345</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>3.600299957575118</v>
+        <v>3.738418097293348</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>3.180149104261709</v>
+        <v>3.413583658774535</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>3.194468264001976</v>
+        <v>3.451658056654885</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; -0.003032</t>
+          <t>X &lt; -0.003017</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>1638</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1.731538181919859</v>
+        <v>1.702342387567228</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.097153065657011</v>
+        <v>1.095966279212355</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.98443296295325</v>
+        <v>1.984279572948928</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>2.053608045491551</v>
+        <v>2.053113553113548</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>2.49211946919683</v>
+        <v>2.540665388962601</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.690592399930821</v>
+        <v>1.714549808880435</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1.789032223814836</v>
+        <v>1.837043902805156</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.56616382422834</v>
+        <v>1.615411386622057</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>2.420932583456477</v>
+        <v>2.494189693236173</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>2.608864824977665</v>
+        <v>2.708212150272239</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>2.648363910917716</v>
+        <v>2.748271946936391</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>2.438541819072796</v>
+        <v>2.562238440101041</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>2.018390965759387</v>
+        <v>2.167080513537215</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>2.122026493885798</v>
+        <v>2.29402525345246</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; -0.001074</t>
+          <t>X &lt; -0.00106</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1867</v>
+        <v>1868</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.4382055548968182</v>
+        <v>0.4342136569117301</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.005380468796040816</v>
+        <v>0.02876676447536397</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.2533514514753747</v>
+        <v>0.277427063098564</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.3835765950637366</v>
+        <v>0.4073111043132442</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.5951531373081664</v>
+        <v>0.6675266314555373</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.4465194318783787</v>
+        <v>-0.3980176141794942</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.111512576289833</v>
+        <v>0.1837245835329497</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.07293884412601415</v>
+        <v>0.1461573477748672</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.8153846468962271</v>
+        <v>0.9121825973104549</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>1.250950585435142</v>
+        <v>1.373150590371274</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.8320019713634892</v>
+        <v>0.9548773805225466</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.6521326679073454</v>
+        <v>0.798911355574802</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.3391055424996736</v>
+        <v>0.5108198101672983</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.4577174648204689</v>
+        <v>0.6527982910263432</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 0.0008844</t>
+          <t>X &lt; 0.0008971</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2104</v>
+        <v>2107</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.5133805474124102</v>
+        <v>0.503651820105901</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.1854644163257717</v>
+        <v>0.2019175446320602</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.5036207882247297</v>
+        <v>0.5200922283629197</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.6813744489233571</v>
+        <v>0.6974371143806337</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.188712272253511</v>
+        <v>1.252326559095536</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.7256300281243426</v>
+        <v>0.7657385610658594</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1.543961493953226</v>
+        <v>1.606838523098119</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.124421367276767</v>
+        <v>1.188466607517817</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1.681309933187443</v>
+        <v>1.768484980820496</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>2.067132581724508</v>
+        <v>2.178638364884499</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>1.482203286582184</v>
+        <v>1.594811158924102</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1.326467370496445</v>
+        <v>1.415673672273812</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.00137355140356</v>
+        <v>1.115437435316061</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.894409581858234</v>
+        <v>1.032256383710163</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.002843</t>
+          <t>X &lt; 0.002854</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2346</v>
+        <v>2348</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.1618802184000003</v>
+        <v>0.1730227577365326</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.08528200424609622</v>
+        <v>-0.04729231719786497</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.1167070543066302</v>
+        <v>0.1126323861399072</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.3748094357466485</v>
+        <v>0.370284740812842</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.8595377854642621</v>
+        <v>0.903182107527023</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.3043968960882637</v>
+        <v>0.3241788699575352</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.072201455833181</v>
+        <v>1.11531153712049</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.392004082293667</v>
+        <v>0.4365315876400473</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.4588991636225472</v>
+        <v>0.5699167297809282</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.7172497620070999</v>
+        <v>0.853413532270892</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.4699228577963552</v>
+        <v>0.6066836469153785</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.2059207884977923</v>
+        <v>0.3667243195443319</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.04152441088771752</v>
+        <v>0.2271030198970223</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.2672600611142499</v>
+        <v>0.4761478819123894</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.004801</t>
+          <t>X &lt; 0.004812</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>2590</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.1257036753220007</v>
+        <v>-0.154899469674632</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.1550021235060655</v>
+        <v>0.1538153370614097</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.4166013951216812</v>
+        <v>0.4164480051173598</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.8170968089803097</v>
+        <v>0.8166023166023066</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.089618066695429</v>
+        <v>1.138163986461201</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.4217411310795569</v>
+        <v>0.44569854002917</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>1.225061659844272</v>
+        <v>1.273073338834593</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.7193829774474949</v>
+        <v>0.7686305398412117</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.5811807437046426</v>
+        <v>0.6544378534843389</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.5806827967956281</v>
+        <v>0.6800301220902014</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.2215414840952832</v>
+        <v>0.3214495201139584</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.09157071103973635</v>
+        <v>0.03212590998850828</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.1256211782527572</v>
+        <v>0.02306836952507041</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.1001144719737752</v>
+        <v>0.2721132315404375</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.00676</t>
+          <t>X &lt; 0.006769</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2846</v>
+        <v>2850</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.3390620979500838</v>
+        <v>-0.3697609476939974</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.08929313483414347</v>
+        <v>-0.05820119074459029</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.04262087366925016</v>
+        <v>0.07437661041439014</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.594194331864351</v>
+        <v>0.6253132832080155</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.9337137675327085</v>
+        <v>1.01325712471224</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.5990653252576834</v>
+        <v>0.6544636961627432</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1.286826876103873</v>
+        <v>1.365737431498694</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.8197582323171346</v>
+        <v>0.8999046711153511</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.7081856652301184</v>
+        <v>0.7927566233820542</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.6157926983847943</v>
+        <v>0.7057701478302292</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.2354063679531464</v>
+        <v>0.3261911038029126</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.04644878960018417</v>
+        <v>0.03348064818534624</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.009818195267762064</v>
+        <v>0.09446307249871921</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.07536931722159323</v>
+        <v>0.2031570573210999</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.008718</t>
+          <t>X &lt; 0.008726</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3046</v>
+        <v>3052</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.1701982330908933</v>
+        <v>-0.1525479741993578</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.273681933496583</v>
+        <v>-0.2773701416183414</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.04570667780586035</v>
+        <v>-0.06369793374417299</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.2156230216658273</v>
+        <v>0.1972477064220186</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.6933937766658289</v>
+        <v>0.7237259573442785</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.0730359151176998</v>
+        <v>0.07908028350264829</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.6110721962972931</v>
+        <v>0.6409667892968471</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.4389888032480087</v>
+        <v>0.4700226265544032</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.3962323292480363</v>
+        <v>0.4330500174176066</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.2205039420283939</v>
+        <v>0.2645294313601596</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.1625827976667935</v>
+        <v>-0.1362034146031945</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.3067073160680422</v>
+        <v>-0.2746290756655654</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.05189958122190319</v>
+        <v>-0.01447900747185571</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.1544633400564308</v>
+        <v>-0.09308814283524924</v>
       </c>
     </row>
     <row r="26">
@@ -4948,205 +4948,205 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3224</v>
+        <v>3232</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.2679788593799159</v>
+        <v>-0.2689989964480333</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.02215473888756492</v>
+        <v>-0.01165625698160966</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.07827659997237646</v>
+        <v>0.07529911463348071</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.2394519137866737</v>
+        <v>0.2220650636492252</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.6296674674690621</v>
+        <v>0.6610337444794752</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.2151875819076139</v>
+        <v>0.222185599932061</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.5018792653526916</v>
+        <v>0.5328166394194724</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.423412526678284</v>
+        <v>0.4382710077490017</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0.5035182473366646</v>
+        <v>0.5250607748498339</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.4763112983720887</v>
+        <v>0.5056876395794063</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.1651758528923466</v>
+        <v>0.1777848158056941</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.1860481530639362</v>
+        <v>0.2050109591111706</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.2174993509142809</v>
+        <v>0.2430213493790347</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.1817176987382894</v>
+        <v>0.1826602708003406</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 0.01263</t>
+          <t>X &lt; 0.01264</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3373</v>
+        <v>3380</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.06346266769049436</v>
+        <v>0.07634989547955939</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.02032391190477512</v>
+        <v>0.04627347907602797</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.1876827046645317</v>
+        <v>0.2009352430207443</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.3179078482528936</v>
+        <v>0.3174133558748906</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.6376064608376737</v>
+        <v>0.6861523806034455</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.3728503129579721</v>
+        <v>0.3968077219075852</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.6727553383071836</v>
+        <v>0.7207670172975043</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.5772034241995811</v>
+        <v>0.609963842712979</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.62152811975362</v>
+        <v>0.6617486300258832</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.4692201771896904</v>
+        <v>0.5183934219919664</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.2812635284144847</v>
+        <v>0.3142529744558757</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.1842479647789403</v>
+        <v>0.2244907177379218</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.2550321484586533</v>
+        <v>0.3027055722391907</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.2308139741526603</v>
+        <v>0.255892446088879</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 0.01459</t>
+          <t>X &lt; 0.0146</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3555</v>
+        <v>3562</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.3545696516666581</v>
+        <v>0.3634513935038228</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.1751634575360157</v>
+        <v>0.1972326827782496</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.2295779234266817</v>
+        <v>0.2675313064110441</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.1632842573575459</v>
+        <v>0.1883116883116784</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.4391440585571971</v>
+        <v>0.5127550277189101</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.3715545845426433</v>
+        <v>0.4081504671176361</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.7641041915875348</v>
+        <v>0.8121158705778555</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.5372619949895281</v>
+        <v>0.5708760355173652</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.6885513566932318</v>
+        <v>0.7304222360380663</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.5567834107158518</v>
+        <v>0.608446546856996</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.2555721420719763</v>
+        <v>0.2920096366594791</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.3058402345860003</v>
+        <v>0.3501763740243717</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.2671675609926751</v>
+        <v>0.3199819511101865</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.3401374968069248</v>
+        <v>0.3725080034680488</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 0.01655</t>
+          <t>X &lt; 0.01656</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3696</v>
+        <v>3705</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.2586251300594427</v>
+        <v>0.2916123130440553</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.07793836223178374</v>
+        <v>0.09695630687982515</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.1420063836845671</v>
+        <v>0.203000055820354</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.01700174322649417</v>
+        <v>0.05105342217771636</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.384565187729514</v>
+        <v>0.4394763945697235</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.1958468598166618</v>
+        <v>0.2146319884878451</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.3271775483495816</v>
+        <v>0.357642450386976</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.0910676975925071</v>
+        <v>0.09558618258633089</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.2881888673569151</v>
+        <v>0.3015285532066159</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.3181345342473705</v>
+        <v>0.3413976781946104</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.006496773140057144</v>
+        <v>0.00230446412680152</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.04309458857958504</v>
+        <v>0.06047120149169416</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.01019836334387492</v>
+        <v>0.0161904679103273</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.1226369944962897</v>
+        <v>0.1302825633939761</v>
       </c>
     </row>
     <row r="30">
@@ -5156,49 +5156,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3785</v>
+        <v>3796</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.1922469929052113</v>
+        <v>0.1961414594009767</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.05590946449768808</v>
+        <v>0.07228270625151367</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.1495859226267555</v>
+        <v>0.1922580648390948</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.05705387502433723</v>
+        <v>0.07356973817662293</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.350185961949677</v>
+        <v>0.3876953243670869</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.02938048298466356</v>
+        <v>0.04359951914561577</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.2227890436476088</v>
+        <v>0.234158484130262</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.09790527587346531</v>
+        <v>-0.111940551311605</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.04033458280570557</v>
+        <v>0.02354290979318563</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.04954765758448332</v>
+        <v>0.03067577507981412</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.1667401449466368</v>
+        <v>-0.1998012539679976</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.09114250358750553</v>
+        <v>-0.1152979350913839</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.02102937793988957</v>
+        <v>-0.03639739444425061</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.04453291177533458</v>
+        <v>-0.06225621241805612</v>
       </c>
     </row>
     <row r="31">
@@ -5208,49 +5208,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3872</v>
+        <v>3883</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.02873647911815169</v>
+        <v>0.0444452996316258</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.04987761278458436</v>
+        <v>-0.03576451353538346</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.01867881352963252</v>
+        <v>-0.004622582919580509</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.003222295728278368</v>
+        <v>0.0107913669064672</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.06512392187148208</v>
+        <v>0.07522198288697268</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.1388010016275345</v>
+        <v>-0.1263057080676262</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.003233257545772972</v>
+        <v>0.007033394471179122</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.1983372182510408</v>
+        <v>-0.2132640531644938</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.06459381230979488</v>
+        <v>-0.08175535762526209</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.203690696556194</v>
+        <v>-0.2223478827067424</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.2649450023911939</v>
+        <v>-0.2834410847766478</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.3193639589672088</v>
+        <v>-0.3282344503718591</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.3119622166464708</v>
+        <v>-0.3228314511430312</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.3299407308087012</v>
+        <v>-0.3426047202880014</v>
       </c>
     </row>
     <row r="32">
@@ -5260,49 +5260,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3944</v>
+        <v>3955</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.01692816093616756</v>
+        <v>-0.01515214746763149</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.05349949419757394</v>
+        <v>0.05342145043108104</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.04945252225966357</v>
+        <v>-0.04930627304236168</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.05720476334857238</v>
+        <v>-0.05701675373807547</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.1012674957493616</v>
+        <v>0.09810850644608848</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.05830655711866939</v>
+        <v>0.05672407838248006</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.1899100096584547</v>
+        <v>0.186535008480007</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.04053052644314903</v>
+        <v>0.03749618840895863</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.1201383606566964</v>
+        <v>0.1154573145038</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.006545769156339531</v>
+        <v>-0.01242468251413698</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.1463739357583194</v>
+        <v>-0.1518990179137134</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.1738005043693818</v>
+        <v>-0.1806635067432936</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.1741651051236843</v>
+        <v>-0.1825134942974387</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.1623045683357347</v>
+        <v>-0.1720730533538202</v>
       </c>
     </row>
     <row r="33">
@@ -5312,49 +5312,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3983</v>
+        <v>3994</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.02846357808190447</v>
+        <v>-0.0269573452263856</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.1507013807822943</v>
+        <v>0.150345638134894</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.005150924477405283</v>
+        <v>-0.005129270392494334</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.0886308739028081</v>
+        <v>0.08841158841158148</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.165182322620403</v>
+        <v>0.1623514443234058</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.2007322781488696</v>
+        <v>0.1990072138775716</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.2550691109043512</v>
+        <v>0.2520158618910884</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.1276688911232355</v>
+        <v>0.1249046711153454</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.2560741497916297</v>
+        <v>0.2517792737814943</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.147431099435579</v>
+        <v>0.1421550069264441</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.01808097830690514</v>
+        <v>-0.02293038643757939</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.005317717090846941</v>
+        <v>-0.0007641229015291628</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.07441248246574617</v>
+        <v>-0.08150249850012159</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.0604327184504001</v>
+        <v>-0.06870687893415806</v>
       </c>
     </row>
     <row r="34">
@@ -5364,49 +5364,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4017</v>
+        <v>4028</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.0004735476294186469</v>
+        <v>0.00164269132188366</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.114897131800177</v>
+        <v>0.1146318820363774</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.03149789184538321</v>
+        <v>0.03141826133545322</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.2000936267921318</v>
+        <v>0.1995683860468347</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.2466418138831088</v>
+        <v>0.2440216754251665</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.1850448074267064</v>
+        <v>0.1835788527360407</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.2382028896853043</v>
+        <v>0.2356259073351126</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.08307073039699731</v>
+        <v>0.08086649560716097</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.1601374086881648</v>
+        <v>0.1567579980063201</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.07007199769938666</v>
+        <v>0.06588919544927307</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.0460395297543883</v>
+        <v>-0.04992905270346881</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.02255490676641614</v>
+        <v>-0.02746576250639521</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.05539664809791844</v>
+        <v>-0.06122398580227895</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.08940824182079155</v>
+        <v>-0.09608160537336374</v>
       </c>
     </row>
     <row r="35">
@@ -5416,49 +5416,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4046</v>
+        <v>4056</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.04433649471818057</v>
+        <v>0.03351068678664149</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.1710817108030014</v>
+        <v>0.1594151214222563</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.1347680987456172</v>
+        <v>0.1232509477206492</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.2538052841503315</v>
+        <v>0.2419717518094302</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.2715232412023312</v>
+        <v>0.2581590474156741</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.2865012326428058</v>
+        <v>0.2984407648186362</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.3140247902581876</v>
+        <v>0.3251270450847059</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.1319996556120486</v>
+        <v>0.1190085608248452</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.2327754212188395</v>
+        <v>0.2187557507251654</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.1866697361159098</v>
+        <v>0.1721084072719421</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.0699525031657231</v>
+        <v>0.05570705924954211</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.1182473792131304</v>
+        <v>0.1030854141663511</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.08266504930700336</v>
+        <v>0.06686511531835748</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.0999808732242542</v>
+        <v>0.08330861965889369</v>
       </c>
     </row>
   </sheetData>
